--- a/results/Расчет_ступеней_по_высоте_лопаток.xlsx
+++ b/results/Расчет_ступеней_по_высоте_лопаток.xlsx
@@ -421,22 +421,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -505,6 +506,11 @@
           <t>Ступень 11</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Ступень 12</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
@@ -518,37 +524,40 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>137.6514715849328</v>
+        <v>133.7990100654321</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>153.5943270905852</v>
+        <v>147.4771701302632</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>169.5371825962376</v>
+        <v>161.1553301950943</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>185.48003810189</v>
+        <v>174.8334902599253</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>201.4228936075424</v>
+        <v>188.5116503247563</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>217.3657491131949</v>
+        <v>202.1898103895874</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>233.3086046188473</v>
+        <v>215.8679704544184</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>249.2514601244997</v>
+        <v>229.5461305192495</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>265.1943156301521</v>
+        <v>243.2242905840805</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>281.1371711358045</v>
+        <v>256.9024506489116</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>297.0800266414569</v>
+        <v>270.5806107137426</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>284.2587707785736</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
@@ -563,37 +572,40 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>161.7529180149682</v>
+        <v>147.4023960256757</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>218.9622143471205</v>
+        <v>207.1677018653433</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>233.8018507177582</v>
+        <v>222.2870738601373</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>243.6471249748124</v>
+        <v>231.7127585522443</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>252.0500627921624</v>
+        <v>239.3954249508763</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>259.9187119048945</v>
+        <v>246.3781226232185</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>267.591582886775</v>
+        <v>253.0541152880725</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>275.1750487792977</v>
+        <v>259.5678801883332</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>282.7205751657111</v>
+        <v>265.9844995703933</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>290.243137984971</v>
+        <v>272.3280041197528</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>297.7354674932853</v>
+        <v>278.5969941775153</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>284.7694881357876</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -608,37 +620,40 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>54.44537991517427</v>
+        <v>63.81194118956999</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>55.76408404729032</v>
+        <v>63.54846186139981</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>57.55978582867928</v>
+        <v>63.77128437530303</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>59.83940389255535</v>
+        <v>64.44695292226675</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>62.61670154700634</v>
+        <v>65.5561918560761</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>65.90825124681709</v>
+        <v>67.09631622902928</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>69.73957136066241</v>
+        <v>69.07694721208168</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>74.14098555007563</v>
+        <v>71.5265125265511</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>79.14866946516834</v>
+        <v>74.48786683281418</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>84.80465074463035</v>
+        <v>78.02011719604894</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>91.15680901572985</v>
+        <v>82.19560102427094</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>87.10460458972355</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
@@ -653,37 +668,40 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>135.2095371557407</v>
+        <v>119.5614139338028</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>141.1432602644053</v>
+        <v>126.0550576330157</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>147.393984470497</v>
+        <v>132.6683319614938</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>153.9547911408019</v>
+        <v>139.43469272825</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>160.811916967232</v>
+        <v>146.3734155794993</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>167.9487894950025</v>
+        <v>153.4871854629432</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>175.3398903554385</v>
+        <v>160.7663812076265</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>182.9548958870068</v>
+        <v>168.1825750922314</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>190.7576304395957</v>
+        <v>175.6929124563813</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>198.7060663745155</v>
+        <v>183.2382862348982</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>206.7523240644979</v>
+        <v>190.7463590197664</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>198.1268445387424</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
@@ -698,37 +716,40 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>55.76408404729032</v>
+        <v>63.54846186139981</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>57.55978582867928</v>
+        <v>63.77128437530303</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>59.83940389255535</v>
+        <v>64.44695292226675</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>62.61670154700634</v>
+        <v>65.5561918560761</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>65.90825124681709</v>
+        <v>67.09631622902928</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>69.73957136066241</v>
+        <v>69.07694721208168</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>74.14098555007563</v>
+        <v>71.5265125265511</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>79.14866946516834</v>
+        <v>74.48786683281418</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>84.80465074463035</v>
+        <v>78.02011719604894</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>91.15680901572985</v>
+        <v>82.19560102427094</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>97.50896728682935</v>
+        <v>87.10460458972355</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>92.01360815517616</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -739,37 +760,40 @@
       </c>
       <c r="B7" s="1" t="inlineStr"/>
       <c r="C7" s="2" t="n">
-        <v>246.398610820466</v>
+        <v>237.948890412864</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>251.0655696361242</v>
+        <v>241.957320113039</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>256.1439824412076</v>
+        <v>246.2805455707236</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>261.6098887019486</v>
+        <v>250.9022948474207</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>267.4395307992526</v>
+        <v>255.8063878317935</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>273.6096599962744</v>
+        <v>260.9769082010073</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>280.0977759535114</v>
+        <v>266.3983431546134</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>286.8823047638251</v>
+        <v>272.0556926800991</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>293.9427225171241</v>
+        <v>277.9345510485031</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>301.2596323715276</v>
+        <v>284.021163782167</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>308.814803262653</v>
+        <v>290.3024635592666</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>296.766088500255</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -780,37 +804,40 @@
       </c>
       <c r="B8" s="1" t="inlineStr"/>
       <c r="C8" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>308.7671838180617</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
@@ -821,37 +848,40 @@
       </c>
       <c r="B9" s="1" t="inlineStr"/>
       <c r="C9" s="2" t="n">
-        <v>253.6145004582451</v>
+        <v>241.9345367625784</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>274.2453960514266</v>
+        <v>262.9216903367849</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>280.3033433604229</v>
+        <v>269.0248287874549</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>284.4648877344138</v>
+        <v>272.9725043652084</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>288.1022885647964</v>
+        <v>276.2673915705103</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>291.5770567082678</v>
+        <v>279.3200253385697</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>295.0270143824656</v>
+        <v>282.288468651454</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>298.4944979976199</v>
+        <v>285.230308898267</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>301.9996248516245</v>
+        <v>288.1708935810913</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>305.5468068450203</v>
+        <v>291.1182883561121</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>309.1302571752388</v>
+        <v>294.0692596716657</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>297.0108038237458</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
@@ -866,37 +896,40 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>179.267032761773</v>
+        <v>200.6986694817401</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>172.8646387345668</v>
+        <v>192.7455566399304</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>166.4622447073606</v>
+        <v>184.7924437981207</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>160.0598506801545</v>
+        <v>176.839330956311</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>153.6574566529483</v>
+        <v>168.8862181145013</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>147.2550626257421</v>
+        <v>160.9331052726916</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>140.8526685985359</v>
+        <v>152.9799924308819</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>134.4502745713297</v>
+        <v>145.0268795890722</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>128.0478805441236</v>
+        <v>137.0737667472625</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>121.6454865169174</v>
+        <v>129.1206539054528</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>115.2430924897112</v>
+        <v>121.1675410636431</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>113.2144282218334</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
@@ -911,37 +944,40 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>176.0658357481699</v>
+        <v>196.7221130608353</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>169.6634417209637</v>
+        <v>188.7690002190255</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>163.2610476937575</v>
+        <v>180.8158873772159</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>156.8586536665514</v>
+        <v>172.8627745354061</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>150.4562596393452</v>
+        <v>164.9096616935965</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>144.053865612139</v>
+        <v>156.9565488517867</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>137.6514715849328</v>
+        <v>149.0034360099771</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>131.2490775577267</v>
+        <v>141.0503231681674</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>124.8466835305205</v>
+        <v>133.0972103263576</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>118.4442895033143</v>
+        <v>125.144097484548</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>112.0418954761081</v>
+        <v>117.1909846427383</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>109.2378718009286</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
@@ -956,37 +992,40 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>172.8646387345668</v>
+        <v>192.7455566399304</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>166.4622447073606</v>
+        <v>184.7924437981207</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>160.0598506801545</v>
+        <v>176.839330956311</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>153.6574566529483</v>
+        <v>168.8862181145013</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>147.2550626257421</v>
+        <v>160.9331052726916</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>140.8526685985359</v>
+        <v>152.9799924308819</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>134.4502745713297</v>
+        <v>145.0268795890722</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>128.0478805441236</v>
+        <v>137.0737667472625</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>121.6454865169174</v>
+        <v>129.1206539054528</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>115.2430924897112</v>
+        <v>121.1675410636431</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>108.840698462505</v>
+        <v>113.2144282218334</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>105.2613153800237</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
@@ -997,37 +1036,40 @@
       </c>
       <c r="B13" s="1" t="inlineStr"/>
       <c r="C13" s="2" t="n">
-        <v>181.6364952163126</v>
+        <v>202.9513651330939</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>176.1329266709</v>
+        <v>195.4866338033303</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>170.8798117331878</v>
+        <v>188.2167864831417</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>165.9260838375918</v>
+        <v>181.1633764304738</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>161.3318042151788</v>
+        <v>174.3599151875715</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>157.1721415038235</v>
+        <v>167.8526220238856</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>153.5374940222827</v>
+        <v>161.7060227621535</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>150.5349513898636</v>
+        <v>156.0053198951433</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>148.2884121496223</v>
+        <v>150.8617975242803</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>146.9371777206925</v>
+        <v>146.416152917466</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>146.1310930060742</v>
+        <v>142.8450870640246</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>139.8086141883508</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
@@ -1038,37 +1080,40 @@
       </c>
       <c r="B14" s="1" t="inlineStr"/>
       <c r="C14" s="2" t="n">
-        <v>1.275938380365357</v>
+        <v>1.262954974957081</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1.258747407548489</v>
+        <v>1.252318150418864</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1.23788338186601</v>
+        <v>1.238496258523747</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1.213028617757703</v>
+        <v>1.221317586676903</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1.183834011534</v>
+        <v>1.200531551284985</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1.14995765612035</v>
+        <v>1.175788913384866</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1.111056923178914</v>
+        <v>1.146660511232904</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.066849783866912</v>
+        <v>1.112607629918509</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1.017161350629269</v>
+        <v>1.073023249144744</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0.961988443198516</v>
+        <v>1.027263573514586</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>0.9015698794986845</v>
+        <v>0.9747397760120182</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>0.9150086848650557</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
@@ -1079,37 +1124,40 @@
       </c>
       <c r="B15" s="1" t="inlineStr"/>
       <c r="C15" s="2" t="n">
-        <v>0.9159066365935092</v>
+        <v>1.0246845986156</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.8769037019579211</v>
+        <v>0.9820273996624183</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.8364299680770255</v>
+        <v>0.9377957368838292</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.7947406744383886</v>
+        <v>0.8920313882454487</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.7521411845390105</v>
+        <v>0.8448758042683662</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.7089617300316885</v>
+        <v>0.7965731963730394</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.6655615219970313</v>
+        <v>0.7474432190408075</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.6222986352099144</v>
+        <v>0.6978817737431801</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.579516801618195</v>
+        <v>0.6483194009328516</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0.5375305929556099</v>
+        <v>0.5991967431984951</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0.4966136483809364</v>
+        <v>0.5509268866829359</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>0.5038815503547388</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
@@ -1120,37 +1168,40 @@
       </c>
       <c r="B16" s="1" t="inlineStr"/>
       <c r="C16" s="2" t="n">
-        <v>1.258747407548489</v>
+        <v>1.252318150418864</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1.23788338186601</v>
+        <v>1.238496258523747</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1.213028617757703</v>
+        <v>1.221317586676903</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1.183834011534</v>
+        <v>1.200531551284985</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1.14995765612035</v>
+        <v>1.175788913384866</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1.111056923178914</v>
+        <v>1.146660511232904</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1.066849783866912</v>
+        <v>1.112607629918509</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.017161350629269</v>
+        <v>1.073023249144744</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.961988443198516</v>
+        <v>1.027263573514586</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0.9015698794986845</v>
+        <v>0.9747397760120182</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0.8402582512480227</v>
+        <v>0.9150086848650557</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>0.8524510191761026</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
@@ -1161,37 +1212,40 @@
       </c>
       <c r="B17" s="1" t="inlineStr"/>
       <c r="C17" s="2" t="n">
-        <v>1.136240984816277</v>
+        <v>1.235264811254632</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1.055800909246645</v>
+        <v>1.160118059868575</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.9786356824889182</v>
+        <v>1.085789415167741</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.9052934245276625</v>
+        <v>1.012758553902248</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.8361344488824398</v>
+        <v>0.9415001804207938</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.7713305995343174</v>
+        <v>0.8724656217314807</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0.7109148377366696</v>
+        <v>0.8060408865250563</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.6547977443607806</v>
+        <v>0.7425506585639171</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.6028036170575802</v>
+        <v>0.6822288120213247</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0.5546988540537956</v>
+        <v>0.6252199432339884</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0.5102150483952109</v>
+        <v>0.5715736686102918</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>0.5212652963269806</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
@@ -1202,37 +1256,40 @@
       </c>
       <c r="B18" s="1" t="inlineStr"/>
       <c r="C18" s="2" t="n">
-        <v>1.421164877142657</v>
+        <v>1.430205587867951</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1.140758670670047</v>
+        <v>1.164957720860316</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1.084014091981034</v>
+        <v>1.110646546792661</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1.051367587727839</v>
+        <v>1.080458115601713</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1.025677085056393</v>
+        <v>1.057208509437621</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1.002589766131655</v>
+        <v>1.036408938457388</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0.9803632058699798</v>
+        <v>1.01625834070817</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.9583043122614466</v>
+        <v>0.9959047859260897</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.9359219644700063</v>
+        <v>0.9747226033841933</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0.9128446125557934</v>
+        <v>0.9521302900272457</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0.8887534602638226</v>
+        <v>0.9275279226406408</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>0.9002426775158631</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
@@ -1243,37 +1300,40 @@
       </c>
       <c r="B19" s="1" t="inlineStr"/>
       <c r="C19" s="2" t="n">
-        <v>0.2849238923263795</v>
+        <v>0.1949407766133187</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.08495776142340183</v>
+        <v>0.004839660991741601</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.105378409492116</v>
+        <v>0.02485713162491954</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.1460741632001763</v>
+        <v>0.06769956169946534</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.1895426361739536</v>
+        <v>0.1157083290168276</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.231259166597338</v>
+        <v>0.1639433167259078</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0.2694483681333102</v>
+        <v>0.2102174541831141</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.303506567900666</v>
+        <v>0.2533541273621726</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.3331183474124261</v>
+        <v>0.2924937913628686</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0.3581457585019978</v>
+        <v>0.3269103467932573</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>0.3785384118686117</v>
+        <v>0.355954254030349</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>0.3789773811888825</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
@@ -1284,37 +1344,40 @@
       </c>
       <c r="B20" s="1" t="inlineStr"/>
       <c r="C20" s="2" t="n">
-        <v>0.3428407709549798</v>
+        <v>0.2276335518032633</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.3609796799080884</v>
+        <v>0.2564688588613289</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.3765986496806775</v>
+        <v>0.283521849793074</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.3890933370956114</v>
+        <v>0.3085001630395365</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.397816471581339</v>
+        <v>0.3309131091164996</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.4020951931472255</v>
+        <v>0.3500873148598649</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.4012882618698811</v>
+        <v>0.3651644108777011</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.3948627154193548</v>
+        <v>0.3751414754015637</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.382471641580321</v>
+        <v>0.3789441725817347</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0.3640392865430746</v>
+        <v>0.3755430328135231</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>0.3436446028670863</v>
+        <v>0.3640817981821198</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>0.3485694688213637</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -1329,37 +1392,40 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>308.7671838180617</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
@@ -1374,37 +1440,40 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>320.1197013603089</v>
+        <v>308.7671838180617</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>308.7671838180617</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
@@ -1415,37 +1484,40 @@
       </c>
       <c r="B23" s="1" t="inlineStr"/>
       <c r="C23" s="2" t="n">
-        <v>0.7109111560827139</v>
+        <v>0.6856998637563962</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.7109111560827139</v>
+        <v>0.6856998637563962</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.7109111560827139</v>
+        <v>0.6856998637563962</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.7109111560827139</v>
+        <v>0.6856998637563962</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.7109111560827139</v>
+        <v>0.6856998637563962</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0.7109111560827139</v>
+        <v>0.6856998637563962</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0.7109111560827139</v>
+        <v>0.6856998637563962</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.7109111560827139</v>
+        <v>0.6856998637563962</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.7109111560827139</v>
+        <v>0.6856998637563962</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0.7109111560827139</v>
+        <v>0.6856998637563962</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0.7109111560827139</v>
+        <v>0.6856998637563962</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>0.6856998637563962</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
@@ -1456,37 +1528,40 @@
       </c>
       <c r="B24" s="1" t="inlineStr"/>
       <c r="C24" s="2" t="n">
-        <v>0.7109111560827139</v>
+        <v>0.6856998637563962</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.7109111560827139</v>
+        <v>0.6856998637563962</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.7109111560827139</v>
+        <v>0.6856998637563962</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.7109111560827139</v>
+        <v>0.6856998637563962</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.7109111560827139</v>
+        <v>0.6856998637563962</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0.7109111560827139</v>
+        <v>0.6856998637563962</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0.7109111560827139</v>
+        <v>0.6856998637563962</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.7109111560827139</v>
+        <v>0.6856998637563962</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.7109111560827139</v>
+        <v>0.6856998637563962</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0.7109111560827139</v>
+        <v>0.6856998637563962</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>0.7109111560827139</v>
+        <v>0.6856998637563962</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>0.6856998637563962</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
@@ -1501,37 +1576,40 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>54.44537991517426</v>
+        <v>63.81194118956999</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>55.76408404729033</v>
+        <v>63.54846186139982</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>57.55978582867928</v>
+        <v>63.77128437530303</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>59.83940389255535</v>
+        <v>64.44695292226675</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>62.61670154700633</v>
+        <v>65.55619185607611</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>65.90825124681707</v>
+        <v>67.09631622902928</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>69.73957136066241</v>
+        <v>69.07694721208166</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>74.14098555007561</v>
+        <v>71.52651252655109</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>79.14866946516834</v>
+        <v>74.48786683281418</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>84.80465074463034</v>
+        <v>78.02011719604894</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>91.15680901572985</v>
+        <v>82.19560102427093</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>87.10460458972355</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
@@ -1546,37 +1624,40 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>135.2095371557408</v>
+        <v>119.5614139338028</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>141.1432602644053</v>
+        <v>126.0550576330157</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>147.3939844704971</v>
+        <v>132.6683319614938</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>153.9547911408019</v>
+        <v>139.4346927282501</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>160.811916967232</v>
+        <v>146.3734155794993</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>167.9487894950025</v>
+        <v>153.4871854629432</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>175.3398903554385</v>
+        <v>160.7663812076266</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>182.9548958870068</v>
+        <v>168.1825750922314</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>190.7576304395957</v>
+        <v>175.6929124563814</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>198.7060663745155</v>
+        <v>183.2382862348982</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>206.752324064498</v>
+        <v>190.7463590197664</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>198.1268445387425</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
@@ -1591,37 +1672,40 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>55.76408404729033</v>
+        <v>63.54846186139982</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>57.55978582867928</v>
+        <v>63.77128437530303</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>59.83940389255535</v>
+        <v>64.44695292226675</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>62.61670154700633</v>
+        <v>65.55619185607611</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>65.90825124681707</v>
+        <v>67.09631622902928</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>69.73957136066241</v>
+        <v>69.07694721208166</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>74.14098555007561</v>
+        <v>71.52651252655109</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>79.14866946516834</v>
+        <v>74.48786683281418</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>84.80465074463034</v>
+        <v>78.02011719604894</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>91.15680901572985</v>
+        <v>82.19560102427093</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>97.50896728682936</v>
+        <v>87.10460458972355</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>92.01360815517617</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
@@ -1636,37 +1720,40 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>179.267032761773</v>
+        <v>200.6986694817401</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>172.8646387345668</v>
+        <v>192.7455566399304</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>166.4622447073606</v>
+        <v>184.7924437981207</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>160.0598506801545</v>
+        <v>176.839330956311</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>153.6574566529483</v>
+        <v>168.8862181145013</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>147.2550626257421</v>
+        <v>160.9331052726916</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>140.8526685985359</v>
+        <v>152.9799924308819</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>134.4502745713297</v>
+        <v>145.0268795890722</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>128.0478805441236</v>
+        <v>137.0737667472625</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>121.6454865169174</v>
+        <v>129.1206539054528</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>115.2430924897112</v>
+        <v>121.1675410636431</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>113.2144282218334</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
@@ -1681,37 +1768,40 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>176.0658357481699</v>
+        <v>196.7221130608353</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>169.6634417209637</v>
+        <v>188.7690002190255</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>163.2610476937575</v>
+        <v>180.8158873772159</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>156.8586536665514</v>
+        <v>172.8627745354061</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>150.4562596393452</v>
+        <v>164.9096616935965</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>144.053865612139</v>
+        <v>156.9565488517867</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>137.6514715849328</v>
+        <v>149.0034360099771</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>131.2490775577267</v>
+        <v>141.0503231681674</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>124.8466835305205</v>
+        <v>133.0972103263576</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>118.4442895033143</v>
+        <v>125.144097484548</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>112.0418954761081</v>
+        <v>117.1909846427383</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>109.2378718009286</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
@@ -1726,37 +1816,40 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>172.8646387345668</v>
+        <v>192.7455566399304</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>166.4622447073606</v>
+        <v>184.7924437981207</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>160.0598506801545</v>
+        <v>176.839330956311</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>153.6574566529483</v>
+        <v>168.8862181145013</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>147.2550626257421</v>
+        <v>160.9331052726916</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>140.8526685985359</v>
+        <v>152.9799924308819</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>134.4502745713297</v>
+        <v>145.0268795890722</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>128.0478805441236</v>
+        <v>137.0737667472625</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>121.6454865169174</v>
+        <v>129.1206539054528</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>115.2430924897112</v>
+        <v>121.1675410636431</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>108.840698462505</v>
+        <v>113.2144282218334</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>105.2613153800237</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
@@ -1767,37 +1860,40 @@
       </c>
       <c r="B31" s="1" t="inlineStr"/>
       <c r="C31" s="2" t="n">
-        <v>181.6364952163126</v>
+        <v>202.9513651330939</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>176.1329266709</v>
+        <v>195.4866338033303</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>170.8798117331878</v>
+        <v>188.2167864831417</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>165.9260838375918</v>
+        <v>181.1633764304738</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>161.3318042151788</v>
+        <v>174.3599151875715</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>157.1721415038235</v>
+        <v>167.8526220238856</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>153.5374940222827</v>
+        <v>161.7060227621535</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>150.5349513898636</v>
+        <v>156.0053198951433</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>148.2884121496223</v>
+        <v>150.8617975242803</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>146.9371777206925</v>
+        <v>146.416152917466</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>146.1310930060742</v>
+        <v>142.8450870640246</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>139.8086141883508</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
@@ -1808,37 +1904,40 @@
       </c>
       <c r="B32" s="1" t="inlineStr"/>
       <c r="C32" s="2" t="n">
-        <v>1.275938380365357</v>
+        <v>1.262954974957081</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1.258747407548489</v>
+        <v>1.252318150418863</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1.23788338186601</v>
+        <v>1.238496258523747</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>1.213028617757703</v>
+        <v>1.221317586676903</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>1.183834011534</v>
+        <v>1.200531551284985</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>1.14995765612035</v>
+        <v>1.175788913384866</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1.111056923178914</v>
+        <v>1.146660511232904</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.066849783866912</v>
+        <v>1.112607629918509</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1.017161350629269</v>
+        <v>1.073023249144744</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0.9619884431985161</v>
+        <v>1.027263573514586</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>0.9015698794986845</v>
+        <v>0.9747397760120182</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>0.9150086848650557</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
@@ -1849,37 +1948,40 @@
       </c>
       <c r="B33" s="1" t="inlineStr"/>
       <c r="C33" s="2" t="n">
-        <v>0.915906636593509</v>
+        <v>1.0246845986156</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.8769037019579211</v>
+        <v>0.9820273996624183</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.8364299680770254</v>
+        <v>0.9377957368838293</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.7947406744383886</v>
+        <v>0.8920313882454486</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.7521411845390105</v>
+        <v>0.8448758042683661</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>0.7089617300316886</v>
+        <v>0.7965731963730394</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0.6655615219970313</v>
+        <v>0.7474432190408075</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.6222986352099145</v>
+        <v>0.6978817737431801</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.579516801618195</v>
+        <v>0.6483194009328513</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0.5375305929556098</v>
+        <v>0.5991967431984951</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>0.4966136483809363</v>
+        <v>0.5509268866829359</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>0.5038815503547388</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
@@ -1890,37 +1992,40 @@
       </c>
       <c r="B34" s="1" t="inlineStr"/>
       <c r="C34" s="2" t="n">
-        <v>1.258747407548489</v>
+        <v>1.252318150418863</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1.23788338186601</v>
+        <v>1.238496258523747</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1.213028617757703</v>
+        <v>1.221317586676903</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>1.183834011534</v>
+        <v>1.200531551284985</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1.14995765612035</v>
+        <v>1.175788913384866</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>1.111056923178914</v>
+        <v>1.146660511232904</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1.066849783866912</v>
+        <v>1.112607629918509</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.017161350629269</v>
+        <v>1.073023249144744</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.9619884431985161</v>
+        <v>1.027263573514586</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0.9015698794986845</v>
+        <v>0.9747397760120182</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>0.8402582512480227</v>
+        <v>0.9150086848650557</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>0.8524510191761026</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
@@ -1931,37 +2036,40 @@
       </c>
       <c r="B35" s="1" t="inlineStr"/>
       <c r="C35" s="2" t="n">
-        <v>0.5935863940212751</v>
+        <v>0.6864156518395516</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.579118614579734</v>
+        <v>0.6661550473040231</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.5650430480710906</v>
+        <v>0.6462267168484536</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.5513410283393623</v>
+        <v>0.6265221149969087</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.538005008724306</v>
+        <v>0.6069590807485146</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>0.5250314740183311</v>
+        <v>0.5874844735552959</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0.5124314659658221</v>
+        <v>0.5680638961183928</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.5002238044188417</v>
+        <v>0.5486920041336587</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.4884375763498524</v>
+        <v>0.5293818341629896</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0.4771133680069763</v>
+        <v>0.5101659265830247</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>0.4663052708332422</v>
+        <v>0.4910884042506482</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>0.4722115293545242</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
@@ -1972,37 +2080,40 @@
       </c>
       <c r="B36" s="1" t="inlineStr"/>
       <c r="C36" s="2" t="n">
-        <v>0.7609019106677866</v>
+        <v>0.8048717318259582</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.7586921389816438</v>
+        <v>0.8017013803452042</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.7572358431314905</v>
+        <v>0.79861353501171</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.7565962921948152</v>
+        <v>0.7957143733613891</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.7568308815772203</v>
+        <v>0.7930847431136775</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>0.7580033732816617</v>
+        <v>0.7907676001258164</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0.7601643213529121</v>
+        <v>0.7887739724279766</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.7633621558446173</v>
+        <v>0.7870517722545544</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.767637513843858</v>
+        <v>0.7854843445483178</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0.7730191944131963</v>
+        <v>0.783863096581575</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.7795178971330147</v>
+        <v>0.7818701232259075</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>0.7790198667361168</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
@@ -2013,37 +2124,40 @@
       </c>
       <c r="B37" s="1" t="inlineStr"/>
       <c r="C37" s="2" t="n">
-        <v>0.1673155166465115</v>
+        <v>0.1184560799864066</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.1795735244019098</v>
+        <v>0.1355463330411811</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.1921927950603999</v>
+        <v>0.1523868181632564</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0.2052552638554529</v>
+        <v>0.1691922583644804</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.2188258728529143</v>
+        <v>0.1861256623651629</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>0.2329718992633306</v>
+        <v>0.2032831265705205</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0.24773285538709</v>
+        <v>0.2207100763095838</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.2631383514257756</v>
+        <v>0.2383597681208957</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.2791999374940057</v>
+        <v>0.2561025103853283</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0.29590582640622</v>
+        <v>0.2736971699985503</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>0.3132126262997725</v>
+        <v>0.2907817189752593</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>0.3068083373815926</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
@@ -2054,37 +2168,40 @@
       </c>
       <c r="B38" s="1" t="inlineStr"/>
       <c r="C38" s="2" t="n">
-        <v>0.34284077095498</v>
+        <v>0.2276335518032631</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.3609796799080884</v>
+        <v>0.2564688588613289</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.3765986496806776</v>
+        <v>0.2835218497930739</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0.3890933370956114</v>
+        <v>0.3085001630395364</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.397816471581339</v>
+        <v>0.3309131091164997</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>0.4020951931472254</v>
+        <v>0.3500873148598649</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0.4012882618698811</v>
+        <v>0.3651644108777011</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.3948627154193547</v>
+        <v>0.3751414754015637</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.3824716415803211</v>
+        <v>0.378944172581735</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0.3640392865430747</v>
+        <v>0.3755430328135231</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>0.3436446028670864</v>
+        <v>0.3640817981821198</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>0.3485694688213637</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
@@ -2095,37 +2212,40 @@
       </c>
       <c r="B39" s="1" t="inlineStr"/>
       <c r="C39" s="2" t="n">
-        <v>320.4988519644701</v>
+        <v>316.6749545242313</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>315.857682714509</v>
+        <v>311.9023424126456</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>310.8816304592307</v>
+        <v>306.8733257040238</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>305.5568507653782</v>
+        <v>301.6032562789239</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>299.8639839959151</v>
+        <v>296.0981953341694</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>293.7814065554789</v>
+        <v>290.3519805579891</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>287.2798004558776</v>
+        <v>284.3488836067119</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>280.3255339136225</v>
+        <v>278.0574255764263</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>272.8796399961913</v>
+        <v>271.4332623267771</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>264.8977112702125</v>
+        <v>264.4170040289303</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>256.3298196413898</v>
+        <v>256.936286143264</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>248.9011968387375</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
@@ -2136,37 +2256,40 @@
       </c>
       <c r="B40" s="1" t="inlineStr"/>
       <c r="C40" s="2" t="n">
-        <v>197.6358336086016</v>
+        <v>212.5515131481671</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>198.6276410239583</v>
+        <v>210.2257778582746</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>200.6205779571288</v>
+        <v>208.8825020558515</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>203.4815096373063</v>
+        <v>208.4642333794313</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>207.0694881903153</v>
+        <v>208.9033255749229</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>211.2425788728567</v>
+        <v>210.118339364321</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>215.8571353751045</v>
+        <v>212.0152885729822</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>220.7726310890596</v>
+        <v>214.483089016131</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>225.852257391394</v>
+        <v>217.3964080444979</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>230.9633801127104</v>
+        <v>220.6151229778069</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>235.9774182499772</v>
+        <v>223.9876891329342</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>227.3483494622677</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
@@ -2177,37 +2300,40 @@
       </c>
       <c r="B41" s="1" t="inlineStr"/>
       <c r="C41" s="2" t="n">
-        <v>255.3251796119253</v>
+        <v>272.9439743328568</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>246.6135639496707</v>
+        <v>262.7117365074325</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>237.6727644665303</v>
+        <v>252.3988723295163</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>228.5069246616827</v>
+        <v>241.9814690400069</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>219.1256631088498</v>
+        <v>231.4453120774244</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>209.5411716482445</v>
+        <v>220.7877626061483</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>199.77267406756</v>
+        <v>210.0149078425442</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>189.8433675962449</v>
+        <v>199.1462424361535</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>179.7810884978327</v>
+        <v>188.2116603590246</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>169.6181608095324</v>
+        <v>177.2527835145796</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>159.3911809881898</v>
+        <v>166.3209005735733</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>155.4805367608402</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
@@ -2218,37 +2344,40 @@
       </c>
       <c r="B42" s="1" t="inlineStr"/>
       <c r="C42" s="2" t="n">
-        <v>178.0554115581426</v>
+        <v>198.6824351847945</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>186.6587074613199</v>
+        <v>205.4580163879</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>184.7173219908408</v>
+        <v>201.8066005548523</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>180.6913168325326</v>
+        <v>195.9509638973385</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>175.9587602770414</v>
+        <v>189.336448544344</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>170.9092824450496</v>
+        <v>182.3844413155287</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>165.7054688427446</v>
+        <v>175.268507737364</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>160.4084691007044</v>
+        <v>168.0668547136884</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>155.0608834982843</v>
+        <v>160.8335726775535</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>149.6933037746265</v>
+        <v>153.6164801316091</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>144.3305883382398</v>
+        <v>146.4631727744364</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>139.4268995749411</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
@@ -2259,37 +2388,40 @@
       </c>
       <c r="B43" s="1" t="inlineStr"/>
       <c r="C43" s="2" t="n">
-        <v>329.3211088410575</v>
+        <v>326.2718766347037</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>353.2908490535955</v>
+        <v>348.9155469082214</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>375.6960233125122</v>
+        <v>370.1229094630255</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>396.7916219617101</v>
+        <v>390.0917984928992</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>416.7923881295006</v>
+        <v>409.0577039563908</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>435.8454350925375</v>
+        <v>427.1299245817816</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>454.0611776702718</v>
+        <v>444.4312659450177</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>471.5475653132449</v>
+        <v>461.0363542839652</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>488.3600584646119</v>
+        <v>477.025831392006</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>504.5769424200934</v>
+        <v>492.4400509770026</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>520.2518186552477</v>
+        <v>507.3402053890704</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>521.7685286185019</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
@@ -2300,37 +2432,40 @@
       </c>
       <c r="B44" s="1" t="inlineStr"/>
       <c r="C44" s="2" t="n">
-        <v>0.973210776231033</v>
+        <v>0.9705861191302823</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.8940443364458392</v>
+        <v>0.8939193027551975</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.8274818235183515</v>
+        <v>0.8291119459458369</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0.7700688065305575</v>
+        <v>0.7731596958565997</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.7194564788998619</v>
+        <v>0.7238543424810698</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>0.6740495205441445</v>
+        <v>0.6797743820976329</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0.6326896343128749</v>
+        <v>0.6398039593413525</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.5944798670043067</v>
+        <v>0.6031138824361841</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.5587673178148844</v>
+        <v>0.5690116644935338</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0.5249897270368487</v>
+        <v>0.5369526778017468</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.4927033610453372</v>
+        <v>0.5064378565192246</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>0.4770337480831945</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
@@ -2341,37 +2476,40 @@
       </c>
       <c r="B45" s="1" t="inlineStr"/>
       <c r="C45" s="2" t="n">
-        <v>1.031376080527461</v>
+        <v>1.01907065000851</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.9534869473697689</v>
+        <v>0.9463040700801164</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.8868622682934559</v>
+        <v>0.8834101531170189</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.8285130151687583</v>
+        <v>0.827818287398653</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.7765931779904779</v>
+        <v>0.7782928631444037</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>0.7296450358115966</v>
+        <v>0.7334327609516046</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0.6865219361339741</v>
+        <v>0.692430171875216</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.6465290250465358</v>
+        <v>0.6544413238133387</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.6087932634741232</v>
+        <v>0.6189369497118317</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0.5729270579994631</v>
+        <v>0.5852128385553067</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>0.5384906765101605</v>
+        <v>0.5529150076467954</v>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>0.5216291318476798</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
@@ -2382,37 +2520,40 @@
       </c>
       <c r="B46" s="1" t="inlineStr"/>
       <c r="C46" s="2" t="n">
-        <v>0.8076836548463436</v>
+        <v>0.8163283366743694</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.7532860191435194</v>
+        <v>0.7616870018750188</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0.7082721248205641</v>
+        <v>0.7157236225124972</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>0.6702850845056435</v>
+        <v>0.6763174394727927</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.6378658295484246</v>
+        <v>0.6424379077920499</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>0.6098593134098055</v>
+        <v>0.6129201678110948</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0.5853479419489973</v>
+        <v>0.5870850151170974</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.5637824028337244</v>
+        <v>0.5642158372532415</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.5444472539230326</v>
+        <v>0.5438575546609512</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0.5270380406504113</v>
+        <v>0.5253966577574078</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>0.5112024440533265</v>
+        <v>0.5085234823660012</v>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>0.4928784347822723</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
@@ -2423,37 +2564,40 @@
       </c>
       <c r="B47" s="1" t="inlineStr"/>
       <c r="C47" s="2" t="n">
-        <v>0.6359987569054194</v>
+        <v>0.6839979151165261</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.5996018886593721</v>
+        <v>0.6378198627307841</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.5723169315941179</v>
+        <v>0.6013195272064865</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.5517371927954087</v>
+        <v>0.5721771932741999</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.5362723117184</v>
+        <v>0.5491015141061614</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>0.5246489246333993</v>
+        <v>0.5307615724555451</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0.5158408571395892</v>
+        <v>0.5162875297580325</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5091791387756701</v>
+        <v>0.5048115381932501</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.5038753819897428</v>
+        <v>0.4957191632298202</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0.4995330810488081</v>
+        <v>0.4882696663938627</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0.4957349081442295</v>
+        <v>0.4820111503467031</v>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>0.4764602326675061</v>
       </c>
     </row>
   </sheetData>

--- a/results/Расчет_ступеней_по_высоте_лопаток.xlsx
+++ b/results/Расчет_ступеней_по_высоте_лопаток.xlsx
@@ -524,40 +524,40 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>133.7990100654321</v>
+        <v>131.8158956232372</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>147.4771701302632</v>
+        <v>145.3966857268395</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>161.1553301950943</v>
+        <v>158.9774758304418</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>174.8334902599253</v>
+        <v>172.558265934044</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>188.5116503247563</v>
+        <v>186.1390560376462</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>202.1898103895874</v>
+        <v>199.7198461412485</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>215.8679704544184</v>
+        <v>213.3006362448508</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>229.5461305192495</v>
+        <v>226.881426348453</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>243.2242905840805</v>
+        <v>240.4622164520553</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>256.9024506489116</v>
+        <v>254.0430065556575</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>270.5806107137426</v>
+        <v>267.6237966592598</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>284.2587707785736</v>
+        <v>281.204586762862</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
@@ -572,40 +572,40 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>147.4023960256757</v>
+        <v>143.3083063637941</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>207.1677018653433</v>
+        <v>204.5621867774973</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>222.2870738601373</v>
+        <v>219.804974854066</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>231.7127585522443</v>
+        <v>229.2362683771474</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>239.3954249508763</v>
+        <v>236.8876270249932</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>246.3781226232185</v>
+        <v>243.8215361937053</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>253.0541152880725</v>
+        <v>250.4377566346481</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>259.5678801883332</v>
+        <v>256.8826300063526</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>265.9844995703933</v>
+        <v>263.2211853068605</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>272.3280041197528</v>
+        <v>269.4761381922839</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>278.5969941775153</v>
+        <v>275.64334741065</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>284.7694881357876</v>
+        <v>281.6964949253804</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -620,40 +620,40 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>63.81194118956999</v>
+        <v>63.1329097750037</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>63.54846186139981</v>
+        <v>62.77183610591472</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>63.77128437530303</v>
+        <v>62.90261564382815</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>64.44695292226675</v>
+        <v>63.4876566949365</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>65.5561918560761</v>
+        <v>64.50976044591265</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>67.09631622902928</v>
+        <v>65.96510841054764</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>69.07694721208168</v>
+        <v>67.86700835570147</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>71.5265125265511</v>
+        <v>70.24870063537821</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>74.48786683281418</v>
+        <v>73.15725958263664</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>78.02011719604894</v>
+        <v>76.65702786453478</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>82.19560102427094</v>
+        <v>80.83147187427542</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>87.10460458972355</v>
+        <v>85.77863645278707</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
@@ -668,40 +668,40 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>119.5614139338028</v>
+        <v>118.4818050203146</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>126.0550576330157</v>
+        <v>124.9834481607296</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>132.6683319614938</v>
+        <v>131.5948975476958</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>139.43469272825</v>
+        <v>138.3537448750209</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>146.3734155794993</v>
+        <v>145.2771889560321</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>153.4871854629432</v>
+        <v>152.3690482769383</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>160.7663812076265</v>
+        <v>159.6160150708794</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>168.1825750922314</v>
+        <v>166.9848489838514</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>175.6929124563813</v>
+        <v>174.4284756827955</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>183.2382862348982</v>
+        <v>181.8825525006537</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>190.7463590197664</v>
+        <v>189.2636130442233</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>198.1268445387424</v>
+        <v>196.4736124725757</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
@@ -716,40 +716,40 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>63.54846186139981</v>
+        <v>62.77183610591472</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>63.77128437530303</v>
+        <v>62.90261564382815</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>64.44695292226675</v>
+        <v>63.4876566949365</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>65.5561918560761</v>
+        <v>64.50976044591265</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>67.09631622902928</v>
+        <v>65.96510841054764</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>69.07694721208168</v>
+        <v>67.86700835570147</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>71.5265125265511</v>
+        <v>70.24870063537821</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>74.48786683281418</v>
+        <v>73.15725958263664</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>78.02011719604894</v>
+        <v>76.65702786453478</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>82.19560102427094</v>
+        <v>80.83147187427542</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>87.10460458972355</v>
+        <v>85.77863645278707</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>92.01360815517616</v>
+        <v>90.72580103129872</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -760,40 +760,40 @@
       </c>
       <c r="B7" s="1" t="inlineStr"/>
       <c r="C7" s="2" t="n">
-        <v>237.948890412864</v>
+        <v>235.9528248528826</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>241.957320113039</v>
+        <v>239.9085627833064</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>246.2805455707236</v>
+        <v>244.1780893063224</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>250.9022948474207</v>
+        <v>248.7452471056666</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>255.8063878317935</v>
+        <v>253.5939559174666</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>260.9769082010073</v>
+        <v>258.7083857510594</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>266.3983431546134</v>
+        <v>264.073098019859</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>272.0556926800991</v>
+        <v>269.6731562420169</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>277.9345510485031</v>
+        <v>275.4942089356771</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>284.021163782167</v>
+        <v>281.5225479006893</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>290.3024635592666</v>
+        <v>287.7451453208818</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>296.766088500255</v>
+        <v>294.1496731169576</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -804,40 +804,40 @@
       </c>
       <c r="B8" s="1" t="inlineStr"/>
       <c r="C8" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
@@ -848,40 +848,40 @@
       </c>
       <c r="B9" s="1" t="inlineStr"/>
       <c r="C9" s="2" t="n">
-        <v>241.9345367625784</v>
+        <v>239.2794511089628</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>262.9216903367849</v>
+        <v>260.5932933062032</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>269.0248287874549</v>
+        <v>266.7267025850155</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>272.9725043652084</v>
+        <v>270.6670533262532</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>276.2673915705103</v>
+        <v>273.9414067010373</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>279.3200253385697</v>
+        <v>276.9665884949052</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>282.288468651454</v>
+        <v>279.9027605449339</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>285.230308898267</v>
+        <v>282.8079970334419</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>288.1708935810913</v>
+        <v>285.7073967956575</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>291.1182883561121</v>
+        <v>288.6082377793303</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>294.0692596716657</v>
+        <v>291.5058281963692</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>297.0108038237458</v>
+        <v>294.3849147174485</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
@@ -896,40 +896,40 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>200.6986694817401</v>
+        <v>199.2565864072191</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>192.7455566399304</v>
+        <v>191.1748507347584</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>184.7924437981207</v>
+        <v>183.0931150622978</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>176.839330956311</v>
+        <v>175.0113793898372</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>168.8862181145013</v>
+        <v>166.9296437173765</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>160.9331052726916</v>
+        <v>158.8479080449159</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>152.9799924308819</v>
+        <v>150.7661723724553</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>145.0268795890722</v>
+        <v>142.6844366999946</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>137.0737667472625</v>
+        <v>134.602701027534</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>129.1206539054528</v>
+        <v>126.5209653550734</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>121.1675410636431</v>
+        <v>118.4392296826127</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>113.2144282218334</v>
+        <v>110.3574940101521</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
@@ -944,40 +944,40 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>196.7221130608353</v>
+        <v>195.2157185709887</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>188.7690002190255</v>
+        <v>187.1339828985281</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>180.8158873772159</v>
+        <v>179.0522472260675</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>172.8627745354061</v>
+        <v>170.9705115536069</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>164.9096616935965</v>
+        <v>162.8887758811462</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>156.9565488517867</v>
+        <v>154.8070402086856</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>149.0034360099771</v>
+        <v>146.7253045362249</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>141.0503231681674</v>
+        <v>138.6435688637643</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>133.0972103263576</v>
+        <v>130.5618331913037</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>125.144097484548</v>
+        <v>122.480097518843</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>117.1909846427383</v>
+        <v>114.3983618463824</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>109.2378718009286</v>
+        <v>106.3166261739218</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
@@ -992,40 +992,40 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>192.7455566399304</v>
+        <v>191.1748507347584</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>184.7924437981207</v>
+        <v>183.0931150622978</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>176.839330956311</v>
+        <v>175.0113793898372</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>168.8862181145013</v>
+        <v>166.9296437173765</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>160.9331052726916</v>
+        <v>158.8479080449159</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>152.9799924308819</v>
+        <v>150.7661723724553</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>145.0268795890722</v>
+        <v>142.6844366999946</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>137.0737667472625</v>
+        <v>134.602701027534</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>129.1206539054528</v>
+        <v>126.5209653550734</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>121.1675410636431</v>
+        <v>118.4392296826127</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>113.2144282218334</v>
+        <v>110.3574940101521</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>105.2613153800237</v>
+        <v>102.2757583376915</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
@@ -1036,40 +1036,40 @@
       </c>
       <c r="B13" s="1" t="inlineStr"/>
       <c r="C13" s="2" t="n">
-        <v>202.9513651330939</v>
+        <v>201.2166170115306</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>195.4866338033303</v>
+        <v>193.5970760059433</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>188.2167864831417</v>
+        <v>186.1710650679843</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>181.1633764304738</v>
+        <v>178.9609318940849</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>174.3599151875715</v>
+        <v>172.0001552844106</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>167.8526220238856</v>
+        <v>165.3371390674029</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>161.7060227621535</v>
+        <v>159.040021432826</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>156.0053198951433</v>
+        <v>153.1987981465552</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>150.8617975242803</v>
+        <v>147.9319255448388</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>146.416152917466</v>
+        <v>143.3930890007342</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>142.8450870640246</v>
+        <v>139.773928026296</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>139.8086141883508</v>
+        <v>136.7168669781482</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
@@ -1080,40 +1080,40 @@
       </c>
       <c r="B14" s="1" t="inlineStr"/>
       <c r="C14" s="2" t="n">
-        <v>1.262954974957081</v>
+        <v>1.263960413517295</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1.252318150418864</v>
+        <v>1.253539469396991</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1.238496258523747</v>
+        <v>1.239874358014764</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1.221317586676903</v>
+        <v>1.22279688589888</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1.200531551284985</v>
+        <v>1.202026324602637</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1.175788913384866</v>
+        <v>1.177194043197223</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1.146660511232904</v>
+        <v>1.147819786142874</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.112607629918509</v>
+        <v>1.113298604686115</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1.073023249144744</v>
+        <v>1.072953245860255</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1.027263573514586</v>
+        <v>1.026061588748283</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>0.9747397760120182</v>
+        <v>0.9719311589381018</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.9150086848650557</v>
+        <v>0.9100635927466534</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
@@ -1124,40 +1124,40 @@
       </c>
       <c r="B15" s="1" t="inlineStr"/>
       <c r="C15" s="2" t="n">
-        <v>1.0246845986156</v>
+        <v>1.025298576923191</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.9820273996624183</v>
+        <v>0.9819527018938013</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.9377957368838292</v>
+        <v>0.9369953752985757</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.8920313882454487</v>
+        <v>0.8904551733163805</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.8448758042683662</v>
+        <v>0.8424857485472056</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.7965731963730394</v>
+        <v>0.7933347861790676</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.7474432190408075</v>
+        <v>0.7433434051954089</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.6978817737431801</v>
+        <v>0.6929314331016215</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.6483194009328516</v>
+        <v>0.6425482039479457</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0.5991967431984951</v>
+        <v>0.5926511294523578</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0.5509268866829359</v>
+        <v>0.5436772842140083</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.5038815503547388</v>
+        <v>0.4960032468828308</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
@@ -1168,40 +1168,40 @@
       </c>
       <c r="B16" s="1" t="inlineStr"/>
       <c r="C16" s="2" t="n">
-        <v>1.252318150418864</v>
+        <v>1.253539469396991</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1.238496258523747</v>
+        <v>1.239874358014764</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1.221317586676903</v>
+        <v>1.22279688589888</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1.200531551284985</v>
+        <v>1.202026324602637</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1.175788913384866</v>
+        <v>1.177194043197223</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1.146660511232904</v>
+        <v>1.147819786142874</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1.112607629918509</v>
+        <v>1.113298604686115</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.073023249144744</v>
+        <v>1.072953245860255</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1.027263573514586</v>
+        <v>1.026061588748283</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0.9747397760120182</v>
+        <v>0.9719311589381018</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0.9150086848650557</v>
+        <v>0.9100635927466534</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.8524510191761026</v>
+        <v>0.8451707320323851</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
@@ -1212,40 +1212,40 @@
       </c>
       <c r="B17" s="1" t="inlineStr"/>
       <c r="C17" s="2" t="n">
-        <v>1.235264811254632</v>
+        <v>1.238854298178526</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1.160118059868575</v>
+        <v>1.162847113736222</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1.085789415167741</v>
+        <v>1.087559254200616</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1.012758553902248</v>
+        <v>1.013477964061208</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.9415001804207938</v>
+        <v>0.941115429938413</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.8724656217314807</v>
+        <v>0.8709473701553111</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0.8060408865250563</v>
+        <v>0.8033994195460497</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.7425506585639171</v>
+        <v>0.7388314868921215</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.6822288120213247</v>
+        <v>0.6775001027724478</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0.6252199432339884</v>
+        <v>0.6195648937626838</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0.5715736686102918</v>
+        <v>0.5650943056573683</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.5212652963269806</v>
+        <v>0.5140608900158519</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
@@ -1256,40 +1256,40 @@
       </c>
       <c r="B18" s="1" t="inlineStr"/>
       <c r="C18" s="2" t="n">
-        <v>1.430205587867951</v>
+        <v>1.444300660871426</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1.164957720860316</v>
+        <v>1.168713890096634</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1.110646546792661</v>
+        <v>1.113046042834421</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1.080458115601713</v>
+        <v>1.082214080284579</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1.057208509437621</v>
+        <v>1.058474483255031</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1.036408938457388</v>
+        <v>1.037204964518872</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1.01625834070817</v>
+        <v>1.016529278647963</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.9959047859260897</v>
+        <v>0.9955401536080093</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.9747226033841933</v>
+        <v>0.9735638239077175</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0.9521302900272457</v>
+        <v>0.9499642765458586</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0.9275279226406408</v>
+        <v>0.9240529437980581</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.9002426775158631</v>
+        <v>0.8950835428209692</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
@@ -1300,40 +1300,40 @@
       </c>
       <c r="B19" s="1" t="inlineStr"/>
       <c r="C19" s="2" t="n">
-        <v>0.1949407766133187</v>
+        <v>0.2054463626929006</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.004839660991741601</v>
+        <v>0.005866776360412329</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.02485713162491954</v>
+        <v>0.02548678863380505</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.06769956169946534</v>
+        <v>0.06873611622337128</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.1157083290168276</v>
+        <v>0.117359053316618</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.1639433167259078</v>
+        <v>0.1662575943635612</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0.2102174541831141</v>
+        <v>0.2131298591019133</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.2533541273621726</v>
+        <v>0.2567086667158878</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.2924937913628686</v>
+        <v>0.2960637211352697</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0.3269103467932573</v>
+        <v>0.3303993827831748</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>0.355954254030349</v>
+        <v>0.3589586381406898</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.3789773811888825</v>
+        <v>0.3810226528051174</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
@@ -1344,40 +1344,40 @@
       </c>
       <c r="B20" s="1" t="inlineStr"/>
       <c r="C20" s="2" t="n">
-        <v>0.2276335518032633</v>
+        <v>0.2282408924738</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.2564688588613289</v>
+        <v>0.2579216561209626</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.283521849793074</v>
+        <v>0.2858015106003043</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.3085001630395365</v>
+        <v>0.3115711512862563</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.3309131091164996</v>
+        <v>0.3347082946500178</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.3500873148598649</v>
+        <v>0.3544849999638067</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.3651644108777011</v>
+        <v>0.3699551994907062</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.3751414754015637</v>
+        <v>0.3800218127586336</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.3789441725817347</v>
+        <v>0.383513384800337</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0.3755430328135231</v>
+        <v>0.379280029485744</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>0.3640817981821198</v>
+        <v>0.3663863085326451</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.3485694688213637</v>
+        <v>0.3491674851495544</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -1392,40 +1392,40 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
@@ -1440,40 +1440,40 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>308.7671838180617</v>
+        <v>306.5485944726447</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
@@ -1484,40 +1484,40 @@
       </c>
       <c r="B23" s="1" t="inlineStr"/>
       <c r="C23" s="2" t="n">
-        <v>0.6856998637563962</v>
+        <v>0.6807728945329433</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.6856998637563962</v>
+        <v>0.6807728945329433</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.6856998637563962</v>
+        <v>0.6807728945329433</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.6856998637563962</v>
+        <v>0.6807728945329433</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.6856998637563962</v>
+        <v>0.6807728945329433</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0.6856998637563962</v>
+        <v>0.6807728945329433</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0.6856998637563962</v>
+        <v>0.6807728945329433</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.6856998637563962</v>
+        <v>0.6807728945329433</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.6856998637563962</v>
+        <v>0.6807728945329433</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0.6856998637563962</v>
+        <v>0.6807728945329433</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0.6856998637563962</v>
+        <v>0.6807728945329433</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.6856998637563962</v>
+        <v>0.6807728945329433</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
@@ -1528,40 +1528,40 @@
       </c>
       <c r="B24" s="1" t="inlineStr"/>
       <c r="C24" s="2" t="n">
-        <v>0.6856998637563962</v>
+        <v>0.6807728945329433</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.6856998637563962</v>
+        <v>0.6807728945329433</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.6856998637563962</v>
+        <v>0.6807728945329433</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.6856998637563962</v>
+        <v>0.6807728945329433</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.6856998637563962</v>
+        <v>0.6807728945329433</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0.6856998637563962</v>
+        <v>0.6807728945329433</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0.6856998637563962</v>
+        <v>0.6807728945329433</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.6856998637563962</v>
+        <v>0.6807728945329433</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.6856998637563962</v>
+        <v>0.6807728945329433</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0.6856998637563962</v>
+        <v>0.6807728945329433</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>0.6856998637563962</v>
+        <v>0.6807728945329433</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.6856998637563962</v>
+        <v>0.6807728945329433</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
@@ -1576,40 +1576,40 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>63.81194118956999</v>
+        <v>63.1329097750037</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>63.54846186139982</v>
+        <v>62.77183610591472</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>63.77128437530303</v>
+        <v>62.90261564382815</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>64.44695292226675</v>
+        <v>63.4876566949365</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>65.55619185607611</v>
+        <v>64.50976044591263</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>67.09631622902928</v>
+        <v>65.96510841054763</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>69.07694721208166</v>
+        <v>67.86700835570147</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>71.52651252655109</v>
+        <v>70.24870063537821</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>74.48786683281418</v>
+        <v>73.15725958263666</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>78.02011719604894</v>
+        <v>76.65702786453478</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>82.19560102427093</v>
+        <v>80.83147187427544</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>87.10460458972355</v>
+        <v>85.77863645278707</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
@@ -1624,40 +1624,40 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>119.5614139338028</v>
+        <v>118.4818050203147</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>126.0550576330157</v>
+        <v>124.9834481607296</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>132.6683319614938</v>
+        <v>131.5948975476958</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>139.4346927282501</v>
+        <v>138.3537448750209</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>146.3734155794993</v>
+        <v>145.2771889560321</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>153.4871854629432</v>
+        <v>152.3690482769383</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>160.7663812076266</v>
+        <v>159.6160150708794</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>168.1825750922314</v>
+        <v>166.9848489838514</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>175.6929124563814</v>
+        <v>174.4284756827955</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>183.2382862348982</v>
+        <v>181.8825525006537</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>190.7463590197664</v>
+        <v>189.2636130442233</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>198.1268445387425</v>
+        <v>196.4736124725757</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
@@ -1672,40 +1672,40 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>63.54846186139982</v>
+        <v>62.77183610591472</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>63.77128437530303</v>
+        <v>62.90261564382815</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>64.44695292226675</v>
+        <v>63.4876566949365</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>65.55619185607611</v>
+        <v>64.50976044591263</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>67.09631622902928</v>
+        <v>65.96510841054763</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>69.07694721208166</v>
+        <v>67.86700835570147</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>71.52651252655109</v>
+        <v>70.24870063537821</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>74.48786683281418</v>
+        <v>73.15725958263666</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>78.02011719604894</v>
+        <v>76.65702786453478</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>82.19560102427093</v>
+        <v>80.83147187427544</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>87.10460458972355</v>
+        <v>85.77863645278707</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>92.01360815517617</v>
+        <v>90.7258010312987</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
@@ -1720,40 +1720,40 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>200.6986694817401</v>
+        <v>199.2565864072191</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>192.7455566399304</v>
+        <v>191.1748507347584</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>184.7924437981207</v>
+        <v>183.0931150622978</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>176.839330956311</v>
+        <v>175.0113793898372</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>168.8862181145013</v>
+        <v>166.9296437173765</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>160.9331052726916</v>
+        <v>158.8479080449159</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>152.9799924308819</v>
+        <v>150.7661723724553</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>145.0268795890722</v>
+        <v>142.6844366999946</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>137.0737667472625</v>
+        <v>134.602701027534</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>129.1206539054528</v>
+        <v>126.5209653550734</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>121.1675410636431</v>
+        <v>118.4392296826127</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>113.2144282218334</v>
+        <v>110.3574940101521</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
@@ -1768,40 +1768,40 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>196.7221130608353</v>
+        <v>195.2157185709887</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>188.7690002190255</v>
+        <v>187.1339828985281</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>180.8158873772159</v>
+        <v>179.0522472260675</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>172.8627745354061</v>
+        <v>170.9705115536069</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>164.9096616935965</v>
+        <v>162.8887758811462</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>156.9565488517867</v>
+        <v>154.8070402086856</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>149.0034360099771</v>
+        <v>146.7253045362249</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>141.0503231681674</v>
+        <v>138.6435688637643</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>133.0972103263576</v>
+        <v>130.5618331913037</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>125.144097484548</v>
+        <v>122.480097518843</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>117.1909846427383</v>
+        <v>114.3983618463824</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>109.2378718009286</v>
+        <v>106.3166261739218</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
@@ -1816,40 +1816,40 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>192.7455566399304</v>
+        <v>191.1748507347584</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>184.7924437981207</v>
+        <v>183.0931150622978</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>176.839330956311</v>
+        <v>175.0113793898372</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>168.8862181145013</v>
+        <v>166.9296437173765</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>160.9331052726916</v>
+        <v>158.8479080449159</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>152.9799924308819</v>
+        <v>150.7661723724553</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>145.0268795890722</v>
+        <v>142.6844366999946</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>137.0737667472625</v>
+        <v>134.602701027534</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>129.1206539054528</v>
+        <v>126.5209653550734</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>121.1675410636431</v>
+        <v>118.4392296826127</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>113.2144282218334</v>
+        <v>110.3574940101521</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>105.2613153800237</v>
+        <v>102.2757583376915</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
@@ -1860,40 +1860,40 @@
       </c>
       <c r="B31" s="1" t="inlineStr"/>
       <c r="C31" s="2" t="n">
-        <v>202.9513651330939</v>
+        <v>201.2166170115306</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>195.4866338033303</v>
+        <v>193.5970760059433</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>188.2167864831417</v>
+        <v>186.1710650679843</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>181.1633764304738</v>
+        <v>178.9609318940849</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>174.3599151875715</v>
+        <v>172.0001552844106</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>167.8526220238856</v>
+        <v>165.3371390674029</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>161.7060227621535</v>
+        <v>159.040021432826</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>156.0053198951433</v>
+        <v>153.1987981465552</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>150.8617975242803</v>
+        <v>147.9319255448388</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>146.416152917466</v>
+        <v>143.3930890007342</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>142.8450870640246</v>
+        <v>139.773928026296</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>139.8086141883508</v>
+        <v>136.7168669781482</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
@@ -1904,40 +1904,40 @@
       </c>
       <c r="B32" s="1" t="inlineStr"/>
       <c r="C32" s="2" t="n">
-        <v>1.262954974957081</v>
+        <v>1.263960413517295</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1.252318150418863</v>
+        <v>1.253539469396991</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1.238496258523747</v>
+        <v>1.239874358014764</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>1.221317586676903</v>
+        <v>1.22279688589888</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>1.200531551284985</v>
+        <v>1.202026324602637</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>1.175788913384866</v>
+        <v>1.177194043197224</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1.146660511232904</v>
+        <v>1.147819786142874</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.112607629918509</v>
+        <v>1.113298604686115</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1.073023249144744</v>
+        <v>1.072953245860255</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1.027263573514586</v>
+        <v>1.026061588748283</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>0.9747397760120182</v>
+        <v>0.9719311589381017</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.9150086848650557</v>
+        <v>0.9100635927466534</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
@@ -1948,40 +1948,40 @@
       </c>
       <c r="B33" s="1" t="inlineStr"/>
       <c r="C33" s="2" t="n">
-        <v>1.0246845986156</v>
+        <v>1.025298576923191</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.9820273996624183</v>
+        <v>0.9819527018938013</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.9377957368838293</v>
+        <v>0.9369953752985757</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.8920313882454486</v>
+        <v>0.8904551733163805</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.8448758042683661</v>
+        <v>0.8424857485472055</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>0.7965731963730394</v>
+        <v>0.7933347861790676</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0.7474432190408075</v>
+        <v>0.7433434051954089</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.6978817737431801</v>
+        <v>0.6929314331016215</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.6483194009328513</v>
+        <v>0.6425482039479457</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0.5991967431984951</v>
+        <v>0.5926511294523578</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>0.5509268866829359</v>
+        <v>0.5436772842140083</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.5038815503547388</v>
+        <v>0.4960032468828308</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
@@ -1992,40 +1992,40 @@
       </c>
       <c r="B34" s="1" t="inlineStr"/>
       <c r="C34" s="2" t="n">
-        <v>1.252318150418863</v>
+        <v>1.253539469396991</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1.238496258523747</v>
+        <v>1.239874358014764</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1.221317586676903</v>
+        <v>1.22279688589888</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>1.200531551284985</v>
+        <v>1.202026324602637</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1.175788913384866</v>
+        <v>1.177194043197224</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>1.146660511232904</v>
+        <v>1.147819786142874</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1.112607629918509</v>
+        <v>1.113298604686115</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.073023249144744</v>
+        <v>1.072953245860255</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>1.027263573514586</v>
+        <v>1.026061588748283</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0.9747397760120182</v>
+        <v>0.9719311589381017</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>0.9150086848650557</v>
+        <v>0.9100635927466534</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.8524510191761026</v>
+        <v>0.8451707320323852</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
@@ -2036,40 +2036,40 @@
       </c>
       <c r="B35" s="1" t="inlineStr"/>
       <c r="C35" s="2" t="n">
-        <v>0.6864156518395516</v>
+        <v>0.6859713621172263</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.6661550473040231</v>
+        <v>0.6650452676615818</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.6462267168484536</v>
+        <v>0.6444424815372659</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.6265221149969087</v>
+        <v>0.6240433857254404</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.6069590807485146</v>
+        <v>0.6037670001509156</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>0.5874844735552959</v>
+        <v>0.5835548339830264</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0.5680638961183928</v>
+        <v>0.5633758820902205</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.5486920041336587</v>
+        <v>0.5432292808163677</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.5293818341629896</v>
+        <v>0.523129964929599</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0.5101659265830247</v>
+        <v>0.5031123582188483</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>0.4910884042506482</v>
+        <v>0.4832307453184389</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.4722115293545242</v>
+        <v>0.4635480071574731</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
@@ -2080,40 +2080,40 @@
       </c>
       <c r="B36" s="1" t="inlineStr"/>
       <c r="C36" s="2" t="n">
-        <v>0.8048717318259582</v>
+        <v>0.8040478542246802</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.8017013803452042</v>
+        <v>0.8005010283847622</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.79861353501171</v>
+        <v>0.7969752774493983</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.7957143733613891</v>
+        <v>0.7935817820982608</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.7930847431136775</v>
+        <v>0.7903875391334443</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>0.7907676001258164</v>
+        <v>0.7874289737237021</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0.7887739724279766</v>
+        <v>0.7846923256098197</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.7870517722545544</v>
+        <v>0.7820906541333305</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.7854843445483178</v>
+        <v>0.7794660188101106</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0.783863096581575</v>
+        <v>0.7765536495460788</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.7818701232259075</v>
+        <v>0.7729394765230466</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.7790198667361168</v>
+        <v>0.7680316027741193</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
@@ -2124,40 +2124,40 @@
       </c>
       <c r="B37" s="1" t="inlineStr"/>
       <c r="C37" s="2" t="n">
-        <v>0.1184560799864066</v>
+        <v>0.1180764921074539</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.1355463330411811</v>
+        <v>0.1354557607231804</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.1523868181632564</v>
+        <v>0.1525327959121324</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0.1691922583644804</v>
+        <v>0.1695383963728204</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.1861256623651629</v>
+        <v>0.1866205389825287</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>0.2032831265705205</v>
+        <v>0.2038741397406757</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0.2207100763095838</v>
+        <v>0.2213164435195992</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.2383597681208957</v>
+        <v>0.2388613733169628</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.2561025103853283</v>
+        <v>0.2563360538805116</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0.2736971699985503</v>
+        <v>0.2734412913272305</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>0.2907817189752593</v>
+        <v>0.2897087312046077</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.3068083373815926</v>
+        <v>0.3044835956166462</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
@@ -2168,40 +2168,40 @@
       </c>
       <c r="B38" s="1" t="inlineStr"/>
       <c r="C38" s="2" t="n">
-        <v>0.2276335518032631</v>
+        <v>0.2282408924738002</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.2564688588613289</v>
+        <v>0.2579216561209626</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.2835218497930739</v>
+        <v>0.2858015106003043</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0.3085001630395364</v>
+        <v>0.3115711512862566</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.3309131091164997</v>
+        <v>0.3347082946500182</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>0.3500873148598649</v>
+        <v>0.3544849999638067</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0.3651644108777011</v>
+        <v>0.3699551994907062</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.3751414754015637</v>
+        <v>0.3800218127586333</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.378944172581735</v>
+        <v>0.383513384800337</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0.3755430328135231</v>
+        <v>0.3792800294857439</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>0.3640817981821198</v>
+        <v>0.3663863085326451</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.3485694688213637</v>
+        <v>0.3491674851495545</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
@@ -2212,40 +2212,40 @@
       </c>
       <c r="B39" s="1" t="inlineStr"/>
       <c r="C39" s="2" t="n">
-        <v>316.6749545242313</v>
+        <v>314.5701555829461</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>311.9023424126456</v>
+        <v>309.7982108942016</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>306.8733257040238</v>
+        <v>304.772787142599</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>301.6032562789239</v>
+        <v>299.5122741880747</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>296.0981953341694</v>
+        <v>294.0209229436405</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>290.3519805579891</v>
+        <v>288.293377752659</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>284.3488836067119</v>
+        <v>282.3107123067431</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>278.0574255764263</v>
+        <v>276.0371139971909</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>271.4332623267771</v>
+        <v>269.4242051591646</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>264.4170040289303</v>
+        <v>262.4074828809398</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>256.936286143264</v>
+        <v>254.9040418704614</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>248.9011968387375</v>
+        <v>246.8160263197884</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
@@ -2256,40 +2256,40 @@
       </c>
       <c r="B40" s="1" t="inlineStr"/>
       <c r="C40" s="2" t="n">
-        <v>212.5515131481671</v>
+        <v>210.7618081429513</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>210.2257778582746</v>
+        <v>208.2659101445495</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>208.8825020558515</v>
+        <v>206.7691165118553</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>208.4642333794313</v>
+        <v>206.2168293707466</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>208.9033255749229</v>
+        <v>206.5410165021746</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>210.118339364321</v>
+        <v>207.660751601391</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>212.0152885729822</v>
+        <v>209.4788267411302</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>214.483089016131</v>
+        <v>211.8788787036171</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>217.3964080444979</v>
+        <v>214.7296805683502</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>220.6151229778069</v>
+        <v>217.8837766117229</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>223.9876891329342</v>
+        <v>221.1769059517512</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>227.3483494622677</v>
+        <v>224.4327929220609</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
@@ -2300,40 +2300,40 @@
       </c>
       <c r="B41" s="1" t="inlineStr"/>
       <c r="C41" s="2" t="n">
-        <v>272.9439743328568</v>
+        <v>271.0687995179351</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>262.7117365074325</v>
+        <v>260.7393907922885</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>252.3988723295163</v>
+        <v>250.3367797675996</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>241.9814690400069</v>
+        <v>239.8341578092439</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>231.4453120774244</v>
+        <v>229.2187155215777</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>220.7877626061483</v>
+        <v>218.4869610830073</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>210.0149078425442</v>
+        <v>207.6475328071683</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>199.1462424361535</v>
+        <v>196.7233545925395</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>188.2116603590246</v>
+        <v>185.7474577896496</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>177.2527835145796</v>
+        <v>174.7655466880916</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>166.3209005735733</v>
+        <v>163.8375782957042</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>155.4805367608402</v>
+        <v>153.0350504404822</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
@@ -2344,40 +2344,40 @@
       </c>
       <c r="B42" s="1" t="inlineStr"/>
       <c r="C42" s="2" t="n">
-        <v>198.6824351847945</v>
+        <v>196.788038117527</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>205.4580163879</v>
+        <v>203.3516736968311</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>201.8066005548523</v>
+        <v>199.6014152632706</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>195.9509638973385</v>
+        <v>193.6247631348237</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>189.336448544344</v>
+        <v>186.8829196883579</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>182.3844413155287</v>
+        <v>179.8020501672326</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>175.268507737364</v>
+        <v>172.5598555050506</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>168.0668547136884</v>
+        <v>165.2381621177473</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>160.8335726775535</v>
+        <v>157.8940707203957</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>153.6164801316091</v>
+        <v>150.5789179883501</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>146.4631727744364</v>
+        <v>143.3472835541374</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>139.4268995749411</v>
+        <v>136.2577142571018</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
@@ -2388,40 +2388,40 @@
       </c>
       <c r="B43" s="1" t="inlineStr"/>
       <c r="C43" s="2" t="n">
-        <v>326.2718766347037</v>
+        <v>326.4880494232335</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>348.9155469082214</v>
+        <v>349.1284711068405</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>370.1229094630255</v>
+        <v>370.331957905283</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>390.0917984928992</v>
+        <v>390.2973869534582</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>409.0577039563908</v>
+        <v>409.2589650277441</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>427.1299245817816</v>
+        <v>427.3266475274125</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>444.4312659450177</v>
+        <v>444.6227227940063</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>461.0363542839652</v>
+        <v>461.2220150851436</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>477.025831392006</v>
+        <v>477.2047767231235</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>492.4400509770026</v>
+        <v>492.6119039013639</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>507.3402053890704</v>
+        <v>507.5038920028636</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>521.7685286185019</v>
+        <v>521.9227459001808</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
@@ -2432,40 +2432,40 @@
       </c>
       <c r="B44" s="1" t="inlineStr"/>
       <c r="C44" s="2" t="n">
-        <v>0.9705861191302823</v>
+        <v>0.9634966919575119</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.8939193027551975</v>
+        <v>0.8873473134747493</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.8291119459458369</v>
+        <v>0.8229718787071257</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0.7731596958565997</v>
+        <v>0.76739502799641</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.7238543424810698</v>
+        <v>0.7184226811591251</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>0.6797743820976329</v>
+        <v>0.6746440443645988</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0.6398039593413525</v>
+        <v>0.6349444097969273</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.6031138824361841</v>
+        <v>0.5984907592631572</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.5690116644935338</v>
+        <v>0.5645882403132058</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0.5369526778017468</v>
+        <v>0.5326860370257758</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.5064378565192246</v>
+        <v>0.5022701222339061</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.4770337480831945</v>
+        <v>0.4728976237548241</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
@@ -2476,40 +2476,40 @@
       </c>
       <c r="B45" s="1" t="inlineStr"/>
       <c r="C45" s="2" t="n">
-        <v>1.01907065000851</v>
+        <v>1.012297336253858</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.9463040700801164</v>
+        <v>0.9399201865719472</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.8834101531170189</v>
+        <v>0.8773632375438932</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.827818287398653</v>
+        <v>0.8220791145701367</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.7782928631444037</v>
+        <v>0.772832761388191</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>0.7334327609516046</v>
+        <v>0.7282327043295886</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0.692430171875216</v>
+        <v>0.6874669334561038</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.6544413238133387</v>
+        <v>0.649686279485034</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.6189369497118317</v>
+        <v>0.6143557878289457</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0.5852128385553067</v>
+        <v>0.5807653273996938</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>0.5529150076467954</v>
+        <v>0.5485417119379508</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.5216291318476798</v>
+        <v>0.5172591822396891</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
@@ -2520,40 +2520,40 @@
       </c>
       <c r="B46" s="1" t="inlineStr"/>
       <c r="C46" s="2" t="n">
-        <v>0.8163283366743694</v>
+        <v>0.8102668014124158</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.7616870018750188</v>
+        <v>0.7557708555521092</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0.7157236225124972</v>
+        <v>0.7099294706681303</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>0.6763174394727927</v>
+        <v>0.6706389262199457</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.6424379077920499</v>
+        <v>0.6368645265581221</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>0.6129201678110948</v>
+        <v>0.6074478490009285</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0.5870850151170974</v>
+        <v>0.5817024223816692</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.5642158372532415</v>
+        <v>0.5589037376408996</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.5438575546609512</v>
+        <v>0.5385892027183966</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0.5253966577574078</v>
+        <v>0.5201384789422266</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>0.5085234823660012</v>
+        <v>0.5032219799449003</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.4928784347822723</v>
+        <v>0.4874696705720056</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
@@ -2564,40 +2564,40 @@
       </c>
       <c r="B47" s="1" t="inlineStr"/>
       <c r="C47" s="2" t="n">
-        <v>0.6839979151165261</v>
+        <v>0.6782385842413425</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.6378198627307841</v>
+        <v>0.6318736720738927</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.6013195272064865</v>
+        <v>0.5952356284422855</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.5721771932741999</v>
+        <v>0.5660086851469479</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.5491015141061614</v>
+        <v>0.5428921946275799</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>0.5307615724555451</v>
+        <v>0.5245536748039339</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0.5162875297580325</v>
+        <v>0.5101108826760857</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5048115381932501</v>
+        <v>0.4986822185360721</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.4957191632298202</v>
+        <v>0.4896383455892302</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0.4882696663938627</v>
+        <v>0.4822245976743076</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0.4820111503467031</v>
+        <v>0.4759624749048438</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.4764602326675061</v>
+        <v>0.4703500200761771</v>
       </c>
     </row>
   </sheetData>

--- a/results/Расчет_ступеней_по_высоте_лопаток.xlsx
+++ b/results/Расчет_ступеней_по_высоте_лопаток.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1564,1039 +1564,1215 @@
         <v>0.6807728945329433</v>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
+    <row r="25" ht="15" customHeight="1">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>c_1u_к_i</t>
-        </is>
-      </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>Окружная составляющая абсолютной скорости (периферия), вход</t>
-        </is>
-      </c>
+          <t>D_ср1_i</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr"/>
       <c r="C25" s="2" t="n">
-        <v>63.1329097750037</v>
+        <v>0.4867526195910545</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>62.77183610591472</v>
+        <v>0.501832502447439</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>62.90261564382815</v>
+        <v>0.5169123853038237</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>63.4876566949365</v>
+        <v>0.5319922681602083</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>64.50976044591263</v>
+        <v>0.5470721510165928</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>65.96510841054763</v>
+        <v>0.5621520338729775</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>67.86700835570147</v>
+        <v>0.577231916729362</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>70.24870063537821</v>
+        <v>0.5923117995857468</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>73.15725958263666</v>
+        <v>0.6073916824421313</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>76.65702786453478</v>
+        <v>0.6224715652985159</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>80.83147187427544</v>
+        <v>0.6375514481549005</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>85.77863645278707</v>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
+        <v>0.652631331011285</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>c_2u_к_i</t>
-        </is>
-      </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>Окружная составляющая абсолютной скорости (периферия), выход из РК</t>
-        </is>
-      </c>
+          <t>D_ср2_i</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr"/>
       <c r="C26" s="2" t="n">
-        <v>118.4818050203147</v>
+        <v>0.499513600828743</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>124.9834481607296</v>
+        <v>0.5675288881640966</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>131.5948975476958</v>
+        <v>0.5844542258540137</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>138.3537448750209</v>
+        <v>0.5949265769048206</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>145.2771889560321</v>
+        <v>0.6034225179525432</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>152.3690482769383</v>
+        <v>0.6111218150628972</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>159.6160150708794</v>
+        <v>0.6184683559077462</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>166.9848489838514</v>
+        <v>0.6256246358243144</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>174.4284756827955</v>
+        <v>0.6326628619275969</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>181.8825525006537</v>
+        <v>0.6396082573033322</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>189.2636130442233</v>
+        <v>0.6464562235743894</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>196.4736124725757</v>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
+        <v>0.6531775376318343</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>c_3u_к_i</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>Окружная составляющая абсолютной скорости (периферия), выход из ступени</t>
-        </is>
-      </c>
+          <t>D_вт1_i</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr"/>
       <c r="C27" s="2" t="n">
-        <v>62.77183610591472</v>
+        <v>0.2927323446491656</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>62.90261564382815</v>
+        <v>0.3228921103619348</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>63.4876566949365</v>
+        <v>0.3530518760747041</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>64.50976044591263</v>
+        <v>0.3832116417874732</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>65.96510841054763</v>
+        <v>0.4133714075002424</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>67.86700835570147</v>
+        <v>0.4435311732130116</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>70.24870063537821</v>
+        <v>0.4736909389257808</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>73.15725958263666</v>
+        <v>0.5038507046385501</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>76.65702786453478</v>
+        <v>0.5340104703513192</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>80.83147187427544</v>
+        <v>0.5641702360640884</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>85.77863645278707</v>
+        <v>0.5943300017768577</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>90.7258010312987</v>
+        <v>0.6244897674896268</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>c_a1_к_i</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>Осевая скорость (периферия), вход</t>
-        </is>
-      </c>
+          <t>D_вт2_i</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr"/>
       <c r="C28" s="2" t="n">
-        <v>199.2565864072191</v>
+        <v>0.3182543071245426</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>191.1748507347584</v>
+        <v>0.45428488179525</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>183.0931150622978</v>
+        <v>0.4881355571750841</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>175.0113793898372</v>
+        <v>0.5090802592766979</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>166.9296437173765</v>
+        <v>0.526072141372143</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>158.8479080449159</v>
+        <v>0.5414707355928511</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>150.7661723724553</v>
+        <v>0.5561638172825492</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>142.6844366999946</v>
+        <v>0.5704763771156854</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>134.602701027534</v>
+        <v>0.5845528293222505</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>126.5209653550734</v>
+        <v>0.598443620073721</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>118.4392296826127</v>
+        <v>0.6121395526158354</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>110.3574940101521</v>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
+        <v>0.6255821807307252</v>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>c_a2_к_i</t>
+          <t>c_1u_к_i</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>Осевая скорость (периферия), выход из РК</t>
+          <t>Окружная составляющая абсолютной скорости (периферия), вход</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>195.2157185709887</v>
+        <v>63.1329097750037</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>187.1339828985281</v>
+        <v>62.77183610591472</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>179.0522472260675</v>
+        <v>62.90261564382815</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>170.9705115536069</v>
+        <v>63.4876566949365</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>162.8887758811462</v>
+        <v>64.50976044591263</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>154.8070402086856</v>
+        <v>65.96510841054763</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>146.7253045362249</v>
+        <v>67.86700835570147</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>138.6435688637643</v>
+        <v>70.24870063537821</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>130.5618331913037</v>
+        <v>73.15725958263666</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>122.480097518843</v>
+        <v>76.65702786453478</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>114.3983618463824</v>
+        <v>80.83147187427544</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>106.3166261739218</v>
+        <v>85.77863645278707</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>c_a3_к_i</t>
+          <t>c_2u_к_i</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>Осевая скорость (периферия), выход из ступени</t>
+          <t>Окружная составляющая абсолютной скорости (периферия), выход из РК</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>191.1748507347584</v>
+        <v>118.4818050203147</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>183.0931150622978</v>
+        <v>124.9834481607296</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>175.0113793898372</v>
+        <v>131.5948975476958</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>166.9296437173765</v>
+        <v>138.3537448750209</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>158.8479080449159</v>
+        <v>145.2771889560321</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>150.7661723724553</v>
+        <v>152.3690482769383</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>142.6844366999946</v>
+        <v>159.6160150708794</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>134.602701027534</v>
+        <v>166.9848489838514</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>126.5209653550734</v>
+        <v>174.4284756827955</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>118.4392296826127</v>
+        <v>181.8825525006537</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>110.3574940101521</v>
+        <v>189.2636130442233</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>102.2757583376915</v>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
+        <v>196.4736124725757</v>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>c_1_к_i</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="inlineStr"/>
+          <t>c_3u_к_i</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>Окружная составляющая абсолютной скорости (периферия), выход из ступени</t>
+        </is>
+      </c>
       <c r="C31" s="2" t="n">
-        <v>201.2166170115306</v>
+        <v>62.77183610591472</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>193.5970760059433</v>
+        <v>62.90261564382815</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>186.1710650679843</v>
+        <v>63.4876566949365</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>178.9609318940849</v>
+        <v>64.50976044591263</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>172.0001552844106</v>
+        <v>65.96510841054763</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>165.3371390674029</v>
+        <v>67.86700835570147</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>159.040021432826</v>
+        <v>70.24870063537821</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>153.1987981465552</v>
+        <v>73.15725958263666</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>147.9319255448388</v>
+        <v>76.65702786453478</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>143.3930890007342</v>
+        <v>80.83147187427544</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>139.773928026296</v>
+        <v>85.77863645278707</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>136.7168669781482</v>
+        <v>90.7258010312987</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>α_1_к_i</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="inlineStr"/>
+          <t>c_a1_к_i</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>Осевая скорость (периферия), вход</t>
+        </is>
+      </c>
       <c r="C32" s="2" t="n">
-        <v>1.263960413517295</v>
+        <v>199.2565864072191</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1.253539469396991</v>
+        <v>191.1748507347584</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1.239874358014764</v>
+        <v>183.0931150622978</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>1.22279688589888</v>
+        <v>175.0113793898372</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>1.202026324602637</v>
+        <v>166.9296437173765</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>1.177194043197224</v>
+        <v>158.8479080449159</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1.147819786142874</v>
+        <v>150.7661723724553</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.113298604686115</v>
+        <v>142.6844366999946</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1.072953245860255</v>
+        <v>134.602701027534</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1.026061588748283</v>
+        <v>126.5209653550734</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>0.9719311589381017</v>
+        <v>118.4392296826127</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.9100635927466534</v>
+        <v>110.3574940101521</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>α_2_к_i</t>
-        </is>
-      </c>
-      <c r="B33" s="1" t="inlineStr"/>
+          <t>c_a2_к_i</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>Осевая скорость (периферия), выход из РК</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="n">
-        <v>1.025298576923191</v>
+        <v>195.2157185709887</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.9819527018938013</v>
+        <v>187.1339828985281</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.9369953752985757</v>
+        <v>179.0522472260675</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.8904551733163805</v>
+        <v>170.9705115536069</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.8424857485472055</v>
+        <v>162.8887758811462</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>0.7933347861790676</v>
+        <v>154.8070402086856</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0.7433434051954089</v>
+        <v>146.7253045362249</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.6929314331016215</v>
+        <v>138.6435688637643</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.6425482039479457</v>
+        <v>130.5618331913037</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0.5926511294523578</v>
+        <v>122.480097518843</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>0.5436772842140083</v>
+        <v>114.3983618463824</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.4960032468828308</v>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
+        <v>106.3166261739218</v>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>α_3_к_i</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="inlineStr"/>
+          <t>c_a3_к_i</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>Осевая скорость (периферия), выход из ступени</t>
+        </is>
+      </c>
       <c r="C34" s="2" t="n">
-        <v>1.253539469396991</v>
+        <v>191.1748507347584</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1.239874358014764</v>
+        <v>183.0931150622978</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1.22279688589888</v>
+        <v>175.0113793898372</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>1.202026324602637</v>
+        <v>166.9296437173765</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1.177194043197224</v>
+        <v>158.8479080449159</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>1.147819786142874</v>
+        <v>150.7661723724553</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1.113298604686115</v>
+        <v>142.6844366999946</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.072953245860255</v>
+        <v>134.602701027534</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>1.026061588748283</v>
+        <v>126.5209653550734</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0.9719311589381017</v>
+        <v>118.4392296826127</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>0.9100635927466534</v>
+        <v>110.3574940101521</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.8451707320323852</v>
+        <v>102.2757583376915</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>β_1_к_i</t>
+          <t>c_1_к_i</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr"/>
       <c r="C35" s="2" t="n">
-        <v>0.6859713621172263</v>
+        <v>201.2166170115306</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.6650452676615818</v>
+        <v>193.5970760059433</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.6444424815372659</v>
+        <v>186.1710650679843</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.6240433857254404</v>
+        <v>178.9609318940849</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.6037670001509156</v>
+        <v>172.0001552844106</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>0.5835548339830264</v>
+        <v>165.3371390674029</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0.5633758820902205</v>
+        <v>159.040021432826</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.5432292808163677</v>
+        <v>153.1987981465552</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.523129964929599</v>
+        <v>147.9319255448388</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0.5031123582188483</v>
+        <v>143.3930890007342</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>0.4832307453184389</v>
+        <v>139.773928026296</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.4635480071574731</v>
+        <v>136.7168669781482</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>β_2_к_i</t>
+          <t>α_1_к_i</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr"/>
       <c r="C36" s="2" t="n">
-        <v>0.8040478542246802</v>
+        <v>1.263960413517295</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.8005010283847622</v>
+        <v>1.253539469396991</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.7969752774493983</v>
+        <v>1.239874358014764</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.7935817820982608</v>
+        <v>1.22279688589888</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.7903875391334443</v>
+        <v>1.202026324602637</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>0.7874289737237021</v>
+        <v>1.177194043197224</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0.7846923256098197</v>
+        <v>1.147819786142874</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.7820906541333305</v>
+        <v>1.113298604686115</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.7794660188101106</v>
+        <v>1.072953245860255</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0.7765536495460788</v>
+        <v>1.026061588748283</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.7729394765230466</v>
+        <v>0.9719311589381017</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.7680316027741193</v>
+        <v>0.9100635927466534</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>ε_к_рк_i</t>
+          <t>α_2_к_i</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr"/>
       <c r="C37" s="2" t="n">
-        <v>0.1180764921074539</v>
+        <v>1.025298576923191</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.1354557607231804</v>
+        <v>0.9819527018938013</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.1525327959121324</v>
+        <v>0.9369953752985757</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0.1695383963728204</v>
+        <v>0.8904551733163805</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.1866205389825287</v>
+        <v>0.8424857485472055</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>0.2038741397406757</v>
+        <v>0.7933347861790676</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0.2213164435195992</v>
+        <v>0.7433434051954089</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.2388613733169628</v>
+        <v>0.6929314331016215</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.2563360538805116</v>
+        <v>0.6425482039479457</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0.2734412913272305</v>
+        <v>0.5926511294523578</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>0.2897087312046077</v>
+        <v>0.5436772842140083</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.3044835956166462</v>
+        <v>0.4960032468828308</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>ε_к_на_i</t>
+          <t>α_3_к_i</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr"/>
       <c r="C38" s="2" t="n">
-        <v>0.2282408924738002</v>
+        <v>1.253539469396991</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.2579216561209626</v>
+        <v>1.239874358014764</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.2858015106003043</v>
+        <v>1.22279688589888</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0.3115711512862566</v>
+        <v>1.202026324602637</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.3347082946500182</v>
+        <v>1.177194043197224</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>0.3544849999638067</v>
+        <v>1.147819786142874</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0.3699551994907062</v>
+        <v>1.113298604686115</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.3800218127586333</v>
+        <v>1.072953245860255</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.383513384800337</v>
+        <v>1.026061588748283</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0.3792800294857439</v>
+        <v>0.9719311589381017</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>0.3663863085326451</v>
+        <v>0.9100635927466534</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.3491674851495545</v>
+        <v>0.8451707320323852</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>W_1к_i</t>
+          <t>β_1_к_i</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr"/>
       <c r="C39" s="2" t="n">
-        <v>314.5701555829461</v>
+        <v>0.6859713621172263</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>309.7982108942016</v>
+        <v>0.6650452676615818</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>304.772787142599</v>
+        <v>0.6444424815372659</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>299.5122741880747</v>
+        <v>0.6240433857254404</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>294.0209229436405</v>
+        <v>0.6037670001509156</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>288.293377752659</v>
+        <v>0.5835548339830264</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>282.3107123067431</v>
+        <v>0.5633758820902205</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>276.0371139971909</v>
+        <v>0.5432292808163677</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>269.4242051591646</v>
+        <v>0.523129964929599</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>262.4074828809398</v>
+        <v>0.5031123582188483</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>254.9040418704614</v>
+        <v>0.4832307453184389</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>246.8160263197884</v>
+        <v>0.4635480071574731</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>W_1вт_i</t>
+          <t>β_2_к_i</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr"/>
       <c r="C40" s="2" t="n">
-        <v>210.7618081429513</v>
+        <v>0.8040478542246802</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>208.2659101445495</v>
+        <v>0.8005010283847622</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>206.7691165118553</v>
+        <v>0.7969752774493983</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>206.2168293707466</v>
+        <v>0.7935817820982608</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>206.5410165021746</v>
+        <v>0.7903875391334443</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>207.660751601391</v>
+        <v>0.7874289737237021</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>209.4788267411302</v>
+        <v>0.7846923256098197</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>211.8788787036171</v>
+        <v>0.7820906541333305</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>214.7296805683502</v>
+        <v>0.7794660188101106</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>217.8837766117229</v>
+        <v>0.7765536495460788</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>221.1769059517512</v>
+        <v>0.7729394765230466</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>224.4327929220609</v>
+        <v>0.7680316027741193</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>W_2к_i</t>
+          <t>ε_к_рк_i</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr"/>
       <c r="C41" s="2" t="n">
-        <v>271.0687995179351</v>
+        <v>0.1180764921074539</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>260.7393907922885</v>
+        <v>0.1354557607231804</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>250.3367797675996</v>
+        <v>0.1525327959121324</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>239.8341578092439</v>
+        <v>0.1695383963728204</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>229.2187155215777</v>
+        <v>0.1866205389825287</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>218.4869610830073</v>
+        <v>0.2038741397406757</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>207.6475328071683</v>
+        <v>0.2213164435195992</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>196.7233545925395</v>
+        <v>0.2388613733169628</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>185.7474577896496</v>
+        <v>0.2563360538805116</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>174.7655466880916</v>
+        <v>0.2734412913272305</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>163.8375782957042</v>
+        <v>0.2897087312046077</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>153.0350504404822</v>
+        <v>0.3044835956166462</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>W_2вт_i</t>
+          <t>ε_к_на_i</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr"/>
       <c r="C42" s="2" t="n">
-        <v>196.788038117527</v>
+        <v>0.2282408924738002</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>203.3516736968311</v>
+        <v>0.2579216561209626</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>199.6014152632706</v>
+        <v>0.2858015106003043</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>193.6247631348237</v>
+        <v>0.3115711512862566</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>186.8829196883579</v>
+        <v>0.3347082946500182</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>179.8020501672326</v>
+        <v>0.3544849999638067</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>172.5598555050506</v>
+        <v>0.3699551994907062</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>165.2381621177473</v>
+        <v>0.3800218127586333</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>157.8940707203957</v>
+        <v>0.383513384800337</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>150.5789179883501</v>
+        <v>0.3792800294857439</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>143.3472835541374</v>
+        <v>0.3663863085326451</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>136.2577142571018</v>
+        <v>0.3491674851495545</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>a_1к_i</t>
+          <t>W_1к_i</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr"/>
       <c r="C43" s="2" t="n">
-        <v>326.4880494232335</v>
+        <v>314.5701555829461</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>349.1284711068405</v>
+        <v>309.7982108942016</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>370.331957905283</v>
+        <v>304.772787142599</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>390.2973869534582</v>
+        <v>299.5122741880747</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>409.2589650277441</v>
+        <v>294.0209229436405</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>427.3266475274125</v>
+        <v>288.293377752659</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>444.6227227940063</v>
+        <v>282.3107123067431</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>461.2220150851436</v>
+        <v>276.0371139971909</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>477.2047767231235</v>
+        <v>269.4242051591646</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>492.6119039013639</v>
+        <v>262.4074828809398</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>507.5038920028636</v>
+        <v>254.9040418704614</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>521.9227459001808</v>
+        <v>246.8160263197884</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>M_w1к_i</t>
+          <t>W_1вт_i</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr"/>
       <c r="C44" s="2" t="n">
-        <v>0.9634966919575119</v>
+        <v>210.7618081429513</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.8873473134747493</v>
+        <v>208.2659101445495</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.8229718787071257</v>
+        <v>206.7691165118553</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0.76739502799641</v>
+        <v>206.2168293707466</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.7184226811591251</v>
+        <v>206.5410165021746</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>0.6746440443645988</v>
+        <v>207.660751601391</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0.6349444097969273</v>
+        <v>209.4788267411302</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.5984907592631572</v>
+        <v>211.8788787036171</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.5645882403132058</v>
+        <v>214.7296805683502</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0.5326860370257758</v>
+        <v>217.8837766117229</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.5022701222339061</v>
+        <v>221.1769059517512</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.4728976237548241</v>
+        <v>224.4327929220609</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>λ_w1к_i</t>
+          <t>W_2к_i</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr"/>
       <c r="C45" s="2" t="n">
-        <v>1.012297336253858</v>
+        <v>271.0687995179351</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.9399201865719472</v>
+        <v>260.7393907922885</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.8773632375438932</v>
+        <v>250.3367797675996</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.8220791145701367</v>
+        <v>239.8341578092439</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.772832761388191</v>
+        <v>229.2187155215777</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>0.7282327043295886</v>
+        <v>218.4869610830073</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0.6874669334561038</v>
+        <v>207.6475328071683</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.649686279485034</v>
+        <v>196.7233545925395</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.6143557878289457</v>
+        <v>185.7474577896496</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0.5807653273996938</v>
+        <v>174.7655466880916</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>0.5485417119379508</v>
+        <v>163.8375782957042</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.5172591822396891</v>
+        <v>153.0350504404822</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>λ_w1_i</t>
+          <t>W_2вт_i</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr"/>
       <c r="C46" s="2" t="n">
-        <v>0.8102668014124158</v>
+        <v>196.788038117527</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.7557708555521092</v>
+        <v>203.3516736968311</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0.7099294706681303</v>
+        <v>199.6014152632706</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>0.6706389262199457</v>
+        <v>193.6247631348237</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.6368645265581221</v>
+        <v>186.8829196883579</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>0.6074478490009285</v>
+        <v>179.8020501672326</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0.5817024223816692</v>
+        <v>172.5598555050506</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.5589037376408996</v>
+        <v>165.2381621177473</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.5385892027183966</v>
+        <v>157.8940707203957</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0.5201384789422266</v>
+        <v>150.5789179883501</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>0.5032219799449003</v>
+        <v>143.3472835541374</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.4874696705720056</v>
+        <v>136.2577142571018</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>λ_w1вт_i</t>
+          <t>a_1к_i</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr"/>
       <c r="C47" s="2" t="n">
+        <v>326.4880494232335</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>349.1284711068405</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>370.331957905283</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>390.2973869534582</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>409.2589650277441</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>427.3266475274125</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>444.6227227940063</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>461.2220150851436</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>477.2047767231235</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>492.6119039013639</v>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>507.5038920028636</v>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>521.9227459001808</v>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>M_w1к_i</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="inlineStr"/>
+      <c r="C48" s="2" t="n">
+        <v>0.9634966919575119</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>0.8873473134747493</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>0.8229718787071257</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>0.76739502799641</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>0.7184226811591251</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>0.6746440443645988</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>0.6349444097969273</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>0.5984907592631572</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>0.5645882403132058</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0.5326860370257758</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>0.5022701222339061</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>0.4728976237548241</v>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>λ_w1к_i</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="inlineStr"/>
+      <c r="C49" s="2" t="n">
+        <v>1.012297336253858</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>0.9399201865719472</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>0.8773632375438932</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>0.8220791145701367</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>0.772832761388191</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>0.7282327043295886</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>0.6874669334561038</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>0.649686279485034</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>0.6143557878289457</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0.5807653273996938</v>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>0.5485417119379508</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>0.5172591822396891</v>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>λ_w1_i</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="inlineStr"/>
+      <c r="C50" s="2" t="n">
+        <v>0.8102668014124158</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>0.7557708555521092</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>0.7099294706681303</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>0.6706389262199457</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>0.6368645265581221</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>0.6074478490009285</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>0.5817024223816692</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>0.5589037376408996</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>0.5385892027183966</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>0.5201384789422266</v>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>0.5032219799449003</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>0.4874696705720056</v>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>λ_w1вт_i</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="inlineStr"/>
+      <c r="C51" s="2" t="n">
         <v>0.6782385842413425</v>
       </c>
-      <c r="D47" s="2" t="n">
+      <c r="D51" s="2" t="n">
         <v>0.6318736720738927</v>
       </c>
-      <c r="E47" s="2" t="n">
+      <c r="E51" s="2" t="n">
         <v>0.5952356284422855</v>
       </c>
-      <c r="F47" s="2" t="n">
+      <c r="F51" s="2" t="n">
         <v>0.5660086851469479</v>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G51" s="2" t="n">
         <v>0.5428921946275799</v>
       </c>
-      <c r="H47" s="2" t="n">
+      <c r="H51" s="2" t="n">
         <v>0.5245536748039339</v>
       </c>
-      <c r="I47" s="2" t="n">
+      <c r="I51" s="2" t="n">
         <v>0.5101108826760857</v>
       </c>
-      <c r="J47" s="2" t="n">
+      <c r="J51" s="2" t="n">
         <v>0.4986822185360721</v>
       </c>
-      <c r="K47" s="2" t="n">
+      <c r="K51" s="2" t="n">
         <v>0.4896383455892302</v>
       </c>
-      <c r="L47" s="2" t="n">
+      <c r="L51" s="2" t="n">
         <v>0.4822245976743076</v>
       </c>
-      <c r="M47" s="2" t="n">
+      <c r="M51" s="2" t="n">
         <v>0.4759624749048438</v>
       </c>
-      <c r="N47" s="2" t="n">
+      <c r="N51" s="2" t="n">
         <v>0.4703500200761771</v>
       </c>
     </row>

--- a/results/Расчет_ступеней_по_высоте_лопаток.xlsx
+++ b/results/Расчет_ступеней_по_высоте_лопаток.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1476,1303 +1476,1039 @@
         <v>306.5485944726447</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>D_к1_i</t>
-        </is>
-      </c>
-      <c r="B23" s="1" t="inlineStr"/>
+          <t>c_1u_к_i</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>Окружная составляющая абсолютной скорости (периферия), вход</t>
+        </is>
+      </c>
       <c r="C23" s="2" t="n">
-        <v>0.6807728945329433</v>
+        <v>63.1329097750037</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.6807728945329433</v>
+        <v>62.77183610591472</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.6807728945329433</v>
+        <v>62.90261564382815</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.6807728945329433</v>
+        <v>63.4876566949365</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.6807728945329433</v>
+        <v>64.50976044591263</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0.6807728945329433</v>
+        <v>65.96510841054763</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0.6807728945329433</v>
+        <v>67.86700835570147</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.6807728945329433</v>
+        <v>70.24870063537821</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.6807728945329433</v>
+        <v>73.15725958263666</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0.6807728945329433</v>
+        <v>76.65702786453478</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0.6807728945329433</v>
+        <v>80.83147187427544</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.6807728945329433</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
+        <v>85.77863645278707</v>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>D_к2_i</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="inlineStr"/>
+          <t>c_2u_к_i</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>Окружная составляющая абсолютной скорости (периферия), выход из РК</t>
+        </is>
+      </c>
       <c r="C24" s="2" t="n">
-        <v>0.6807728945329433</v>
+        <v>118.4818050203147</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.6807728945329433</v>
+        <v>124.9834481607296</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.6807728945329433</v>
+        <v>131.5948975476958</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.6807728945329433</v>
+        <v>138.3537448750209</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.6807728945329433</v>
+        <v>145.2771889560321</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0.6807728945329433</v>
+        <v>152.3690482769383</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0.6807728945329433</v>
+        <v>159.6160150708794</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.6807728945329433</v>
+        <v>166.9848489838514</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.6807728945329433</v>
+        <v>174.4284756827955</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0.6807728945329433</v>
+        <v>181.8825525006537</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>0.6807728945329433</v>
+        <v>189.2636130442233</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.6807728945329433</v>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
+        <v>196.4736124725757</v>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>D_ср1_i</t>
-        </is>
-      </c>
-      <c r="B25" s="1" t="inlineStr"/>
+          <t>c_3u_к_i</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>Окружная составляющая абсолютной скорости (периферия), выход из ступени</t>
+        </is>
+      </c>
       <c r="C25" s="2" t="n">
-        <v>0.4867526195910545</v>
+        <v>62.77183610591472</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.501832502447439</v>
+        <v>62.90261564382815</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.5169123853038237</v>
+        <v>63.4876566949365</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.5319922681602083</v>
+        <v>64.50976044591263</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.5470721510165928</v>
+        <v>65.96510841054763</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0.5621520338729775</v>
+        <v>67.86700835570147</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0.577231916729362</v>
+        <v>70.24870063537821</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.5923117995857468</v>
+        <v>73.15725958263666</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.6073916824421313</v>
+        <v>76.65702786453478</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0.6224715652985159</v>
+        <v>80.83147187427544</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>0.6375514481549005</v>
+        <v>85.77863645278707</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.652631331011285</v>
+        <v>90.7258010312987</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>D_ср2_i</t>
-        </is>
-      </c>
-      <c r="B26" s="1" t="inlineStr"/>
+          <t>c_a1_к_i</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>Осевая скорость (периферия), вход</t>
+        </is>
+      </c>
       <c r="C26" s="2" t="n">
-        <v>0.499513600828743</v>
+        <v>199.2565864072191</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.5675288881640966</v>
+        <v>191.1748507347584</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.5844542258540137</v>
+        <v>183.0931150622978</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.5949265769048206</v>
+        <v>175.0113793898372</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.6034225179525432</v>
+        <v>166.9296437173765</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0.6111218150628972</v>
+        <v>158.8479080449159</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0.6184683559077462</v>
+        <v>150.7661723724553</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.6256246358243144</v>
+        <v>142.6844366999946</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.6326628619275969</v>
+        <v>134.602701027534</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0.6396082573033322</v>
+        <v>126.5209653550734</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>0.6464562235743894</v>
+        <v>118.4392296826127</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.6531775376318343</v>
+        <v>110.3574940101521</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>D_вт1_i</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="inlineStr"/>
+          <t>c_a2_к_i</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>Осевая скорость (периферия), выход из РК</t>
+        </is>
+      </c>
       <c r="C27" s="2" t="n">
-        <v>0.2927323446491656</v>
+        <v>195.2157185709887</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.3228921103619348</v>
+        <v>187.1339828985281</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.3530518760747041</v>
+        <v>179.0522472260675</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.3832116417874732</v>
+        <v>170.9705115536069</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.4133714075002424</v>
+        <v>162.8887758811462</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>0.4435311732130116</v>
+        <v>154.8070402086856</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0.4736909389257808</v>
+        <v>146.7253045362249</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5038507046385501</v>
+        <v>138.6435688637643</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.5340104703513192</v>
+        <v>130.5618331913037</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0.5641702360640884</v>
+        <v>122.480097518843</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0.5943300017768577</v>
+        <v>114.3983618463824</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.6244897674896268</v>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
+        <v>106.3166261739218</v>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>D_вт2_i</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="inlineStr"/>
+          <t>c_a3_к_i</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>Осевая скорость (периферия), выход из ступени</t>
+        </is>
+      </c>
       <c r="C28" s="2" t="n">
-        <v>0.3182543071245426</v>
+        <v>191.1748507347584</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.45428488179525</v>
+        <v>183.0931150622978</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.4881355571750841</v>
+        <v>175.0113793898372</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.5090802592766979</v>
+        <v>166.9296437173765</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.526072141372143</v>
+        <v>158.8479080449159</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>0.5414707355928511</v>
+        <v>150.7661723724553</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0.5561638172825492</v>
+        <v>142.6844366999946</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.5704763771156854</v>
+        <v>134.602701027534</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.5845528293222505</v>
+        <v>126.5209653550734</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0.598443620073721</v>
+        <v>118.4392296826127</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>0.6121395526158354</v>
+        <v>110.3574940101521</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.6255821807307252</v>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
+        <v>102.2757583376915</v>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>c_1u_к_i</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>Окружная составляющая абсолютной скорости (периферия), вход</t>
-        </is>
-      </c>
+          <t>c_1_к_i</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr"/>
       <c r="C29" s="2" t="n">
-        <v>63.1329097750037</v>
+        <v>201.2166170115306</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>62.77183610591472</v>
+        <v>193.5970760059433</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>62.90261564382815</v>
+        <v>186.1710650679843</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>63.4876566949365</v>
+        <v>178.9609318940849</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>64.50976044591263</v>
+        <v>172.0001552844106</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>65.96510841054763</v>
+        <v>165.3371390674029</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>67.86700835570147</v>
+        <v>159.040021432826</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>70.24870063537821</v>
+        <v>153.1987981465552</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>73.15725958263666</v>
+        <v>147.9319255448388</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>76.65702786453478</v>
+        <v>143.3930890007342</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>80.83147187427544</v>
+        <v>139.773928026296</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>85.77863645278707</v>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
+        <v>136.7168669781482</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>c_2u_к_i</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>Окружная составляющая абсолютной скорости (периферия), выход из РК</t>
-        </is>
-      </c>
+          <t>α_1_к_i</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr"/>
       <c r="C30" s="2" t="n">
-        <v>118.4818050203147</v>
+        <v>1.263960413517295</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>124.9834481607296</v>
+        <v>1.253539469396991</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>131.5948975476958</v>
+        <v>1.239874358014764</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>138.3537448750209</v>
+        <v>1.22279688589888</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>145.2771889560321</v>
+        <v>1.202026324602637</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>152.3690482769383</v>
+        <v>1.177194043197224</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>159.6160150708794</v>
+        <v>1.147819786142874</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>166.9848489838514</v>
+        <v>1.113298604686115</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>174.4284756827955</v>
+        <v>1.072953245860255</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>181.8825525006537</v>
+        <v>1.026061588748283</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>189.2636130442233</v>
+        <v>0.9719311589381017</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>196.4736124725757</v>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
+        <v>0.9100635927466534</v>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>c_3u_к_i</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>Окружная составляющая абсолютной скорости (периферия), выход из ступени</t>
-        </is>
-      </c>
+          <t>α_2_к_i</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr"/>
       <c r="C31" s="2" t="n">
-        <v>62.77183610591472</v>
+        <v>1.025298576923191</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>62.90261564382815</v>
+        <v>0.9819527018938013</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>63.4876566949365</v>
+        <v>0.9369953752985757</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>64.50976044591263</v>
+        <v>0.8904551733163805</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>65.96510841054763</v>
+        <v>0.8424857485472055</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>67.86700835570147</v>
+        <v>0.7933347861790676</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>70.24870063537821</v>
+        <v>0.7433434051954089</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>73.15725958263666</v>
+        <v>0.6929314331016215</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>76.65702786453478</v>
+        <v>0.6425482039479457</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>80.83147187427544</v>
+        <v>0.5926511294523578</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>85.77863645278707</v>
+        <v>0.5436772842140083</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>90.7258010312987</v>
+        <v>0.4960032468828308</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>c_a1_к_i</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>Осевая скорость (периферия), вход</t>
-        </is>
-      </c>
+          <t>α_3_к_i</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr"/>
       <c r="C32" s="2" t="n">
-        <v>199.2565864072191</v>
+        <v>1.253539469396991</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>191.1748507347584</v>
+        <v>1.239874358014764</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>183.0931150622978</v>
+        <v>1.22279688589888</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>175.0113793898372</v>
+        <v>1.202026324602637</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>166.9296437173765</v>
+        <v>1.177194043197224</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>158.8479080449159</v>
+        <v>1.147819786142874</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>150.7661723724553</v>
+        <v>1.113298604686115</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>142.6844366999946</v>
+        <v>1.072953245860255</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>134.602701027534</v>
+        <v>1.026061588748283</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>126.5209653550734</v>
+        <v>0.9719311589381017</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>118.4392296826127</v>
+        <v>0.9100635927466534</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>110.3574940101521</v>
+        <v>0.8451707320323852</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>c_a2_к_i</t>
-        </is>
-      </c>
-      <c r="B33" s="1" t="inlineStr">
-        <is>
-          <t>Осевая скорость (периферия), выход из РК</t>
-        </is>
-      </c>
+          <t>β_1_к_i</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr"/>
       <c r="C33" s="2" t="n">
-        <v>195.2157185709887</v>
+        <v>0.6859713621172263</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>187.1339828985281</v>
+        <v>0.6650452676615818</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>179.0522472260675</v>
+        <v>0.6444424815372659</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>170.9705115536069</v>
+        <v>0.6240433857254404</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>162.8887758811462</v>
+        <v>0.6037670001509156</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>154.8070402086856</v>
+        <v>0.5835548339830264</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>146.7253045362249</v>
+        <v>0.5633758820902205</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>138.6435688637643</v>
+        <v>0.5432292808163677</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>130.5618331913037</v>
+        <v>0.523129964929599</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>122.480097518843</v>
+        <v>0.5031123582188483</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>114.3983618463824</v>
+        <v>0.4832307453184389</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>106.3166261739218</v>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
+        <v>0.4635480071574731</v>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>c_a3_к_i</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>Осевая скорость (периферия), выход из ступени</t>
-        </is>
-      </c>
+          <t>β_2_к_i</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr"/>
       <c r="C34" s="2" t="n">
-        <v>191.1748507347584</v>
+        <v>0.8040478542246802</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>183.0931150622978</v>
+        <v>0.8005010283847622</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>175.0113793898372</v>
+        <v>0.7969752774493983</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>166.9296437173765</v>
+        <v>0.7935817820982608</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>158.8479080449159</v>
+        <v>0.7903875391334443</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>150.7661723724553</v>
+        <v>0.7874289737237021</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>142.6844366999946</v>
+        <v>0.7846923256098197</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>134.602701027534</v>
+        <v>0.7820906541333305</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>126.5209653550734</v>
+        <v>0.7794660188101106</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>118.4392296826127</v>
+        <v>0.7765536495460788</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>110.3574940101521</v>
+        <v>0.7729394765230466</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>102.2757583376915</v>
+        <v>0.7680316027741193</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>c_1_к_i</t>
+          <t>ε_к_рк_i</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr"/>
       <c r="C35" s="2" t="n">
-        <v>201.2166170115306</v>
+        <v>0.1180764921074539</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>193.5970760059433</v>
+        <v>0.1354557607231804</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>186.1710650679843</v>
+        <v>0.1525327959121324</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>178.9609318940849</v>
+        <v>0.1695383963728204</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>172.0001552844106</v>
+        <v>0.1866205389825287</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>165.3371390674029</v>
+        <v>0.2038741397406757</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>159.040021432826</v>
+        <v>0.2213164435195992</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>153.1987981465552</v>
+        <v>0.2388613733169628</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>147.9319255448388</v>
+        <v>0.2563360538805116</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>143.3930890007342</v>
+        <v>0.2734412913272305</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>139.773928026296</v>
+        <v>0.2897087312046077</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>136.7168669781482</v>
+        <v>0.3044835956166462</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>α_1_к_i</t>
+          <t>ε_к_на_i</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr"/>
       <c r="C36" s="2" t="n">
-        <v>1.263960413517295</v>
+        <v>0.2282408924738002</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1.253539469396991</v>
+        <v>0.2579216561209626</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1.239874358014764</v>
+        <v>0.2858015106003043</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>1.22279688589888</v>
+        <v>0.3115711512862566</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>1.202026324602637</v>
+        <v>0.3347082946500182</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>1.177194043197224</v>
+        <v>0.3544849999638067</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1.147819786142874</v>
+        <v>0.3699551994907062</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.113298604686115</v>
+        <v>0.3800218127586333</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1.072953245860255</v>
+        <v>0.383513384800337</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1.026061588748283</v>
+        <v>0.3792800294857439</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.9719311589381017</v>
+        <v>0.3663863085326451</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.9100635927466534</v>
+        <v>0.3491674851495545</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>α_2_к_i</t>
+          <t>W_1к_i</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr"/>
       <c r="C37" s="2" t="n">
-        <v>1.025298576923191</v>
+        <v>314.5701555829461</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.9819527018938013</v>
+        <v>309.7982108942016</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.9369953752985757</v>
+        <v>304.772787142599</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0.8904551733163805</v>
+        <v>299.5122741880747</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.8424857485472055</v>
+        <v>294.0209229436405</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>0.7933347861790676</v>
+        <v>288.293377752659</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0.7433434051954089</v>
+        <v>282.3107123067431</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.6929314331016215</v>
+        <v>276.0371139971909</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.6425482039479457</v>
+        <v>269.4242051591646</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0.5926511294523578</v>
+        <v>262.4074828809398</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>0.5436772842140083</v>
+        <v>254.9040418704614</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.4960032468828308</v>
+        <v>246.8160263197884</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>α_3_к_i</t>
+          <t>W_1вт_i</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr"/>
       <c r="C38" s="2" t="n">
-        <v>1.253539469396991</v>
+        <v>210.7618081429513</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1.239874358014764</v>
+        <v>208.2659101445495</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1.22279688589888</v>
+        <v>206.7691165118553</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>1.202026324602637</v>
+        <v>206.2168293707466</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1.177194043197224</v>
+        <v>206.5410165021746</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>1.147819786142874</v>
+        <v>207.660751601391</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1.113298604686115</v>
+        <v>209.4788267411302</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.072953245860255</v>
+        <v>211.8788787036171</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1.026061588748283</v>
+        <v>214.7296805683502</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0.9719311589381017</v>
+        <v>217.8837766117229</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>0.9100635927466534</v>
+        <v>221.1769059517512</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.8451707320323852</v>
+        <v>224.4327929220609</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>β_1_к_i</t>
+          <t>W_2к_i</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr"/>
       <c r="C39" s="2" t="n">
-        <v>0.6859713621172263</v>
+        <v>271.0687995179351</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.6650452676615818</v>
+        <v>260.7393907922885</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.6444424815372659</v>
+        <v>250.3367797675996</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0.6240433857254404</v>
+        <v>239.8341578092439</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.6037670001509156</v>
+        <v>229.2187155215777</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>0.5835548339830264</v>
+        <v>218.4869610830073</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0.5633758820902205</v>
+        <v>207.6475328071683</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.5432292808163677</v>
+        <v>196.7233545925395</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.523129964929599</v>
+        <v>185.7474577896496</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0.5031123582188483</v>
+        <v>174.7655466880916</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>0.4832307453184389</v>
+        <v>163.8375782957042</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.4635480071574731</v>
+        <v>153.0350504404822</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>β_2_к_i</t>
+          <t>W_2вт_i</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr"/>
       <c r="C40" s="2" t="n">
-        <v>0.8040478542246802</v>
+        <v>196.788038117527</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.8005010283847622</v>
+        <v>203.3516736968311</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.7969752774493983</v>
+        <v>199.6014152632706</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>0.7935817820982608</v>
+        <v>193.6247631348237</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.7903875391334443</v>
+        <v>186.8829196883579</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>0.7874289737237021</v>
+        <v>179.8020501672326</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0.7846923256098197</v>
+        <v>172.5598555050506</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.7820906541333305</v>
+        <v>165.2381621177473</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.7794660188101106</v>
+        <v>157.8940707203957</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0.7765536495460788</v>
+        <v>150.5789179883501</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>0.7729394765230466</v>
+        <v>143.3472835541374</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.7680316027741193</v>
+        <v>136.2577142571018</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>ε_к_рк_i</t>
+          <t>a_1к_i</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr"/>
       <c r="C41" s="2" t="n">
-        <v>0.1180764921074539</v>
+        <v>326.4880494232335</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.1354557607231804</v>
+        <v>349.1284711068405</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.1525327959121324</v>
+        <v>370.331957905283</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>0.1695383963728204</v>
+        <v>390.2973869534582</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.1866205389825287</v>
+        <v>409.2589650277441</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>0.2038741397406757</v>
+        <v>427.3266475274125</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0.2213164435195992</v>
+        <v>444.6227227940063</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.2388613733169628</v>
+        <v>461.2220150851436</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.2563360538805116</v>
+        <v>477.2047767231235</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0.2734412913272305</v>
+        <v>492.6119039013639</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>0.2897087312046077</v>
+        <v>507.5038920028636</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.3044835956166462</v>
+        <v>521.9227459001808</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>ε_к_на_i</t>
+          <t>M_w1к_i</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr"/>
       <c r="C42" s="2" t="n">
-        <v>0.2282408924738002</v>
+        <v>0.9634966919575119</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.2579216561209626</v>
+        <v>0.8873473134747493</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.2858015106003043</v>
+        <v>0.8229718787071257</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0.3115711512862566</v>
+        <v>0.76739502799641</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.3347082946500182</v>
+        <v>0.7184226811591251</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>0.3544849999638067</v>
+        <v>0.6746440443645988</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0.3699551994907062</v>
+        <v>0.6349444097969273</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.3800218127586333</v>
+        <v>0.5984907592631572</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.383513384800337</v>
+        <v>0.5645882403132058</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0.3792800294857439</v>
+        <v>0.5326860370257758</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>0.3663863085326451</v>
+        <v>0.5022701222339061</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.3491674851495545</v>
+        <v>0.4728976237548241</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>W_1к_i</t>
+          <t>λ_w1к_i</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr"/>
       <c r="C43" s="2" t="n">
-        <v>314.5701555829461</v>
+        <v>1.012297336253858</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>309.7982108942016</v>
+        <v>0.9399201865719472</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>304.772787142599</v>
+        <v>0.8773632375438932</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>299.5122741880747</v>
+        <v>0.8220791145701367</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>294.0209229436405</v>
+        <v>0.772832761388191</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>288.293377752659</v>
+        <v>0.7282327043295886</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>282.3107123067431</v>
+        <v>0.6874669334561038</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>276.0371139971909</v>
+        <v>0.649686279485034</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>269.4242051591646</v>
+        <v>0.6143557878289457</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>262.4074828809398</v>
+        <v>0.5807653273996938</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>254.9040418704614</v>
+        <v>0.5485417119379508</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>246.8160263197884</v>
+        <v>0.5172591822396891</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>W_1вт_i</t>
+          <t>λ_w1_i</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr"/>
       <c r="C44" s="2" t="n">
-        <v>210.7618081429513</v>
+        <v>0.8102668014124158</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>208.2659101445495</v>
+        <v>0.7557708555521092</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>206.7691165118553</v>
+        <v>0.7099294706681303</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>206.2168293707466</v>
+        <v>0.6706389262199457</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>206.5410165021746</v>
+        <v>0.6368645265581221</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>207.660751601391</v>
+        <v>0.6074478490009285</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>209.4788267411302</v>
+        <v>0.5817024223816692</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>211.8788787036171</v>
+        <v>0.5589037376408996</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>214.7296805683502</v>
+        <v>0.5385892027183966</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>217.8837766117229</v>
+        <v>0.5201384789422266</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>221.1769059517512</v>
+        <v>0.5032219799449003</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>224.4327929220609</v>
+        <v>0.4874696705720056</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>W_2к_i</t>
+          <t>λ_w1вт_i</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr"/>
       <c r="C45" s="2" t="n">
-        <v>271.0687995179351</v>
+        <v>0.6782385842413425</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>260.7393907922885</v>
+        <v>0.6318736720738927</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>250.3367797675996</v>
+        <v>0.5952356284422855</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>239.8341578092439</v>
+        <v>0.5660086851469479</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>229.2187155215777</v>
+        <v>0.5428921946275799</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>218.4869610830073</v>
+        <v>0.5245536748039339</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>207.6475328071683</v>
+        <v>0.5101108826760857</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>196.7233545925395</v>
+        <v>0.4986822185360721</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>185.7474577896496</v>
+        <v>0.4896383455892302</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>174.7655466880916</v>
+        <v>0.4822245976743076</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>163.8375782957042</v>
+        <v>0.4759624749048438</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>153.0350504404822</v>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>W_2вт_i</t>
-        </is>
-      </c>
-      <c r="B46" s="1" t="inlineStr"/>
-      <c r="C46" s="2" t="n">
-        <v>196.788038117527</v>
-      </c>
-      <c r="D46" s="2" t="n">
-        <v>203.3516736968311</v>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>199.6014152632706</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>193.6247631348237</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>186.8829196883579</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>179.8020501672326</v>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>172.5598555050506</v>
-      </c>
-      <c r="J46" s="2" t="n">
-        <v>165.2381621177473</v>
-      </c>
-      <c r="K46" s="2" t="n">
-        <v>157.8940707203957</v>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>150.5789179883501</v>
-      </c>
-      <c r="M46" s="2" t="n">
-        <v>143.3472835541374</v>
-      </c>
-      <c r="N46" s="2" t="n">
-        <v>136.2577142571018</v>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>a_1к_i</t>
-        </is>
-      </c>
-      <c r="B47" s="1" t="inlineStr"/>
-      <c r="C47" s="2" t="n">
-        <v>326.4880494232335</v>
-      </c>
-      <c r="D47" s="2" t="n">
-        <v>349.1284711068405</v>
-      </c>
-      <c r="E47" s="2" t="n">
-        <v>370.331957905283</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>390.2973869534582</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>409.2589650277441</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>427.3266475274125</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>444.6227227940063</v>
-      </c>
-      <c r="J47" s="2" t="n">
-        <v>461.2220150851436</v>
-      </c>
-      <c r="K47" s="2" t="n">
-        <v>477.2047767231235</v>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>492.6119039013639</v>
-      </c>
-      <c r="M47" s="2" t="n">
-        <v>507.5038920028636</v>
-      </c>
-      <c r="N47" s="2" t="n">
-        <v>521.9227459001808</v>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>M_w1к_i</t>
-        </is>
-      </c>
-      <c r="B48" s="1" t="inlineStr"/>
-      <c r="C48" s="2" t="n">
-        <v>0.9634966919575119</v>
-      </c>
-      <c r="D48" s="2" t="n">
-        <v>0.8873473134747493</v>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>0.8229718787071257</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>0.76739502799641</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>0.7184226811591251</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>0.6746440443645988</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>0.6349444097969273</v>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>0.5984907592631572</v>
-      </c>
-      <c r="K48" s="2" t="n">
-        <v>0.5645882403132058</v>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0.5326860370257758</v>
-      </c>
-      <c r="M48" s="2" t="n">
-        <v>0.5022701222339061</v>
-      </c>
-      <c r="N48" s="2" t="n">
-        <v>0.4728976237548241</v>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>λ_w1к_i</t>
-        </is>
-      </c>
-      <c r="B49" s="1" t="inlineStr"/>
-      <c r="C49" s="2" t="n">
-        <v>1.012297336253858</v>
-      </c>
-      <c r="D49" s="2" t="n">
-        <v>0.9399201865719472</v>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>0.8773632375438932</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>0.8220791145701367</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>0.772832761388191</v>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>0.7282327043295886</v>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>0.6874669334561038</v>
-      </c>
-      <c r="J49" s="2" t="n">
-        <v>0.649686279485034</v>
-      </c>
-      <c r="K49" s="2" t="n">
-        <v>0.6143557878289457</v>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0.5807653273996938</v>
-      </c>
-      <c r="M49" s="2" t="n">
-        <v>0.5485417119379508</v>
-      </c>
-      <c r="N49" s="2" t="n">
-        <v>0.5172591822396891</v>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>λ_w1_i</t>
-        </is>
-      </c>
-      <c r="B50" s="1" t="inlineStr"/>
-      <c r="C50" s="2" t="n">
-        <v>0.8102668014124158</v>
-      </c>
-      <c r="D50" s="2" t="n">
-        <v>0.7557708555521092</v>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>0.7099294706681303</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>0.6706389262199457</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>0.6368645265581221</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>0.6074478490009285</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>0.5817024223816692</v>
-      </c>
-      <c r="J50" s="2" t="n">
-        <v>0.5589037376408996</v>
-      </c>
-      <c r="K50" s="2" t="n">
-        <v>0.5385892027183966</v>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>0.5201384789422266</v>
-      </c>
-      <c r="M50" s="2" t="n">
-        <v>0.5032219799449003</v>
-      </c>
-      <c r="N50" s="2" t="n">
-        <v>0.4874696705720056</v>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>λ_w1вт_i</t>
-        </is>
-      </c>
-      <c r="B51" s="1" t="inlineStr"/>
-      <c r="C51" s="2" t="n">
-        <v>0.6782385842413425</v>
-      </c>
-      <c r="D51" s="2" t="n">
-        <v>0.6318736720738927</v>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>0.5952356284422855</v>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>0.5660086851469479</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>0.5428921946275799</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>0.5245536748039339</v>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>0.5101108826760857</v>
-      </c>
-      <c r="J51" s="2" t="n">
-        <v>0.4986822185360721</v>
-      </c>
-      <c r="K51" s="2" t="n">
-        <v>0.4896383455892302</v>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0.4822245976743076</v>
-      </c>
-      <c r="M51" s="2" t="n">
-        <v>0.4759624749048438</v>
-      </c>
-      <c r="N51" s="2" t="n">
         <v>0.4703500200761771</v>
       </c>
     </row>

--- a/results/Расчет_ступеней_по_высоте_лопаток.xlsx
+++ b/results/Расчет_ступеней_по_высоте_лопаток.xlsx
@@ -758,7 +758,11 @@
           <t>U_1_ср_i</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr"/>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Окружная скорость в среднем сечении на входе</t>
+        </is>
+      </c>
       <c r="C7" s="2" t="n">
         <v>235.9528248528826</v>
       </c>
@@ -802,7 +806,11 @@
           <t>U_k2_i</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr"/>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>Окружная скорость концов лопаток на выходе</t>
+        </is>
+      </c>
       <c r="C8" s="2" t="n">
         <v>306.5485944726447</v>
       </c>
@@ -840,13 +848,17 @@
         <v>306.5485944726447</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
           <t>U_2_ср_i</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr"/>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>Окружная скорость в среднем сечении на выходе</t>
+        </is>
+      </c>
       <c r="C9" s="2" t="n">
         <v>239.2794511089628</v>
       </c>
@@ -1034,7 +1046,11 @@
           <t>c_1_вт_i</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr"/>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>Абсолютная скорость (втулка) на входе</t>
+        </is>
+      </c>
       <c r="C13" s="2" t="n">
         <v>201.2166170115306</v>
       </c>
@@ -1078,7 +1094,11 @@
           <t>α_1_вт_i</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr"/>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>Угол абсолютной скорости (втулка) на входе</t>
+        </is>
+      </c>
       <c r="C14" s="2" t="n">
         <v>1.263960413517295</v>
       </c>
@@ -1116,13 +1136,17 @@
         <v>0.9100635927466534</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
           <t>α_2_вт_i</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr"/>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>Угол абсолютной скорости (втулка) на выходе из РК</t>
+        </is>
+      </c>
       <c r="C15" s="2" t="n">
         <v>1.025298576923191</v>
       </c>
@@ -1160,13 +1184,17 @@
         <v>0.4960032468828308</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
           <t>α_3_вт_i</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr"/>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>Угол абсолютной скорости (втулка) на выходе из ступени</t>
+        </is>
+      </c>
       <c r="C16" s="2" t="n">
         <v>1.253539469396991</v>
       </c>
@@ -1204,13 +1232,17 @@
         <v>0.8451707320323851</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
           <t>β_1_вт_i</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr"/>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>Угол относительной скорости (втулка) на входе в РК</t>
+        </is>
+      </c>
       <c r="C17" s="2" t="n">
         <v>1.238854298178526</v>
       </c>
@@ -1248,13 +1280,17 @@
         <v>0.5140608900158519</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="1" t="inlineStr">
         <is>
           <t>β_2_вт_i</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr"/>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>Угол относительной скорости (втулка) на выходе из РК</t>
+        </is>
+      </c>
       <c r="C18" s="2" t="n">
         <v>1.444300660871426</v>
       </c>
@@ -1298,7 +1334,11 @@
           <t>ε_вт_рк_i</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr"/>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>Диффузность решетки РК во втулочном сечении</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="n">
         <v>0.2054463626929006</v>
       </c>
@@ -1342,7 +1382,11 @@
           <t>ε_вт_на_i</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr"/>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>Диффузность решетки НА во втулочном сечении</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="n">
         <v>0.2282408924738</v>
       </c>
@@ -1770,7 +1814,11 @@
           <t>c_1_к_i</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr"/>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>Абсолютная скорость (периферия) на входе</t>
+        </is>
+      </c>
       <c r="C29" s="2" t="n">
         <v>201.2166170115306</v>
       </c>
@@ -1808,13 +1856,17 @@
         <v>136.7168669781482</v>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
         <is>
           <t>α_1_к_i</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr"/>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>Угол абсолютной скорости (периферия) на входе</t>
+        </is>
+      </c>
       <c r="C30" s="2" t="n">
         <v>1.263960413517295</v>
       </c>
@@ -1852,13 +1904,17 @@
         <v>0.9100635927466534</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
+    <row r="31" ht="30" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
         <is>
           <t>α_2_к_i</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr"/>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>Угол абсолютной скорости (периферия) на выходе из РК</t>
+        </is>
+      </c>
       <c r="C31" s="2" t="n">
         <v>1.025298576923191</v>
       </c>
@@ -1896,13 +1952,17 @@
         <v>0.4960032468828308</v>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
+    <row r="32" ht="30" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
           <t>α_3_к_i</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr"/>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>Угол абсолютной скорости (периферия) на выходе из ступени</t>
+        </is>
+      </c>
       <c r="C32" s="2" t="n">
         <v>1.253539469396991</v>
       </c>
@@ -1940,13 +2000,17 @@
         <v>0.8451707320323852</v>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
+    <row r="33" ht="30" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
         <is>
           <t>β_1_к_i</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr"/>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>Угол относительной скорости (периферия) на входе в РК</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="n">
         <v>0.6859713621172263</v>
       </c>
@@ -1984,13 +2048,17 @@
         <v>0.4635480071574731</v>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
+    <row r="34" ht="30" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
         <is>
           <t>β_2_к_i</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr"/>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>Угол относительной скорости (периферия) на выходе из РК</t>
+        </is>
+      </c>
       <c r="C34" s="2" t="n">
         <v>0.8040478542246802</v>
       </c>
@@ -2028,13 +2096,17 @@
         <v>0.7680316027741193</v>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1">
+    <row r="35" ht="30" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
         <is>
           <t>ε_к_рк_i</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr"/>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>Диффузность решетки РК в периферийном сечении</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="n">
         <v>0.1180764921074539</v>
       </c>
@@ -2072,13 +2144,17 @@
         <v>0.3044835956166462</v>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1">
+    <row r="36" ht="30" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
         <is>
           <t>ε_к_на_i</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr"/>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>Диффузность решетки НА в периферийном сечении</t>
+        </is>
+      </c>
       <c r="C36" s="2" t="n">
         <v>0.2282408924738002</v>
       </c>
@@ -2116,13 +2192,17 @@
         <v>0.3491674851495545</v>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1">
+    <row r="37" ht="30" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
         <is>
           <t>W_1к_i</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr"/>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>Относительная скорость на входе в РК (периферия)</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="n">
         <v>314.5701555829461</v>
       </c>
@@ -2160,13 +2240,17 @@
         <v>246.8160263197884</v>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1">
+    <row r="38" ht="30" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
         <is>
           <t>W_1вт_i</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr"/>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>Относительная скорость на входе в РК (втулка)</t>
+        </is>
+      </c>
       <c r="C38" s="2" t="n">
         <v>210.7618081429513</v>
       </c>
@@ -2204,13 +2288,17 @@
         <v>224.4327929220609</v>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1">
+    <row r="39" ht="30" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
         <is>
           <t>W_2к_i</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr"/>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>Относительная скорость на выходе из РК (периферия)</t>
+        </is>
+      </c>
       <c r="C39" s="2" t="n">
         <v>271.0687995179351</v>
       </c>
@@ -2248,13 +2336,17 @@
         <v>153.0350504404822</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1">
+    <row r="40" ht="30" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
         <is>
           <t>W_2вт_i</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr"/>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>Относительная скорость на выходе из РК (втулка)</t>
+        </is>
+      </c>
       <c r="C40" s="2" t="n">
         <v>196.788038117527</v>
       </c>
@@ -2298,7 +2390,11 @@
           <t>a_1к_i</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr"/>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>Скорость звука на входе в РК (периферия)</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="n">
         <v>326.4880494232335</v>
       </c>
@@ -2336,13 +2432,17 @@
         <v>521.9227459001808</v>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1">
+    <row r="42" ht="30" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
           <t>M_w1к_i</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr"/>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>Число Маха относительной скорости на входе (периферия)</t>
+        </is>
+      </c>
       <c r="C42" s="2" t="n">
         <v>0.9634966919575119</v>
       </c>
@@ -2380,13 +2480,17 @@
         <v>0.4728976237548241</v>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1">
+    <row r="43" ht="30" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
         <is>
           <t>λ_w1к_i</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr"/>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>Приведенная относительная скорость на входе (периферия)</t>
+        </is>
+      </c>
       <c r="C43" s="2" t="n">
         <v>1.012297336253858</v>
       </c>
@@ -2424,13 +2528,17 @@
         <v>0.5172591822396891</v>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1">
+    <row r="44" ht="30" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
         <is>
           <t>λ_w1_i</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr"/>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>Приведенная относительная скорость на входе (среднее сечение)</t>
+        </is>
+      </c>
       <c r="C44" s="2" t="n">
         <v>0.8102668014124158</v>
       </c>
@@ -2468,13 +2576,17 @@
         <v>0.4874696705720056</v>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1">
+    <row r="45" ht="30" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
         <is>
           <t>λ_w1вт_i</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr"/>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>Приведенная относительная скорость на входе (втулка)</t>
+        </is>
+      </c>
       <c r="C45" s="2" t="n">
         <v>0.6782385842413425</v>
       </c>

--- a/results/Расчет_ступеней_по_высоте_лопаток.xlsx
+++ b/results/Расчет_ступеней_по_высоте_лопаток.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:R45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -434,10 +434,14 @@
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -511,6 +515,26 @@
           <t>Ступень 12</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Ступень 13</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Ступень 14</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Ступень 15</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Ступень 16</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
@@ -527,36 +551,48 @@
         <v>131.8158956232372</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>145.3966857268395</v>
+        <v>141.7751416992122</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>158.9774758304418</v>
+        <v>151.7343877751872</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>172.558265934044</v>
+        <v>161.6936338511622</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>186.1390560376462</v>
+        <v>171.6528799271372</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>199.7198461412485</v>
+        <v>181.6121260031122</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>213.3006362448508</v>
+        <v>191.5713720790872</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>226.881426348453</v>
+        <v>201.5306181550621</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>240.4622164520553</v>
+        <v>211.4898642310372</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>254.0430065556575</v>
+        <v>221.4491103070121</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>267.6237966592598</v>
+        <v>231.4083563829871</v>
       </c>
       <c r="N2" s="2" t="n">
+        <v>241.3676024589621</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>251.3268485349371</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>261.2860946109121</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>271.2453406868871</v>
+      </c>
+      <c r="R2" s="2" t="n">
         <v>281.204586762862</v>
       </c>
     </row>
@@ -572,40 +608,52 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>143.3083063637941</v>
+        <v>144.0332759055259</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>204.5621867774973</v>
+        <v>197.8036664979193</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>219.804974854066</v>
+        <v>213.1325992693789</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>229.2362683771474</v>
+        <v>222.0504050553689</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>236.8876270249932</v>
+        <v>228.7765346710553</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>243.8215361937053</v>
+        <v>234.5333093752699</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>250.4377566346481</v>
+        <v>239.8159734209494</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>256.8826300063526</v>
+        <v>244.8242742734483</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>263.2211853068605</v>
+        <v>249.6740189293641</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>269.4761381922839</v>
+        <v>254.4288716763121</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>275.64334741065</v>
+        <v>259.117336740016</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>281.6964949253804</v>
+        <v>263.7562776533733</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>268.3530066207064</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>272.9054375058037</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>277.4066444356947</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>281.8433486403413</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -623,36 +671,48 @@
         <v>63.1329097750037</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>62.77183610591472</v>
+        <v>62.81821530502047</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>62.90261564382815</v>
+        <v>62.77443409039851</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>63.4876566949365</v>
+        <v>62.98333954659806</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>64.50976044591265</v>
+        <v>63.43519426679543</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>65.96510841054764</v>
+        <v>64.12150987078904</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>67.86700835570147</v>
+        <v>65.03884417986269</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>70.24870063537821</v>
+        <v>66.19190756681846</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>73.15725958263664</v>
+        <v>67.58700352770863</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>76.65702786453478</v>
+        <v>69.23643654055438</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>80.83147187427542</v>
+        <v>71.15652392075772</v>
       </c>
       <c r="N4" s="2" t="n">
+        <v>73.37117873692699</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>75.90643851400864</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>78.79356526134846</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>82.07065239128174</v>
+      </c>
+      <c r="R4" s="2" t="n">
         <v>85.77863645278707</v>
       </c>
     </row>
@@ -668,39 +728,51 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>118.4818050203146</v>
+        <v>118.4818050203147</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>124.9834481607296</v>
+        <v>123.2407548449228</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>131.5948975476958</v>
+        <v>128.0523504980807</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>138.3537448750209</v>
+        <v>132.9348185643283</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>145.2771889560321</v>
+        <v>137.8978964504892</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>152.3690482769383</v>
+        <v>142.9500725367651</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>159.6160150708794</v>
+        <v>148.094789001872</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>166.9848489838514</v>
+        <v>153.327335473008</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>174.4284756827955</v>
+        <v>158.6414084541208</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>181.8825525006537</v>
+        <v>164.0247034671892</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>189.2636130442233</v>
+        <v>169.4609031968111</v>
       </c>
       <c r="N5" s="2" t="n">
+        <v>174.9260945743784</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>180.3942400749443</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>185.8340776891632</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>191.2075140047</v>
+      </c>
+      <c r="R5" s="2" t="n">
         <v>196.4736124725757</v>
       </c>
     </row>
@@ -716,40 +788,52 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>62.77183610591472</v>
+        <v>62.81821530502047</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>62.90261564382815</v>
+        <v>62.77443409039851</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>63.4876566949365</v>
+        <v>62.98333954659806</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>64.50976044591265</v>
+        <v>63.43519426679543</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>65.96510841054764</v>
+        <v>64.12150987078904</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>67.86700835570147</v>
+        <v>65.03884417986269</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>70.24870063537821</v>
+        <v>66.19190756681846</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>73.15725958263664</v>
+        <v>67.58700352770863</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>76.65702786453478</v>
+        <v>69.23643654055438</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>80.83147187427542</v>
+        <v>71.15652392075772</v>
       </c>
       <c r="M6" s="2" t="n">
+        <v>73.37117873692699</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>75.90643851400864</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>78.79356526134846</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>82.07065239128174</v>
+      </c>
+      <c r="Q6" s="2" t="n">
         <v>85.77863645278707</v>
       </c>
-      <c r="N6" s="2" t="n">
-        <v>90.72580103129872</v>
+      <c r="R6" s="2" t="n">
+        <v>89.4866205142924</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -767,36 +851,48 @@
         <v>235.9528248528826</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>239.9085627833064</v>
+        <v>238.8223519448983</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>244.1780893063224</v>
+        <v>241.862941773502</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>248.7452471056666</v>
+        <v>245.0682272359553</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>253.5939559174666</v>
+        <v>248.4318336691518</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>258.7083857510594</v>
+        <v>251.9474201937026</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>264.073098019859</v>
+        <v>255.608715983452</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>269.6731562420169</v>
+        <v>259.4095515079538</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>275.4942089356771</v>
+        <v>263.3438849162977</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>281.5225479006893</v>
+        <v>267.4058238230061</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>287.7451453208818</v>
+        <v>271.5896428226135</v>
       </c>
       <c r="N7" s="2" t="n">
+        <v>275.8897971019783</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>280.3009325418462</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>284.8178927053008</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>289.4357231040248</v>
+      </c>
+      <c r="R7" s="2" t="n">
         <v>294.1496731169576</v>
       </c>
     </row>
@@ -847,6 +943,18 @@
       <c r="N8" s="2" t="n">
         <v>306.5485944726447</v>
       </c>
+      <c r="O8" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
@@ -860,40 +968,52 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>239.2794511089628</v>
+        <v>239.4969992935521</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>260.5932933062032</v>
+        <v>257.9712496124074</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>266.7267025850155</v>
+        <v>264.0052515050369</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>270.6670533262532</v>
+        <v>267.6550234522111</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>273.9414067010373</v>
+        <v>270.472497298016</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>276.9665884949052</v>
+        <v>272.9266513000059</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>279.9027605449339</v>
+        <v>275.2124105858886</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>282.8079970334419</v>
+        <v>277.4085128890916</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>285.7073967956575</v>
+        <v>279.5614033638178</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>288.6082377793303</v>
+        <v>281.6967265656767</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>291.5058281963692</v>
+        <v>283.8255053482622</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>294.3849147174485</v>
+        <v>285.9540301995386</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>288.0845161888494</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>290.2149363776683</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>292.3409714273949</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>294.4551866973605</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
@@ -911,36 +1031,48 @@
         <v>199.2565864072191</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>191.1748507347584</v>
+        <v>193.3299802474146</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>183.0931150622978</v>
+        <v>187.4033740876102</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>175.0113793898372</v>
+        <v>181.4767679278057</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>166.9296437173765</v>
+        <v>175.5501617680012</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>158.8479080449159</v>
+        <v>169.6235556081967</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>150.7661723724553</v>
+        <v>163.6969494483923</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>142.6844366999946</v>
+        <v>157.7703432885878</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>134.602701027534</v>
+        <v>151.8437371287833</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>126.5209653550734</v>
+        <v>145.9171309689789</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>118.4392296826127</v>
+        <v>139.9905248091744</v>
       </c>
       <c r="N10" s="2" t="n">
+        <v>134.06391864937</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>128.1373124895655</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>122.210706329761</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>116.2841001699566</v>
+      </c>
+      <c r="R10" s="2" t="n">
         <v>110.3574940101521</v>
       </c>
     </row>
@@ -956,40 +1088,52 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>195.2157185709887</v>
+        <v>196.2932833273169</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>187.1339828985281</v>
+        <v>190.3666771675124</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>179.0522472260675</v>
+        <v>184.4400710077079</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>170.9705115536069</v>
+        <v>178.5134648479034</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>162.8887758811462</v>
+        <v>172.5868586880989</v>
       </c>
       <c r="H11" s="2" t="n">
+        <v>166.6602525282945</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>160.73364636849</v>
+      </c>
+      <c r="J11" s="2" t="n">
         <v>154.8070402086856</v>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>146.7253045362249</v>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>138.6435688637643</v>
-      </c>
       <c r="K11" s="2" t="n">
-        <v>130.5618331913037</v>
+        <v>148.8804340488811</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>122.480097518843</v>
+        <v>142.9538278890766</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>114.3983618463824</v>
+        <v>137.0272217292722</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>106.3166261739218</v>
+        <v>131.1006155694677</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>125.1740094096633</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>119.2474032498588</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>113.3207970900543</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>107.3941909302498</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
@@ -1004,40 +1148,52 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>191.1748507347584</v>
+        <v>193.3299802474146</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>183.0931150622978</v>
+        <v>187.4033740876102</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>175.0113793898372</v>
+        <v>181.4767679278057</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>166.9296437173765</v>
+        <v>175.5501617680012</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>158.8479080449159</v>
+        <v>169.6235556081967</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>150.7661723724553</v>
+        <v>163.6969494483923</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>142.6844366999946</v>
+        <v>157.7703432885878</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>134.602701027534</v>
+        <v>151.8437371287833</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>126.5209653550734</v>
+        <v>145.9171309689789</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>118.4392296826127</v>
+        <v>139.9905248091744</v>
       </c>
       <c r="M12" s="2" t="n">
+        <v>134.06391864937</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>128.1373124895655</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>122.210706329761</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>116.2841001699566</v>
+      </c>
+      <c r="Q12" s="2" t="n">
         <v>110.3574940101521</v>
       </c>
-      <c r="N12" s="2" t="n">
-        <v>102.2757583376915</v>
+      <c r="R12" s="2" t="n">
+        <v>104.4308878503476</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
@@ -1052,40 +1208,52 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>201.2166170115306</v>
+        <v>203.2796336000575</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>193.5970760059433</v>
+        <v>197.6376841464971</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>186.1710650679843</v>
+        <v>192.0955969249808</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>178.9609318940849</v>
+        <v>186.6598059798559</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>172.0001552844106</v>
+        <v>181.3386849110711</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>165.3371390674029</v>
+        <v>176.1440958731287</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>159.040021432826</v>
+        <v>171.0931028672199</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>153.1987981465552</v>
+        <v>166.2062680860429</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>147.9319255448388</v>
+        <v>161.5100407251894</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>143.3930890007342</v>
+        <v>157.0369317480237</v>
       </c>
       <c r="M13" s="2" t="n">
+        <v>152.8282177900108</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>148.9327306535723</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>145.4093623815656</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>142.3291394489094</v>
+      </c>
+      <c r="Q13" s="2" t="n">
         <v>139.773928026296</v>
       </c>
-      <c r="N13" s="2" t="n">
-        <v>136.7168669781482</v>
+      <c r="R13" s="2" t="n">
+        <v>137.5269631318923</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
@@ -1103,36 +1271,48 @@
         <v>1.263960413517295</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1.253539469396991</v>
+        <v>1.256630058327822</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1.239874358014764</v>
+        <v>1.247573851996579</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1.22279688589888</v>
+        <v>1.23674299694349</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1.202026324602637</v>
+        <v>1.224045425357769</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1.177194043197223</v>
+        <v>1.209378485331547</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1.147819786142874</v>
+        <v>1.19260890515868</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.113298604686115</v>
+        <v>1.173554368824711</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1.072953245860255</v>
+        <v>1.152017253470188</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1.026061588748283</v>
+        <v>1.127762972610197</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>0.9719311589381018</v>
+        <v>1.100534531961805</v>
       </c>
       <c r="N14" s="2" t="n">
+        <v>1.070039917987022</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>1.035995965757883</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>0.998130982221335</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>0.956203642950578</v>
+      </c>
+      <c r="R14" s="2" t="n">
         <v>0.9100635927466534</v>
       </c>
     </row>
@@ -1148,40 +1328,52 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1.025298576923191</v>
+        <v>1.027737036196883</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.9819527018938013</v>
+        <v>0.9962607887002388</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.9369953752985757</v>
+        <v>0.9639221817078881</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.8904551733163805</v>
+        <v>0.9307108419430931</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.8424857485472056</v>
+        <v>0.8966619145806796</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.7933347861790676</v>
+        <v>0.8618296975047204</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.7433434051954089</v>
+        <v>0.8263005119355699</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.6929314331016215</v>
+        <v>0.7902002675388272</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.6425482039479457</v>
+        <v>0.7536680647298354</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0.5926511294523578</v>
+        <v>0.7168660817915981</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0.5436772842140083</v>
+        <v>0.6799669415261361</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.4960032468828308</v>
+        <v>0.643157266807891</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>0.6066144477575084</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>0.5705094165037157</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>0.5350040001465581</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>0.5002358174427599</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
@@ -1196,40 +1388,52 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1.253539469396991</v>
+        <v>1.256630058327822</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1.239874358014764</v>
+        <v>1.247573851996579</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1.22279688589888</v>
+        <v>1.23674299694349</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1.202026324602637</v>
+        <v>1.224045425357769</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1.177194043197223</v>
+        <v>1.209378485331547</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1.147819786142874</v>
+        <v>1.19260890515868</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1.113298604686115</v>
+        <v>1.173554368824711</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.072953245860255</v>
+        <v>1.152017253470188</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1.026061588748283</v>
+        <v>1.127762972610197</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0.9719311589381018</v>
+        <v>1.100534531961805</v>
       </c>
       <c r="M16" s="2" t="n">
+        <v>1.070039917987022</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>1.035995965757883</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0.998130982221335</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>0.956203642950578</v>
+      </c>
+      <c r="Q16" s="2" t="n">
         <v>0.9100635927466534</v>
       </c>
-      <c r="N16" s="2" t="n">
-        <v>0.8451707320323851</v>
+      <c r="R16" s="2" t="n">
+        <v>0.8623112159794667</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
@@ -1247,36 +1451,48 @@
         <v>1.238854298178526</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1.162847113736222</v>
+        <v>1.183065343615517</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1.087559254200616</v>
+        <v>1.127594655730443</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1.013477964061208</v>
+        <v>1.072626874380507</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.941115429938413</v>
+        <v>1.018369838213023</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.8709473701553111</v>
+        <v>0.9650168726546282</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0.8033994195460497</v>
+        <v>0.9127569192891843</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.7388314868921215</v>
+        <v>0.8617792674053384</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.6775001027724478</v>
+        <v>0.8122419851622158</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0.6195648937626838</v>
+        <v>0.764284516988142</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0.5650943056573683</v>
+        <v>0.7180171480059852</v>
       </c>
       <c r="N17" s="2" t="n">
+        <v>0.6735303223469826</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>0.6308767346766875</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>0.5900824873631386</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>0.5511521998126707</v>
+      </c>
+      <c r="R17" s="2" t="n">
         <v>0.5140608900158519</v>
       </c>
     </row>
@@ -1292,40 +1508,52 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1.444300660871426</v>
+        <v>1.441354280908203</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1.168713890096634</v>
+        <v>1.197482459133908</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1.113046042834421</v>
+        <v>1.138593898695273</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1.082214080284579</v>
+        <v>1.107781456925439</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1.058474483255031</v>
+        <v>1.086121274601831</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1.037204964518872</v>
+        <v>1.068321275422009</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1.016529278647963</v>
+        <v>1.052244235604623</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.9955401536080093</v>
+        <v>1.036992137278087</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.9735638239077175</v>
+        <v>1.022001837851195</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0.9499642765458586</v>
+        <v>1.006892515432078</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0.9240529437980581</v>
+        <v>0.9914066368294098</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.8950835428209692</v>
+        <v>0.9752814267898019</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>0.9582659803345102</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>0.9401050336607781</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>0.9205046743503615</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>0.89916093915558</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
@@ -1340,40 +1568,52 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.2054463626929006</v>
+        <v>0.202499982729677</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.005866776360412329</v>
+        <v>0.01441711551839076</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.02548678863380505</v>
+        <v>0.01099924296483001</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.06873611622337128</v>
+        <v>0.03515458254493242</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.117359053316618</v>
+        <v>0.06775143638880832</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.1662575943635612</v>
+        <v>0.1033044027673811</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0.2131298591019133</v>
+        <v>0.139487316315439</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.2567086667158878</v>
+        <v>0.1752128698727489</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.2960637211352697</v>
+        <v>0.209759852688979</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0.3303993827831748</v>
+        <v>0.242607998443936</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>0.3589586381406898</v>
+        <v>0.2733894888234246</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.3810226528051174</v>
+        <v>0.3017511044428193</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>0.3273892456578227</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>0.3500225462976395</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>0.3693524745376908</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>0.3851000491397282</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
@@ -1388,40 +1628,52 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.2282408924738</v>
+        <v>0.2288930221309395</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.2579216561209626</v>
+        <v>0.2513130632963398</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.2858015106003043</v>
+        <v>0.2728208152356019</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.3115711512862563</v>
+        <v>0.293334583414676</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.3347082946500178</v>
+        <v>0.3127165707508677</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.3544849999638067</v>
+        <v>0.3307792076539595</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.3699551994907062</v>
+        <v>0.3472538568891409</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.3800218127586336</v>
+        <v>0.3618169859313606</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.383513384800337</v>
+        <v>0.3740949078803616</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0.379280029485744</v>
+        <v>0.3836684501702067</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>0.3663863085326451</v>
+        <v>0.3900729764608858</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.3491674851495544</v>
+        <v>0.3928386989499922</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>0.3915165344638266</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>0.3856942264468624</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>0.3750595926000952</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>0.3620753985367068</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -1471,6 +1723,18 @@
       <c r="N21" s="2" t="n">
         <v>306.5485944726447</v>
       </c>
+      <c r="O21" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
@@ -1519,6 +1783,18 @@
       <c r="N22" s="2" t="n">
         <v>306.5485944726447</v>
       </c>
+      <c r="O22" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
@@ -1535,36 +1811,48 @@
         <v>63.1329097750037</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>62.77183610591472</v>
+        <v>62.81821530502046</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>62.90261564382815</v>
+        <v>62.7744340903985</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>63.4876566949365</v>
+        <v>62.98333954659807</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>64.50976044591263</v>
+        <v>63.43519426679543</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>65.96510841054763</v>
+        <v>64.12150987078903</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>67.86700835570147</v>
+        <v>65.03884417986271</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>70.24870063537821</v>
+        <v>66.19190756681846</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>73.15725958263666</v>
+        <v>67.58700352770862</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>76.65702786453478</v>
+        <v>69.23643654055438</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>80.83147187427544</v>
+        <v>71.15652392075773</v>
       </c>
       <c r="N23" s="2" t="n">
+        <v>73.37117873692701</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>75.90643851400864</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>78.79356526134846</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>82.07065239128175</v>
+      </c>
+      <c r="R23" s="2" t="n">
         <v>85.77863645278707</v>
       </c>
     </row>
@@ -1583,36 +1871,48 @@
         <v>118.4818050203147</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>124.9834481607296</v>
+        <v>123.2407548449227</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>131.5948975476958</v>
+        <v>128.0523504980807</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>138.3537448750209</v>
+        <v>132.9348185643283</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>145.2771889560321</v>
+        <v>137.8978964504892</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>152.3690482769383</v>
+        <v>142.950072536765</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>159.6160150708794</v>
+        <v>148.094789001872</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>166.9848489838514</v>
+        <v>153.3273354730081</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>174.4284756827955</v>
+        <v>158.6414084541208</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>181.8825525006537</v>
+        <v>164.0247034671892</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>189.2636130442233</v>
+        <v>169.4609031968112</v>
       </c>
       <c r="N24" s="2" t="n">
+        <v>174.9260945743783</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>180.3942400749443</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>185.8340776891633</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>191.2075140047</v>
+      </c>
+      <c r="R24" s="2" t="n">
         <v>196.4736124725757</v>
       </c>
     </row>
@@ -1628,40 +1928,52 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>62.77183610591472</v>
+        <v>62.81821530502046</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>62.90261564382815</v>
+        <v>62.7744340903985</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>63.4876566949365</v>
+        <v>62.98333954659807</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>64.50976044591263</v>
+        <v>63.43519426679543</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>65.96510841054763</v>
+        <v>64.12150987078903</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>67.86700835570147</v>
+        <v>65.03884417986271</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>70.24870063537821</v>
+        <v>66.19190756681846</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>73.15725958263666</v>
+        <v>67.58700352770862</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>76.65702786453478</v>
+        <v>69.23643654055438</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>80.83147187427544</v>
+        <v>71.15652392075773</v>
       </c>
       <c r="M25" s="2" t="n">
+        <v>73.37117873692701</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>75.90643851400864</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>78.79356526134846</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>82.07065239128175</v>
+      </c>
+      <c r="Q25" s="2" t="n">
         <v>85.77863645278707</v>
       </c>
-      <c r="N25" s="2" t="n">
-        <v>90.7258010312987</v>
+      <c r="R25" s="2" t="n">
+        <v>89.48662051429238</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
@@ -1679,36 +1991,48 @@
         <v>199.2565864072191</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>191.1748507347584</v>
+        <v>193.3299802474146</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>183.0931150622978</v>
+        <v>187.4033740876102</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>175.0113793898372</v>
+        <v>181.4767679278057</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>166.9296437173765</v>
+        <v>175.5501617680012</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>158.8479080449159</v>
+        <v>169.6235556081967</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>150.7661723724553</v>
+        <v>163.6969494483923</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>142.6844366999946</v>
+        <v>157.7703432885878</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>134.602701027534</v>
+        <v>151.8437371287833</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>126.5209653550734</v>
+        <v>145.9171309689789</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>118.4392296826127</v>
+        <v>139.9905248091744</v>
       </c>
       <c r="N26" s="2" t="n">
+        <v>134.06391864937</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>128.1373124895655</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>122.210706329761</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>116.2841001699566</v>
+      </c>
+      <c r="R26" s="2" t="n">
         <v>110.3574940101521</v>
       </c>
     </row>
@@ -1724,40 +2048,52 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>195.2157185709887</v>
+        <v>196.2932833273169</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>187.1339828985281</v>
+        <v>190.3666771675124</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>179.0522472260675</v>
+        <v>184.4400710077079</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>170.9705115536069</v>
+        <v>178.5134648479034</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>162.8887758811462</v>
+        <v>172.5868586880989</v>
       </c>
       <c r="H27" s="2" t="n">
+        <v>166.6602525282945</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>160.73364636849</v>
+      </c>
+      <c r="J27" s="2" t="n">
         <v>154.8070402086856</v>
       </c>
-      <c r="I27" s="2" t="n">
-        <v>146.7253045362249</v>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>138.6435688637643</v>
-      </c>
       <c r="K27" s="2" t="n">
-        <v>130.5618331913037</v>
+        <v>148.8804340488811</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>122.480097518843</v>
+        <v>142.9538278890766</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>114.3983618463824</v>
+        <v>137.0272217292722</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>106.3166261739218</v>
+        <v>131.1006155694677</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>125.1740094096633</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>119.2474032498588</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>113.3207970900543</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>107.3941909302498</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
@@ -1772,40 +2108,52 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>191.1748507347584</v>
+        <v>193.3299802474146</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>183.0931150622978</v>
+        <v>187.4033740876102</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>175.0113793898372</v>
+        <v>181.4767679278057</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>166.9296437173765</v>
+        <v>175.5501617680012</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>158.8479080449159</v>
+        <v>169.6235556081967</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>150.7661723724553</v>
+        <v>163.6969494483923</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>142.6844366999946</v>
+        <v>157.7703432885878</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>134.602701027534</v>
+        <v>151.8437371287833</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>126.5209653550734</v>
+        <v>145.9171309689789</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>118.4392296826127</v>
+        <v>139.9905248091744</v>
       </c>
       <c r="M28" s="2" t="n">
+        <v>134.06391864937</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>128.1373124895655</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>122.210706329761</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>116.2841001699566</v>
+      </c>
+      <c r="Q28" s="2" t="n">
         <v>110.3574940101521</v>
       </c>
-      <c r="N28" s="2" t="n">
-        <v>102.2757583376915</v>
+      <c r="R28" s="2" t="n">
+        <v>104.4308878503476</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
@@ -1820,40 +2168,52 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>201.2166170115306</v>
+        <v>203.2796336000575</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>193.5970760059433</v>
+        <v>197.6376841464971</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>186.1710650679843</v>
+        <v>192.0955969249808</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>178.9609318940849</v>
+        <v>186.6598059798559</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>172.0001552844106</v>
+        <v>181.3386849110711</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>165.3371390674029</v>
+        <v>176.1440958731287</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>159.040021432826</v>
+        <v>171.0931028672199</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>153.1987981465552</v>
+        <v>166.2062680860429</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>147.9319255448388</v>
+        <v>161.5100407251894</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>143.3930890007342</v>
+        <v>157.0369317480237</v>
       </c>
       <c r="M29" s="2" t="n">
+        <v>152.8282177900108</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>148.9327306535723</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>145.4093623815656</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>142.3291394489094</v>
+      </c>
+      <c r="Q29" s="2" t="n">
         <v>139.773928026296</v>
       </c>
-      <c r="N29" s="2" t="n">
-        <v>136.7168669781482</v>
+      <c r="R29" s="2" t="n">
+        <v>137.5269631318923</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
@@ -1871,36 +2231,48 @@
         <v>1.263960413517295</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1.253539469396991</v>
+        <v>1.256630058327822</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1.239874358014764</v>
+        <v>1.247573851996579</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1.22279688589888</v>
+        <v>1.23674299694349</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>1.202026324602637</v>
+        <v>1.224045425357769</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>1.177194043197224</v>
+        <v>1.209378485331547</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1.147819786142874</v>
+        <v>1.19260890515868</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.113298604686115</v>
+        <v>1.173554368824711</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1.072953245860255</v>
+        <v>1.152017253470188</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1.026061588748283</v>
+        <v>1.127762972610197</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>0.9719311589381017</v>
+        <v>1.100534531961805</v>
       </c>
       <c r="N30" s="2" t="n">
+        <v>1.070039917987022</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>1.035995965757883</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>0.998130982221335</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>0.9562036429505779</v>
+      </c>
+      <c r="R30" s="2" t="n">
         <v>0.9100635927466534</v>
       </c>
     </row>
@@ -1916,40 +2288,52 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>1.025298576923191</v>
+        <v>1.027737036196883</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.9819527018938013</v>
+        <v>0.9962607887002389</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.9369953752985757</v>
+        <v>0.9639221817078881</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.8904551733163805</v>
+        <v>0.9307108419430931</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.8424857485472055</v>
+        <v>0.8966619145806796</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0.7933347861790676</v>
+        <v>0.8618296975047204</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0.7433434051954089</v>
+        <v>0.8263005119355699</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.6929314331016215</v>
+        <v>0.7902002675388271</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.6425482039479457</v>
+        <v>0.7536680647298354</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0.5926511294523578</v>
+        <v>0.7168660817915981</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>0.5436772842140083</v>
+        <v>0.6799669415261361</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.4960032468828308</v>
+        <v>0.643157266807891</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>0.6066144477575085</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>0.5705094165037156</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>0.5350040001465581</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>0.5002358174427599</v>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
@@ -1964,40 +2348,52 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>1.253539469396991</v>
+        <v>1.256630058327822</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1.239874358014764</v>
+        <v>1.247573851996579</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1.22279688589888</v>
+        <v>1.23674299694349</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>1.202026324602637</v>
+        <v>1.224045425357769</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>1.177194043197224</v>
+        <v>1.209378485331547</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>1.147819786142874</v>
+        <v>1.19260890515868</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1.113298604686115</v>
+        <v>1.173554368824711</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.072953245860255</v>
+        <v>1.152017253470188</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1.026061588748283</v>
+        <v>1.127762972610197</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0.9719311589381017</v>
+        <v>1.100534531961805</v>
       </c>
       <c r="M32" s="2" t="n">
+        <v>1.070039917987022</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>1.035995965757883</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>0.998130982221335</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>0.9562036429505779</v>
+      </c>
+      <c r="Q32" s="2" t="n">
         <v>0.9100635927466534</v>
       </c>
-      <c r="N32" s="2" t="n">
-        <v>0.8451707320323852</v>
+      <c r="R32" s="2" t="n">
+        <v>0.8623112159794668</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
@@ -2015,36 +2411,48 @@
         <v>0.6859713621172263</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.6650452676615818</v>
+        <v>0.6705884899542028</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.6444424815372659</v>
+        <v>0.6553986380229417</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.6240433857254404</v>
+        <v>0.6403479484884566</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.6037670001509156</v>
+        <v>0.6253992375560833</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>0.5835548339830264</v>
+        <v>0.6105171847183516</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0.5633758820902205</v>
+        <v>0.5956753972960683</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.5432292808163677</v>
+        <v>0.5808618150235404</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.523129964929599</v>
+        <v>0.5660655201964543</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0.5031123582188483</v>
+        <v>0.5512847063075731</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>0.4832307453184389</v>
+        <v>0.536522304657185</v>
       </c>
       <c r="N33" s="2" t="n">
+        <v>0.5217920725601732</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>0.5071077195318678</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>0.4924881203936635</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>0.4779595934526376</v>
+      </c>
+      <c r="R33" s="2" t="n">
         <v>0.4635480071574731</v>
       </c>
     </row>
@@ -2060,40 +2468,52 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>0.8040478542246802</v>
+        <v>0.8067979877758287</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.8005010283847622</v>
+        <v>0.8042862538765255</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.7969752774493983</v>
+        <v>0.8017737518398845</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.7935817820982608</v>
+        <v>0.7993118065138726</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.7903875391334443</v>
+        <v>0.796932609201779</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>0.7874289737237021</v>
+        <v>0.7946685995501205</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0.7846923256098197</v>
+        <v>0.7925406814235351</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.7820906541333305</v>
+        <v>0.7905462851891686</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.7794660188101106</v>
+        <v>0.7886774259944044</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0.7765536495460788</v>
+        <v>0.7869041883167932</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>0.7729394765230466</v>
+        <v>0.7851775641424952</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.7680316027741193</v>
+        <v>0.7834117236377515</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>0.7814975291784722</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>0.7792842964411948</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>0.776563149738308</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>0.7730715643917837</v>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
@@ -2108,40 +2528,52 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>0.1180764921074539</v>
+        <v>0.1208266256586024</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.1354557607231804</v>
+        <v>0.1336977639223227</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.1525327959121324</v>
+        <v>0.1463751138169428</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.1695383963728204</v>
+        <v>0.158963858025416</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.1866205389825287</v>
+        <v>0.1715333716456957</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>0.2038741397406757</v>
+        <v>0.1841514148317689</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0.2213164435195992</v>
+        <v>0.1968652841274667</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.2388613733169628</v>
+        <v>0.2096844701656282</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.2563360538805116</v>
+        <v>0.2226119057979501</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0.2734412913272305</v>
+        <v>0.2356194820092201</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>0.2897087312046077</v>
+        <v>0.2486552594853102</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.3044835956166462</v>
+        <v>0.2616196510775782</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>0.2743898096466043</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>0.2867961760475313</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>0.2986035562856704</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>0.3095235572343106</v>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
@@ -2156,40 +2588,52 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>0.2282408924738002</v>
+        <v>0.2288930221309393</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.2579216561209626</v>
+        <v>0.2513130632963397</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.2858015106003043</v>
+        <v>0.2728208152356019</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.3115711512862566</v>
+        <v>0.293334583414676</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.3347082946500182</v>
+        <v>0.3127165707508679</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>0.3544849999638067</v>
+        <v>0.3307792076539593</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0.3699551994907062</v>
+        <v>0.3472538568891409</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.3800218127586333</v>
+        <v>0.3618169859313607</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.383513384800337</v>
+        <v>0.3740949078803616</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0.3792800294857439</v>
+        <v>0.3836684501702067</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.3663863085326451</v>
+        <v>0.3900729764608858</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.3491674851495545</v>
+        <v>0.3928386989499922</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>0.3915165344638265</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>0.3856942264468624</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>0.3750595926000952</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>0.3620753985367069</v>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
@@ -2207,36 +2651,48 @@
         <v>314.5701555829461</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>309.7982108942016</v>
+        <v>311.0964143021574</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>304.772787142599</v>
+        <v>307.4831148038699</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>299.5122741880747</v>
+        <v>303.7397746504608</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>294.0209229436405</v>
+        <v>299.8699462373995</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>288.293377752659</v>
+        <v>295.8767344110082</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>282.3107123067431</v>
+        <v>291.7595769553956</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>276.0371139971909</v>
+        <v>287.5114226630731</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>269.4242051591646</v>
+        <v>283.1239347921154</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>262.4074828809398</v>
+        <v>278.5836847566697</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>254.9040418704614</v>
+        <v>273.8736458935993</v>
       </c>
       <c r="N37" s="2" t="n">
+        <v>268.9699639231351</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>263.8464988535879</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>258.472068263976</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>252.808897061437</v>
+      </c>
+      <c r="R37" s="2" t="n">
         <v>246.8160263197884</v>
       </c>
     </row>
@@ -2255,36 +2711,48 @@
         <v>210.7618081429513</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>208.2659101445495</v>
+        <v>208.8316965598937</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>206.7691165118553</v>
+        <v>207.4461327164729</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>206.2168293707466</v>
+        <v>206.5854290583349</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>206.5410165021746</v>
+        <v>206.2254271093939</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>207.660751601391</v>
+        <v>206.339999748764</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>209.4788267411302</v>
+        <v>206.8989412135246</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>211.8788787036171</v>
+        <v>207.8654560168361</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>214.7296805683502</v>
+        <v>209.199794033925</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>217.8837766117229</v>
+        <v>210.8566033240416</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>221.1769059517512</v>
+        <v>212.7862703368112</v>
       </c>
       <c r="N38" s="2" t="n">
+        <v>214.9323909210021</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>217.2360262570626</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>219.6337406001647</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>222.0564222085818</v>
+      </c>
+      <c r="R38" s="2" t="n">
         <v>224.4327929220609</v>
       </c>
     </row>
@@ -2300,40 +2768,52 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>271.0687995179351</v>
+        <v>271.8458577472266</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>260.7393907922885</v>
+        <v>264.2749247370671</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>250.3367797675996</v>
+        <v>256.6691428792238</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>239.8341578092439</v>
+        <v>249.0156627948266</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>229.2187155215777</v>
+        <v>241.3074423534967</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>218.4869610830073</v>
+        <v>233.5382541520755</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>207.6475328071683</v>
+        <v>225.7053688840393</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>196.7233545925395</v>
+        <v>217.8117855112696</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>185.7474577896496</v>
+        <v>209.8616671012157</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>174.7655466880916</v>
+        <v>201.8634598323201</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>163.8375782957042</v>
+        <v>193.8285185265093</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>153.0350504404822</v>
+        <v>185.7736630477057</v>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>177.7173423309921</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>169.6818721729103</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>161.694674917383</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>153.7856102107036</v>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
@@ -2348,40 +2828,52 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>196.788038117527</v>
+        <v>197.9493135724802</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>203.3516736968311</v>
+        <v>204.4482809171367</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>199.6014152632706</v>
+        <v>203.117671619961</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>193.6247631348237</v>
+        <v>199.5210387093195</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>186.8829196883579</v>
+        <v>195.0516615582917</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>179.8020501672326</v>
+        <v>190.1660564943506</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>172.5598555050506</v>
+        <v>185.0623698814786</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>165.2381621177473</v>
+        <v>179.8246632362344</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>157.8940707203957</v>
+        <v>174.5059305941222</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>150.5789179883501</v>
+        <v>169.1410965369538</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>143.3472835541374</v>
+        <v>163.7520551642948</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>136.2577142571018</v>
+        <v>158.360894252783</v>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>152.9878336468045</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>147.6528526041854</v>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>142.3793985806406</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>137.1914869768414</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
@@ -2399,36 +2891,48 @@
         <v>326.4880494232335</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>349.1284711068405</v>
+        <v>343.2511704264326</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>370.331957905283</v>
+        <v>359.1728263886171</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>390.2973869534582</v>
+        <v>374.4043820758214</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>409.2589650277441</v>
+        <v>388.9997261794932</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>427.3266475274125</v>
+        <v>403.0379031394633</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>444.6227227940063</v>
+        <v>416.584207688006</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>461.2220150851436</v>
+        <v>429.6821761092369</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>477.2047767231235</v>
+        <v>442.3584482492194</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>492.6119039013639</v>
+        <v>454.6611295735622</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>507.5038920028636</v>
+        <v>466.6231066059428</v>
       </c>
       <c r="N41" s="2" t="n">
+        <v>478.2488618262352</v>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>489.5728862470405</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>500.6158448723494</v>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>511.3932185174863</v>
+      </c>
+      <c r="R41" s="2" t="n">
         <v>521.9227459001808</v>
       </c>
     </row>
@@ -2447,36 +2951,48 @@
         <v>0.9634966919575119</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.8873473134747493</v>
+        <v>0.9063229527103194</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.8229718787071257</v>
+        <v>0.856086797811313</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0.76739502799641</v>
+        <v>0.8112612704114927</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.7184226811591251</v>
+        <v>0.7708744404077876</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>0.6746440443645988</v>
+        <v>0.7341163997387758</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0.6349444097969273</v>
+        <v>0.7003615873357932</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.5984907592631572</v>
+        <v>0.6691257833091496</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.5645882403132058</v>
+        <v>0.6400328419467798</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0.5326860370257758</v>
+        <v>0.6127281762968393</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>0.5022701222339061</v>
+        <v>0.5869268838520723</v>
       </c>
       <c r="N42" s="2" t="n">
+        <v>0.5624058631233323</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>0.5389320084210095</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>0.5163082050067413</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>0.4943532450319197</v>
+      </c>
+      <c r="R42" s="2" t="n">
         <v>0.4728976237548241</v>
       </c>
     </row>
@@ -2495,36 +3011,48 @@
         <v>1.012297336253858</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.9399201865719472</v>
+        <v>0.9581961788137892</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.8773632375438932</v>
+        <v>0.9095745549609253</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.8220791145701367</v>
+        <v>0.8656953243460359</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.772832761388191</v>
+        <v>0.8255644869432375</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>0.7282327043295886</v>
+        <v>0.7886332120169451</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0.6874669334561038</v>
+        <v>0.7544739956090307</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.649686279485034</v>
+        <v>0.7226514090371025</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.6143557878289457</v>
+        <v>0.69271326391988</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0.5807653273996938</v>
+        <v>0.664482224583045</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>0.5485417119379508</v>
+        <v>0.6377420554852364</v>
       </c>
       <c r="N43" s="2" t="n">
+        <v>0.6120646462538168</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>0.5873562037492842</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>0.563440159915512</v>
+      </c>
+      <c r="Q43" s="2" t="n">
+        <v>0.5401203854543033</v>
+      </c>
+      <c r="R43" s="2" t="n">
         <v>0.5172591822396891</v>
       </c>
     </row>
@@ -2543,36 +3071,48 @@
         <v>0.8102668014124158</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.7557708555521092</v>
+        <v>0.7694023987739284</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.7099294706681303</v>
+        <v>0.7333605416173485</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0.6706389262199457</v>
+        <v>0.7015252700585143</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.6368645265581221</v>
+        <v>0.6730762014819419</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>0.6074478490009285</v>
+        <v>0.647556179476995</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0.5817024223816692</v>
+        <v>0.6246081969296378</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.5589037376408996</v>
+        <v>0.6038666837709337</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.5385892027183966</v>
+        <v>0.5849503864399258</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0.5201384789422266</v>
+        <v>0.5677054937628523</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.5032219799449003</v>
+        <v>0.5519470682297333</v>
       </c>
       <c r="N44" s="2" t="n">
+        <v>0.5373033600536083</v>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>0.5236900362851913</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>0.510952486515638</v>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>0.498918216718421</v>
+      </c>
+      <c r="R44" s="2" t="n">
         <v>0.4874696705720056</v>
       </c>
     </row>
@@ -2591,36 +3131,48 @@
         <v>0.6782385842413425</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.6318736720738927</v>
+        <v>0.643214529192673</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.5952356284422855</v>
+        <v>0.6136523105156737</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.5660086851469479</v>
+        <v>0.5887936152570951</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.5428921946275799</v>
+        <v>0.5677540916068736</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>0.5245536748039339</v>
+        <v>0.5499809814157157</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0.5101108826760857</v>
+        <v>0.5350291239574648</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.4986822185360721</v>
+        <v>0.5224636408854563</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.4896383455892302</v>
+        <v>0.5118446529185583</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0.4822245976743076</v>
+        <v>0.5029385154667761</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>0.4759624749048438</v>
+        <v>0.4954940187138565</v>
       </c>
       <c r="N45" s="2" t="n">
+        <v>0.4890974289424548</v>
+      </c>
+      <c r="O45" s="2" t="n">
+        <v>0.4835953035356831</v>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>0.4787769555053555</v>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>0.4744184312736267</v>
+      </c>
+      <c r="R45" s="2" t="n">
         <v>0.4703500200761771</v>
       </c>
     </row>

--- a/results/Расчет_ступеней_по_высоте_лопаток.xlsx
+++ b/results/Расчет_ступеней_по_высоте_лопаток.xlsx
@@ -421,27 +421,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R45"/>
+  <dimension ref="A1:Q45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="21" customWidth="1" min="15" max="15"/>
     <col width="21" customWidth="1" min="16" max="16"/>
     <col width="21" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -530,11 +529,6 @@
           <t>Ступень 15</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Ступень 16</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
@@ -551,48 +545,45 @@
         <v>131.8158956232372</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>141.7751416992122</v>
+        <v>142.4865164189247</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>151.7343877751872</v>
+        <v>153.1571372146122</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>161.6936338511622</v>
+        <v>163.8277580102997</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>171.6528799271372</v>
+        <v>174.4983788059872</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>181.6121260031122</v>
+        <v>185.1689996016746</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>191.5713720790872</v>
+        <v>195.8396203973622</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>201.5306181550621</v>
+        <v>206.5102411930496</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>211.4898642310372</v>
+        <v>217.1808619887371</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>221.4491103070121</v>
+        <v>227.8514827844246</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>231.4083563829871</v>
+        <v>238.5221035801121</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>241.3676024589621</v>
+        <v>249.1927243757996</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>251.3268485349371</v>
+        <v>259.8633451714871</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>261.2860946109121</v>
+        <v>270.5339659671746</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>271.2453406868871</v>
-      </c>
-      <c r="R2" s="2" t="n">
         <v>281.204586762862</v>
       </c>
     </row>
@@ -608,52 +599,49 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>144.0332759055259</v>
+        <v>143.8937069864961</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>197.8036664979193</v>
+        <v>199.3218027121427</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>213.1325992693789</v>
+        <v>214.6106485564616</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>222.0504050553689</v>
+        <v>223.5946434223144</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>228.7765346710553</v>
+        <v>230.4761436463095</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>234.5333093752699</v>
+        <v>236.4407028896329</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>239.8159734209494</v>
+        <v>241.9664569227971</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>244.8242742734483</v>
+        <v>247.2437889129714</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>249.6740189293641</v>
+        <v>252.378219696918</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>254.4288716763121</v>
+        <v>257.426908181266</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>259.117336740016</v>
+        <v>262.4129518738098</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>263.7562776533733</v>
+        <v>267.3481807597404</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>268.3530066207064</v>
+        <v>272.2332725443987</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>272.9054375058037</v>
+        <v>277.0606615803001</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>277.4066444356947</v>
-      </c>
-      <c r="R3" s="2" t="n">
-        <v>281.8433486403413</v>
+        <v>281.8147654251001</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -671,48 +659,45 @@
         <v>63.1329097750037</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>62.81821530502047</v>
+        <v>62.80642477082593</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>62.77443409039851</v>
+        <v>62.78941520151581</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>62.98333954659806</v>
+        <v>63.0603909279457</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>63.43519426679543</v>
+        <v>63.60787993305775</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>64.12150987078904</v>
+        <v>64.42213701134727</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>65.03884417986269</v>
+        <v>65.50441864600705</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>66.19190756681846</v>
+        <v>66.85804007069402</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>67.58700352770863</v>
+        <v>68.4969900497446</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>69.23643654055438</v>
+        <v>70.43856590231844</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>71.15652392075772</v>
+        <v>72.70674107972968</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>73.37117873692699</v>
+        <v>75.334499370907</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>75.90643851400864</v>
+        <v>78.35800689750069</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>78.79356526134846</v>
+        <v>81.82277126626019</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>82.07065239128174</v>
-      </c>
-      <c r="R4" s="2" t="n">
         <v>85.77863645278707</v>
       </c>
     </row>
@@ -731,49 +716,46 @@
         <v>118.4818050203147</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>123.2407548449228</v>
+        <v>123.5823732775564</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>128.0523504980807</v>
+        <v>128.7448987217674</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>132.9348185643283</v>
+        <v>133.9908714920751</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>137.8978964504892</v>
+        <v>139.3317636055374</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>142.9500725367651</v>
+        <v>144.7773202676591</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>148.094789001872</v>
+        <v>150.3262849952473</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>153.327335473008</v>
+        <v>155.9753425546451</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>158.6414084541208</v>
+        <v>161.7105041815161</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>164.0247034671892</v>
+        <v>167.5144725567006</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>169.4609031968111</v>
+        <v>173.3632742288845</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>174.9260945743784</v>
+        <v>179.2239254091391</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>180.3942400749443</v>
+        <v>185.0602599758142</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>185.8340776891632</v>
+        <v>190.8267703221603</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>191.2075140047</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>196.4736124725757</v>
+        <v>196.4736124725758</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
@@ -788,52 +770,49 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>62.81821530502047</v>
+        <v>62.80642477082593</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>62.77443409039851</v>
+        <v>62.78941520151581</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>62.98333954659806</v>
+        <v>63.0603909279457</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>63.43519426679543</v>
+        <v>63.60787993305775</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>64.12150987078904</v>
+        <v>64.42213701134727</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>65.03884417986269</v>
+        <v>65.50441864600705</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>66.19190756681846</v>
+        <v>66.85804007069402</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>67.58700352770863</v>
+        <v>68.4969900497446</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>69.23643654055438</v>
+        <v>70.43856590231844</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>71.15652392075772</v>
+        <v>72.70674107972968</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>73.37117873692699</v>
+        <v>75.334499370907</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>75.90643851400864</v>
+        <v>78.35800689750069</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>78.79356526134846</v>
+        <v>81.82277126626019</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>82.07065239128174</v>
+        <v>85.77863645278707</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>85.77863645278707</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>89.4866205142924</v>
+        <v>89.73450163931395</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -851,48 +830,45 @@
         <v>235.9528248528826</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>238.8223519448983</v>
+        <v>239.0339391533705</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>241.862941773502</v>
+        <v>242.3109050919186</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>245.0682272359553</v>
+        <v>245.7758888376109</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>248.4318336691518</v>
+        <v>249.421054623574</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>251.9474201937026</v>
+        <v>253.2386218437454</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>255.608715983452</v>
+        <v>257.2209144787189</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>259.4095515079538</v>
+        <v>261.3604029790717</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>263.3438849162977</v>
+        <v>265.6497389301605</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>267.4058238230061</v>
+        <v>270.0817829660258</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>271.5896428226135</v>
+        <v>274.6496264965926</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>275.8897971019783</v>
+        <v>279.3466078682424</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>280.3009325418462</v>
+        <v>284.1663236001668</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>284.8178927053008</v>
+        <v>289.1026353348257</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>289.4357231040248</v>
-      </c>
-      <c r="R7" s="2" t="n">
         <v>294.1496731169576</v>
       </c>
     </row>
@@ -952,9 +928,6 @@
       <c r="Q8" s="2" t="n">
         <v>306.5485944726447</v>
       </c>
-      <c r="R8" s="2" t="n">
-        <v>306.5485944726447</v>
-      </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
@@ -968,52 +941,49 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>239.4969992935521</v>
+        <v>239.4550476430488</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>257.9712496124074</v>
+        <v>258.5548508629961</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>264.0052515050369</v>
+        <v>264.6032607952698</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>267.6550234522111</v>
+        <v>268.2970418587446</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>270.472497298016</v>
+        <v>271.1930065130997</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>272.9266513000059</v>
+        <v>273.748284703391</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>275.2124105858886</v>
+        <v>276.1519573069561</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>277.4085128890916</v>
+        <v>278.4793815789563</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>279.5614033638178</v>
+        <v>280.772867769074</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>281.6967265656767</v>
+        <v>283.0553424941136</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>283.8255053482622</v>
+        <v>285.3354149805807</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>285.9540301995386</v>
+        <v>287.6170114307365</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>288.0845161888494</v>
+        <v>289.8991164641476</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>290.2149363776683</v>
+        <v>292.1768736300561</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>292.3409714273949</v>
-      </c>
-      <c r="R9" s="2" t="n">
-        <v>294.4551866973605</v>
+        <v>294.441507590861</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
@@ -1031,48 +1001,45 @@
         <v>199.2565864072191</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>193.3299802474146</v>
+        <v>192.906651236</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>187.4033740876102</v>
+        <v>186.5567160647809</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>181.4767679278057</v>
+        <v>180.2067808935618</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>175.5501617680012</v>
+        <v>173.8568457223428</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>169.6235556081967</v>
+        <v>167.5069105511237</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>163.6969494483923</v>
+        <v>161.1569753799047</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>157.7703432885878</v>
+        <v>154.8070402086856</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>151.8437371287833</v>
+        <v>148.4571050374665</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>145.9171309689789</v>
+        <v>142.1071698662474</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>139.9905248091744</v>
+        <v>135.7572346950284</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>134.06391864937</v>
+        <v>129.4072995238093</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>128.1373124895655</v>
+        <v>123.0573643525902</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>122.210706329761</v>
+        <v>116.7074291813712</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>116.2841001699566</v>
-      </c>
-      <c r="R10" s="2" t="n">
         <v>110.3574940101521</v>
       </c>
     </row>
@@ -1088,52 +1055,49 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>196.2932833273169</v>
+        <v>196.0816188216095</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>190.3666771675124</v>
+        <v>189.7316836503905</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>184.4400710077079</v>
+        <v>183.3817484791714</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>178.5134648479034</v>
+        <v>177.0318133079523</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>172.5868586880989</v>
+        <v>170.6818781367333</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>166.6602525282945</v>
+        <v>164.3319429655142</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>160.73364636849</v>
+        <v>157.9820077942951</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>154.8070402086856</v>
+        <v>151.6320726230761</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>148.8804340488811</v>
+        <v>145.282137451857</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>142.9538278890766</v>
+        <v>138.9322022806379</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>137.0272217292722</v>
+        <v>132.5822671094188</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>131.1006155694677</v>
+        <v>126.2323319381998</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>125.1740094096633</v>
+        <v>119.8823967669807</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>119.2474032498588</v>
+        <v>113.5324615957616</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>113.3207970900543</v>
-      </c>
-      <c r="R11" s="2" t="n">
-        <v>107.3941909302498</v>
+        <v>107.1825264245426</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
@@ -1148,52 +1112,49 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>193.3299802474146</v>
+        <v>192.906651236</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>187.4033740876102</v>
+        <v>186.5567160647809</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>181.4767679278057</v>
+        <v>180.2067808935618</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>175.5501617680012</v>
+        <v>173.8568457223428</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>169.6235556081967</v>
+        <v>167.5069105511237</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>163.6969494483923</v>
+        <v>161.1569753799047</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>157.7703432885878</v>
+        <v>154.8070402086856</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>151.8437371287833</v>
+        <v>148.4571050374665</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>145.9171309689789</v>
+        <v>142.1071698662474</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>139.9905248091744</v>
+        <v>135.7572346950284</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>134.06391864937</v>
+        <v>129.4072995238093</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>128.1373124895655</v>
+        <v>123.0573643525902</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>122.210706329761</v>
+        <v>116.7074291813712</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>116.2841001699566</v>
+        <v>110.3574940101521</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>110.3574940101521</v>
-      </c>
-      <c r="R12" s="2" t="n">
-        <v>104.4308878503476</v>
+        <v>104.007558838933</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
@@ -1208,52 +1169,49 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>203.2796336000575</v>
+        <v>202.8734164043706</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>197.6376841464971</v>
+        <v>196.8398307513589</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>192.0955969249808</v>
+        <v>190.9217032817525</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>186.6598059798559</v>
+        <v>185.1274296102574</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>181.3386849110711</v>
+        <v>179.4680384343991</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>176.1440958731287</v>
+        <v>173.96091393112</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>171.0931028672199</v>
+        <v>168.6274509688981</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>166.2062680860429</v>
+        <v>163.4972467107021</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>161.5100407251894</v>
+        <v>158.6065550151372</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>157.0369317480237</v>
+        <v>154.0009641868383</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>152.8282177900108</v>
+        <v>149.7382247975115</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>148.9327306535723</v>
+        <v>145.887258409893</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>145.4093623815656</v>
+        <v>142.5327678950195</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>142.3291394489094</v>
+        <v>139.773928026296</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>139.773928026296</v>
-      </c>
-      <c r="R13" s="2" t="n">
-        <v>137.5269631318923</v>
+        <v>137.3675838037859</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
@@ -1271,48 +1229,45 @@
         <v>1.263960413517295</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1.256630058327822</v>
+        <v>1.256040502296066</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1.247573851996579</v>
+        <v>1.246135503953614</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1.23674299694349</v>
+        <v>1.234180744644355</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1.224045425357769</v>
+        <v>1.220059669161307</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1.209378485331547</v>
+        <v>1.203641203861314</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1.19260890515868</v>
+        <v>1.184730466592799</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.173554368824711</v>
+        <v>1.16311285290277</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1.152017253470188</v>
+        <v>1.138508913756399</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1.127762972610197</v>
+        <v>1.110616990886047</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1.100534531961805</v>
+        <v>1.079103625265681</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>1.070039917987022</v>
+        <v>1.043605004052686</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1.035995965757883</v>
+        <v>1.003785044743806</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>0.998130982221335</v>
+        <v>0.9593371267112549</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>0.956203642950578</v>
-      </c>
-      <c r="R14" s="2" t="n">
         <v>0.9100635927466534</v>
       </c>
     </row>
@@ -1328,52 +1283,49 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1.027737036196883</v>
+        <v>1.027259602127857</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.9962607887002388</v>
+        <v>0.9934702855998878</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.9639221817078881</v>
+        <v>0.9586894843126806</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.9307108419430931</v>
+        <v>0.9229100135873011</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.8966619145806796</v>
+        <v>0.8861805048961304</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.8618296975047204</v>
+        <v>0.8485751747230408</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.8263005119355699</v>
+        <v>0.8102244494859512</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.7902002675388272</v>
+        <v>0.7712795787154946</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.7536680647298354</v>
+        <v>0.7319352811294417</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0.7168660817915981</v>
+        <v>0.6923972572989723</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0.6799669415261361</v>
+        <v>0.6528843072915057</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.643157266807891</v>
+        <v>0.6136243984002563</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>0.6066144477575084</v>
+        <v>0.5748284642310716</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>0.5705094165037157</v>
+        <v>0.5366982795159334</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>0.5350040001465581</v>
-      </c>
-      <c r="R15" s="2" t="n">
-        <v>0.5002358174427599</v>
+        <v>0.4994059576906549</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
@@ -1388,52 +1340,49 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1.256630058327822</v>
+        <v>1.256040502296066</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1.247573851996579</v>
+        <v>1.246135503953614</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1.23674299694349</v>
+        <v>1.234180744644355</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1.224045425357769</v>
+        <v>1.220059669161307</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1.209378485331547</v>
+        <v>1.203641203861314</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1.19260890515868</v>
+        <v>1.184730466592799</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1.173554368824711</v>
+        <v>1.16311285290277</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.152017253470188</v>
+        <v>1.138508913756399</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1.127762972610197</v>
+        <v>1.110616990886047</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1.100534531961805</v>
+        <v>1.079103625265681</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1.070039917987022</v>
+        <v>1.043605004052686</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>1.035995965757883</v>
+        <v>1.003785044743806</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>0.998130982221335</v>
+        <v>0.9593371267112549</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>0.956203642950578</v>
+        <v>0.9100635927466534</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>0.9100635927466534</v>
-      </c>
-      <c r="R16" s="2" t="n">
-        <v>0.8623112159794667</v>
+        <v>0.8589357287416615</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
@@ -1451,48 +1400,45 @@
         <v>1.238854298178526</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1.183065343615517</v>
+        <v>1.179090818970713</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1.127594655730443</v>
+        <v>1.119707946820009</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1.072626874380507</v>
+        <v>1.060935254666393</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1.018369838213023</v>
+        <v>1.003026602926231</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.9650168726546282</v>
+        <v>0.9462156398576294</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0.9127569192891843</v>
+        <v>0.8907446283554146</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.8617792674053384</v>
+        <v>0.8368194719467054</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.8122419851622158</v>
+        <v>0.784635000875035</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0.764284516988142</v>
+        <v>0.7343416704175429</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0.7180171480059852</v>
+        <v>0.6860549834527299</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.6735303223469826</v>
+        <v>0.639860226576201</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>0.6308767346766875</v>
+        <v>0.5957954851603467</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>0.5900824873631386</v>
+        <v>0.5538714632197934</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>0.5511521998126707</v>
-      </c>
-      <c r="R17" s="2" t="n">
         <v>0.5140608900158519</v>
       </c>
     </row>
@@ -1508,52 +1454,49 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1.441354280908203</v>
+        <v>1.441916078676133</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1.197482459133908</v>
+        <v>1.19098642640402</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1.138593898695273</v>
+        <v>1.132882090428324</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1.107781456925439</v>
+        <v>1.102244789494197</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1.086121274601831</v>
+        <v>1.08031894092724</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1.068321275422009</v>
+        <v>1.061988888304444</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1.052244235604623</v>
+        <v>1.045162292914203</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.036992137278087</v>
+        <v>1.028975604591301</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1.022001837851195</v>
+        <v>1.012858663989262</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1.006892515432078</v>
+        <v>0.9964147465708382</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0.9914066368294098</v>
+        <v>0.9793475061685435</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.9752814267898019</v>
+        <v>0.9613388689653023</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>0.9582659803345102</v>
+        <v>0.9420774356570143</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>0.9401050336607781</v>
+        <v>0.9212094507966357</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>0.9205046743503615</v>
-      </c>
-      <c r="R18" s="2" t="n">
-        <v>0.89916093915558</v>
+        <v>0.8983629074856455</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
@@ -1568,52 +1511,49 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.202499982729677</v>
+        <v>0.2030617804976078</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.01441711551839076</v>
+        <v>0.01189560743330786</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.01099924296483001</v>
+        <v>0.01317414360831437</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.03515458254493242</v>
+        <v>0.04130953482780408</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.06775143638880832</v>
+        <v>0.07729233800100932</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.1033044027673811</v>
+        <v>0.1157732484468146</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0.139487316315439</v>
+        <v>0.1544176645587889</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.1752128698727489</v>
+        <v>0.1921561326445961</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.209759852688979</v>
+        <v>0.2282236631142266</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0.242607998443936</v>
+        <v>0.2620730761532952</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>0.2733894888234246</v>
+        <v>0.2932925227158136</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.3017511044428193</v>
+        <v>0.3214786423891013</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>0.3273892456578227</v>
+        <v>0.3462819504966675</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>0.3500225462976395</v>
+        <v>0.3673379875768423</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>0.3693524745376908</v>
-      </c>
-      <c r="R19" s="2" t="n">
-        <v>0.3851000491397282</v>
+        <v>0.3843020174697936</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
@@ -1628,52 +1568,49 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.2288930221309395</v>
+        <v>0.2287809001682086</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.2513130632963398</v>
+        <v>0.2526652183537259</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.2728208152356019</v>
+        <v>0.275491260331674</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.293334583414676</v>
+        <v>0.2971496555740062</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.3127165707508677</v>
+        <v>0.317460698965184</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.3307792076539595</v>
+        <v>0.3361552918697579</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.3472538568891409</v>
+        <v>0.3528884034168187</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.3618169859313606</v>
+        <v>0.3672293350409043</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.3740949078803616</v>
+        <v>0.3786817097566055</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0.3836684501702067</v>
+        <v>0.3867063679667089</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>0.3900729764608858</v>
+        <v>0.3907206967611802</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.3928386989499922</v>
+        <v>0.3901606463435494</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>0.3915165344638266</v>
+        <v>0.3845086624801833</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>0.3856942264468624</v>
+        <v>0.37336531323072</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>0.3750595926000952</v>
-      </c>
-      <c r="R20" s="2" t="n">
-        <v>0.3620753985367068</v>
+        <v>0.3595297710510065</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -1732,9 +1669,6 @@
       <c r="Q21" s="2" t="n">
         <v>306.5485944726447</v>
       </c>
-      <c r="R21" s="2" t="n">
-        <v>306.5485944726447</v>
-      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
@@ -1792,9 +1726,6 @@
       <c r="Q22" s="2" t="n">
         <v>306.5485944726447</v>
       </c>
-      <c r="R22" s="2" t="n">
-        <v>306.5485944726447</v>
-      </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
@@ -1811,48 +1742,45 @@
         <v>63.1329097750037</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>62.81821530502046</v>
+        <v>62.80642477082593</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>62.7744340903985</v>
+        <v>62.7894152015158</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>62.98333954659807</v>
+        <v>63.06039092794571</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>63.43519426679543</v>
+        <v>63.60787993305775</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>64.12150987078903</v>
+        <v>64.42213701134727</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>65.03884417986271</v>
+        <v>65.50441864600705</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>66.19190756681846</v>
+        <v>66.85804007069403</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>67.58700352770862</v>
+        <v>68.4969900497446</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>69.23643654055438</v>
+        <v>70.43856590231844</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>71.15652392075773</v>
+        <v>72.70674107972968</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>73.37117873692701</v>
+        <v>75.334499370907</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>75.90643851400864</v>
+        <v>78.35800689750067</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>78.79356526134846</v>
+        <v>81.82277126626018</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>82.07065239128175</v>
-      </c>
-      <c r="R23" s="2" t="n">
         <v>85.77863645278707</v>
       </c>
     </row>
@@ -1871,48 +1799,45 @@
         <v>118.4818050203147</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>123.2407548449227</v>
+        <v>123.5823732775564</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>128.0523504980807</v>
+        <v>128.7448987217674</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>132.9348185643283</v>
+        <v>133.9908714920751</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>137.8978964504892</v>
+        <v>139.3317636055374</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>142.950072536765</v>
+        <v>144.7773202676591</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>148.094789001872</v>
+        <v>150.3262849952473</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>153.3273354730081</v>
+        <v>155.9753425546451</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>158.6414084541208</v>
+        <v>161.7105041815161</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>164.0247034671892</v>
+        <v>167.5144725567006</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>169.4609031968112</v>
+        <v>173.3632742288845</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>174.9260945743783</v>
+        <v>179.2239254091391</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>180.3942400749443</v>
+        <v>185.0602599758142</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>185.8340776891633</v>
+        <v>190.8267703221603</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>191.2075140047</v>
-      </c>
-      <c r="R24" s="2" t="n">
         <v>196.4736124725757</v>
       </c>
     </row>
@@ -1928,52 +1853,49 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>62.81821530502046</v>
+        <v>62.80642477082593</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>62.7744340903985</v>
+        <v>62.7894152015158</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>62.98333954659807</v>
+        <v>63.06039092794571</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>63.43519426679543</v>
+        <v>63.60787993305775</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>64.12150987078903</v>
+        <v>64.42213701134727</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>65.03884417986271</v>
+        <v>65.50441864600705</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>66.19190756681846</v>
+        <v>66.85804007069403</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>67.58700352770862</v>
+        <v>68.4969900497446</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>69.23643654055438</v>
+        <v>70.43856590231844</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>71.15652392075773</v>
+        <v>72.70674107972968</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>73.37117873692701</v>
+        <v>75.334499370907</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>75.90643851400864</v>
+        <v>78.35800689750067</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>78.79356526134846</v>
+        <v>81.82277126626018</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>82.07065239128175</v>
+        <v>85.77863645278707</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>85.77863645278707</v>
-      </c>
-      <c r="R25" s="2" t="n">
-        <v>89.48662051429238</v>
+        <v>89.73450163931396</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
@@ -1991,48 +1913,45 @@
         <v>199.2565864072191</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>193.3299802474146</v>
+        <v>192.906651236</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>187.4033740876102</v>
+        <v>186.5567160647809</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>181.4767679278057</v>
+        <v>180.2067808935618</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>175.5501617680012</v>
+        <v>173.8568457223428</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>169.6235556081967</v>
+        <v>167.5069105511237</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>163.6969494483923</v>
+        <v>161.1569753799047</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>157.7703432885878</v>
+        <v>154.8070402086856</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>151.8437371287833</v>
+        <v>148.4571050374665</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>145.9171309689789</v>
+        <v>142.1071698662474</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>139.9905248091744</v>
+        <v>135.7572346950284</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>134.06391864937</v>
+        <v>129.4072995238093</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>128.1373124895655</v>
+        <v>123.0573643525902</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>122.210706329761</v>
+        <v>116.7074291813712</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>116.2841001699566</v>
-      </c>
-      <c r="R26" s="2" t="n">
         <v>110.3574940101521</v>
       </c>
     </row>
@@ -2048,52 +1967,49 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>196.2932833273169</v>
+        <v>196.0816188216095</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>190.3666771675124</v>
+        <v>189.7316836503905</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>184.4400710077079</v>
+        <v>183.3817484791714</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>178.5134648479034</v>
+        <v>177.0318133079523</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>172.5868586880989</v>
+        <v>170.6818781367333</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>166.6602525282945</v>
+        <v>164.3319429655142</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>160.73364636849</v>
+        <v>157.9820077942951</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>154.8070402086856</v>
+        <v>151.6320726230761</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>148.8804340488811</v>
+        <v>145.282137451857</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>142.9538278890766</v>
+        <v>138.9322022806379</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>137.0272217292722</v>
+        <v>132.5822671094188</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>131.1006155694677</v>
+        <v>126.2323319381998</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>125.1740094096633</v>
+        <v>119.8823967669807</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>119.2474032498588</v>
+        <v>113.5324615957616</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>113.3207970900543</v>
-      </c>
-      <c r="R27" s="2" t="n">
-        <v>107.3941909302498</v>
+        <v>107.1825264245426</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
@@ -2108,52 +2024,49 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>193.3299802474146</v>
+        <v>192.906651236</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>187.4033740876102</v>
+        <v>186.5567160647809</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>181.4767679278057</v>
+        <v>180.2067808935618</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>175.5501617680012</v>
+        <v>173.8568457223428</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>169.6235556081967</v>
+        <v>167.5069105511237</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>163.6969494483923</v>
+        <v>161.1569753799047</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>157.7703432885878</v>
+        <v>154.8070402086856</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>151.8437371287833</v>
+        <v>148.4571050374665</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>145.9171309689789</v>
+        <v>142.1071698662474</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>139.9905248091744</v>
+        <v>135.7572346950284</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>134.06391864937</v>
+        <v>129.4072995238093</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>128.1373124895655</v>
+        <v>123.0573643525902</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>122.210706329761</v>
+        <v>116.7074291813712</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>116.2841001699566</v>
+        <v>110.3574940101521</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>110.3574940101521</v>
-      </c>
-      <c r="R28" s="2" t="n">
-        <v>104.4308878503476</v>
+        <v>104.007558838933</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
@@ -2168,52 +2081,49 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>203.2796336000575</v>
+        <v>202.8734164043707</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>197.6376841464971</v>
+        <v>196.8398307513589</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>192.0955969249808</v>
+        <v>190.9217032817525</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>186.6598059798559</v>
+        <v>185.1274296102574</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>181.3386849110711</v>
+        <v>179.4680384343991</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>176.1440958731287</v>
+        <v>173.96091393112</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>171.0931028672199</v>
+        <v>168.6274509688981</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>166.2062680860429</v>
+        <v>163.4972467107021</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>161.5100407251894</v>
+        <v>158.6065550151372</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>157.0369317480237</v>
+        <v>154.0009641868383</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>152.8282177900108</v>
+        <v>149.7382247975115</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>148.9327306535723</v>
+        <v>145.887258409893</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>145.4093623815656</v>
+        <v>142.5327678950195</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>142.3291394489094</v>
+        <v>139.773928026296</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>139.773928026296</v>
-      </c>
-      <c r="R29" s="2" t="n">
-        <v>137.5269631318923</v>
+        <v>137.3675838037859</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
@@ -2231,48 +2141,45 @@
         <v>1.263960413517295</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1.256630058327822</v>
+        <v>1.256040502296066</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1.247573851996579</v>
+        <v>1.246135503953614</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1.23674299694349</v>
+        <v>1.234180744644354</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>1.224045425357769</v>
+        <v>1.220059669161307</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>1.209378485331547</v>
+        <v>1.203641203861314</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1.19260890515868</v>
+        <v>1.184730466592799</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.173554368824711</v>
+        <v>1.16311285290277</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1.152017253470188</v>
+        <v>1.138508913756399</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1.127762972610197</v>
+        <v>1.110616990886047</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1.100534531961805</v>
+        <v>1.079103625265681</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>1.070039917987022</v>
+        <v>1.043605004052686</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1.035995965757883</v>
+        <v>1.003785044743806</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>0.998130982221335</v>
+        <v>0.9593371267112549</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>0.9562036429505779</v>
-      </c>
-      <c r="R30" s="2" t="n">
         <v>0.9100635927466534</v>
       </c>
     </row>
@@ -2288,52 +2195,49 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>1.027737036196883</v>
+        <v>1.027259602127857</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.9962607887002389</v>
+        <v>0.9934702855998878</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.9639221817078881</v>
+        <v>0.9586894843126805</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.9307108419430931</v>
+        <v>0.9229100135873012</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.8966619145806796</v>
+        <v>0.8861805048961303</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0.8618296975047204</v>
+        <v>0.8485751747230408</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0.8263005119355699</v>
+        <v>0.8102244494859511</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.7902002675388271</v>
+        <v>0.7712795787154946</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.7536680647298354</v>
+        <v>0.7319352811294417</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0.7168660817915981</v>
+        <v>0.6923972572989722</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>0.6799669415261361</v>
+        <v>0.6528843072915056</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.643157266807891</v>
+        <v>0.6136243984002563</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>0.6066144477575085</v>
+        <v>0.5748284642310716</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>0.5705094165037156</v>
+        <v>0.5366982795159333</v>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>0.5350040001465581</v>
-      </c>
-      <c r="R31" s="2" t="n">
-        <v>0.5002358174427599</v>
+        <v>0.4994059576906551</v>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
@@ -2348,52 +2252,49 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>1.256630058327822</v>
+        <v>1.256040502296066</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1.247573851996579</v>
+        <v>1.246135503953614</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1.23674299694349</v>
+        <v>1.234180744644354</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>1.224045425357769</v>
+        <v>1.220059669161307</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>1.209378485331547</v>
+        <v>1.203641203861314</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>1.19260890515868</v>
+        <v>1.184730466592799</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1.173554368824711</v>
+        <v>1.16311285290277</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.152017253470188</v>
+        <v>1.138508913756399</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1.127762972610197</v>
+        <v>1.110616990886047</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1.100534531961805</v>
+        <v>1.079103625265681</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1.070039917987022</v>
+        <v>1.043605004052686</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>1.035995965757883</v>
+        <v>1.003785044743806</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>0.998130982221335</v>
+        <v>0.9593371267112549</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>0.9562036429505779</v>
+        <v>0.9100635927466534</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>0.9100635927466534</v>
-      </c>
-      <c r="R32" s="2" t="n">
-        <v>0.8623112159794668</v>
+        <v>0.8589357287416614</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
@@ -2411,48 +2312,45 @@
         <v>0.6859713621172263</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.6705884899542028</v>
+        <v>0.6694979483838538</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.6553986380229417</v>
+        <v>0.6532416357917733</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.6403479484884566</v>
+        <v>0.6371380242861987</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.6253992375560833</v>
+        <v>0.6211422733362593</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>0.6105171847183516</v>
+        <v>0.6052120725482549</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0.5956753972960683</v>
+        <v>0.5893250755336579</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.5808618150235404</v>
+        <v>0.5734608119872697</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.5660655201964543</v>
+        <v>0.5576165131413827</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0.5512847063075731</v>
+        <v>0.5417922061935735</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>0.536522304657185</v>
+        <v>0.5259963576530508</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.5217920725601732</v>
+        <v>0.5102492768364771</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>0.5071077195318678</v>
+        <v>0.4945713844241342</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>0.4924881203936635</v>
+        <v>0.4789937430112529</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>0.4779595934526376</v>
-      </c>
-      <c r="R33" s="2" t="n">
         <v>0.4635480071574731</v>
       </c>
     </row>
@@ -2468,52 +2366,49 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>0.8067979877758287</v>
+        <v>0.8062590248346283</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.8042862538765255</v>
+        <v>0.8035488409222</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.8017737518398845</v>
+        <v>0.8008406719728749</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.7993118065138726</v>
+        <v>0.798195588988343</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.796932609201779</v>
+        <v>0.7956524962048552</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>0.7946685995501205</v>
+        <v>0.7932503279827856</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0.7925406814235351</v>
+        <v>0.7909985954175668</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.7905462851891686</v>
+        <v>0.788901795817506</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.7886774259944044</v>
+        <v>0.7869287247700162</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0.7869041883167932</v>
+        <v>0.7850315016047531</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>0.7851775641424952</v>
+        <v>0.7831290676610276</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.7834117236377515</v>
+        <v>0.781090136549892</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>0.7814975291784722</v>
+        <v>0.7787448545022609</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>0.7792842964411948</v>
+        <v>0.7758485229457669</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>0.776563149738308</v>
-      </c>
-      <c r="R34" s="2" t="n">
-        <v>0.7730715643917837</v>
+        <v>0.7720854603304109</v>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
@@ -2528,52 +2423,49 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>0.1208266256586024</v>
+        <v>0.120287662717402</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.1336977639223227</v>
+        <v>0.1340508925383462</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.1463751138169428</v>
+        <v>0.1475990361811016</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.158963858025416</v>
+        <v>0.1610575647021443</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.1715333716456957</v>
+        <v>0.174510222868596</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>0.1841514148317689</v>
+        <v>0.1880382554345307</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0.1968652841274667</v>
+        <v>0.2016735198839089</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.2096844701656282</v>
+        <v>0.2154409838302362</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.2226119057979501</v>
+        <v>0.2293122116286335</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0.2356194820092201</v>
+        <v>0.2432392954111796</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>0.2486552594853102</v>
+        <v>0.2571327100079769</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.2616196510775782</v>
+        <v>0.2708408597134149</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>0.2743898096466043</v>
+        <v>0.2841734700781267</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>0.2867961760475313</v>
+        <v>0.296854779934514</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>0.2986035562856704</v>
-      </c>
-      <c r="R35" s="2" t="n">
-        <v>0.3095235572343106</v>
+        <v>0.3085374531729378</v>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
@@ -2588,52 +2480,49 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>0.2288930221309393</v>
+        <v>0.2287809001682086</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.2513130632963397</v>
+        <v>0.2526652183537259</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.2728208152356019</v>
+        <v>0.2754912603316739</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.293334583414676</v>
+        <v>0.2971496555740061</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.3127165707508679</v>
+        <v>0.3174606989651841</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>0.3307792076539593</v>
+        <v>0.3361552918697579</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0.3472538568891409</v>
+        <v>0.3528884034168186</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.3618169859313607</v>
+        <v>0.3672293350409043</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.3740949078803616</v>
+        <v>0.3786817097566055</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0.3836684501702067</v>
+        <v>0.386706367966709</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.3900729764608858</v>
+        <v>0.3907206967611803</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.3928386989499922</v>
+        <v>0.3901606463435494</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>0.3915165344638265</v>
+        <v>0.3845086624801833</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>0.3856942264468624</v>
+        <v>0.3733653132307201</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>0.3750595926000952</v>
-      </c>
-      <c r="R36" s="2" t="n">
-        <v>0.3620753985367069</v>
+        <v>0.3595297710510063</v>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
@@ -2651,48 +2540,45 @@
         <v>314.5701555829461</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>311.0964143021574</v>
+        <v>310.8427598996605</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>307.4831148038699</v>
+        <v>306.9559346026879</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>303.7397746504608</v>
+        <v>302.9207638070474</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>299.8699462373995</v>
+        <v>298.7413489718616</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>295.8767344110082</v>
+        <v>294.4211040077454</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>291.7595769553956</v>
+        <v>289.9549368669936</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>287.5114226630731</v>
+        <v>285.3362605202641</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>283.1239347921154</v>
+        <v>280.5496006135498</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>278.5836847566697</v>
+        <v>275.5764745381484</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>273.8736458935993</v>
+        <v>270.392380015182</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>268.9699639231351</v>
+        <v>264.9645390307169</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>263.8464988535879</v>
+        <v>259.2567437489247</v>
       </c>
       <c r="P37" s="2" t="n">
-        <v>258.472068263976</v>
+        <v>253.2238528296889</v>
       </c>
       <c r="Q37" s="2" t="n">
-        <v>252.808897061437</v>
-      </c>
-      <c r="R37" s="2" t="n">
         <v>246.8160263197884</v>
       </c>
     </row>
@@ -2711,48 +2597,45 @@
         <v>210.7618081429513</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>208.8316965598937</v>
+        <v>208.7148607457964</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>207.4461327164729</v>
+        <v>207.2914216524928</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>206.5854290583349</v>
+        <v>206.4668160957835</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>206.2254271093939</v>
+        <v>206.2108279038947</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>206.339999748764</v>
+        <v>206.4906048898825</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>206.8989412135246</v>
+        <v>207.2651334141023</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>207.8654560168361</v>
+        <v>208.4897047254191</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>209.199794033925</v>
+        <v>210.1104609744029</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>210.8566033240416</v>
+        <v>212.0690315173985</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>212.7862703368112</v>
+        <v>214.3006327876197</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>214.9323909210021</v>
+        <v>216.7323962214619</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>217.2360262570626</v>
+        <v>219.2881728305482</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>219.6337406001647</v>
+        <v>221.8840666464611</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>222.0564222085818</v>
-      </c>
-      <c r="R38" s="2" t="n">
         <v>224.4327929220609</v>
       </c>
     </row>
@@ -2768,52 +2651,49 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>271.8458577472266</v>
+        <v>271.6930594156023</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>264.2749247370671</v>
+        <v>263.5806325950786</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>256.6691428792238</v>
+        <v>255.4271322666185</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>249.0156627948266</v>
+        <v>247.2173753669849</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>241.3074423534967</v>
+        <v>238.9430309708183</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>233.5382541520755</v>
+        <v>230.5969050892176</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>225.7053688840393</v>
+        <v>222.179487723706</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>217.8117855112696</v>
+        <v>213.6927458785889</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>209.8616671012157</v>
+        <v>205.1462206860301</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>201.8634598323201</v>
+        <v>196.5518859932046</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>193.8285185265093</v>
+        <v>187.9265470344896</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>185.7736630477057</v>
+        <v>179.2935385859933</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>177.7173423309921</v>
+        <v>170.6786585177232</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>169.6818721729103</v>
+        <v>162.1146520852101</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>161.694674917383</v>
-      </c>
-      <c r="R39" s="2" t="n">
-        <v>153.7856102107036</v>
+        <v>153.6378717408676</v>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
@@ -2828,52 +2708,49 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>197.9493135724802</v>
+        <v>197.72143536107</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>204.4482809171367</v>
+        <v>204.2904132647651</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>203.117671619961</v>
+        <v>202.4889939477017</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>199.5210387093195</v>
+        <v>198.4164783157589</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>195.0516615582917</v>
+        <v>193.4931563061065</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>190.1660564943506</v>
+        <v>188.1679122287415</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>185.0623698814786</v>
+        <v>182.6368963206165</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>179.8246632362344</v>
+        <v>176.9808315853231</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>174.5059305941222</v>
+        <v>171.2528367629632</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>169.1410965369538</v>
+        <v>165.4883769649389</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>163.7520551642948</v>
+        <v>159.7119364372569</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>158.360894252783</v>
+        <v>153.9496216547927</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>152.9878336468045</v>
+        <v>148.2259193760605</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>147.6528526041854</v>
+        <v>142.5689441551482</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>142.3793985806406</v>
-      </c>
-      <c r="R40" s="2" t="n">
-        <v>137.1914869768414</v>
+        <v>137.0080521648779</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
@@ -2891,48 +2768,45 @@
         <v>326.4880494232335</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>343.2511704264326</v>
+        <v>344.4149824347055</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>359.1728263886171</v>
+        <v>361.4111258356249</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>374.4043820758214</v>
+        <v>377.5784039499244</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>388.9997261794932</v>
+        <v>393.0634234348115</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>403.0379031394633</v>
+        <v>407.93615809925</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>416.584207688006</v>
+        <v>422.2473000638935</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>429.6821761092369</v>
+        <v>436.0696392363308</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>442.3584482492194</v>
+        <v>449.4331984205353</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>454.6611295735622</v>
+        <v>462.3829435045579</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>466.6231066059428</v>
+        <v>474.9590045788212</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>478.2488618262352</v>
+        <v>487.1703723797199</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>489.5728862470405</v>
+        <v>499.0549259694296</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>500.6158448723494</v>
+        <v>510.6318774865657</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>511.3932185174863</v>
-      </c>
-      <c r="R41" s="2" t="n">
         <v>521.9227459001808</v>
       </c>
     </row>
@@ -2951,48 +2825,45 @@
         <v>0.9634966919575119</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.9063229527103194</v>
+        <v>0.9025239195527458</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.856086797811313</v>
+        <v>0.8493261902022795</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0.8112612704114927</v>
+        <v>0.8022724833786353</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.7708744404077876</v>
+        <v>0.7600334479389865</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>0.7341163997387758</v>
+        <v>0.721733286354365</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0.7003615873357932</v>
+        <v>0.6866945906418306</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.6691257833091496</v>
+        <v>0.6543364519024089</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.6400328419467798</v>
+        <v>0.6242298112366838</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0.6127281762968393</v>
+        <v>0.5959918686650948</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>0.5869268838520723</v>
+        <v>0.5692962495888619</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.5624058631233323</v>
+        <v>0.5438847558327973</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>0.5389320084210095</v>
+        <v>0.5194954107412336</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>0.5163082050067413</v>
+        <v>0.4959029469059166</v>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>0.4943532450319197</v>
-      </c>
-      <c r="R42" s="2" t="n">
         <v>0.4728976237548241</v>
       </c>
     </row>
@@ -3011,48 +2882,45 @@
         <v>1.012297336253858</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.9581961788137892</v>
+        <v>0.9545557258404633</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.9095745549609253</v>
+        <v>0.9031825985895713</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.8656953243460359</v>
+        <v>0.8567715131510854</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.8255644869432375</v>
+        <v>0.8146991568544276</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>0.7886332120169451</v>
+        <v>0.7761882703298274</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0.7544739956090307</v>
+        <v>0.7405474047796768</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.7226514090371025</v>
+        <v>0.7074580631056323</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.69271326391988</v>
+        <v>0.6763976034649201</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0.664482224583045</v>
+        <v>0.6470840611245059</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>0.6377420554852364</v>
+        <v>0.6192946645527041</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.6120646462538168</v>
+        <v>0.5925760095770414</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>0.5873562037492842</v>
+        <v>0.5668165391510179</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>0.563440159915512</v>
+        <v>0.5417699140006729</v>
       </c>
       <c r="Q43" s="2" t="n">
-        <v>0.5401203854543033</v>
-      </c>
-      <c r="R43" s="2" t="n">
         <v>0.5172591822396891</v>
       </c>
     </row>
@@ -3071,48 +2939,45 @@
         <v>0.8102668014124158</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.7694023987739284</v>
+        <v>0.7666797833898045</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.7333605416173485</v>
+        <v>0.7286899647968932</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0.7015252700585143</v>
+        <v>0.6951371042708789</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.6730762014819419</v>
+        <v>0.6654966735829467</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>0.647556179476995</v>
+        <v>0.6391258250398036</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0.6246081969296378</v>
+        <v>0.6154468860696426</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.6038666837709337</v>
+        <v>0.5941904540151988</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.5849503864399258</v>
+        <v>0.5749133725656465</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0.5677054937628523</v>
+        <v>0.5573725168712873</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.5519470682297333</v>
+        <v>0.5413756198605113</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.5373033600536083</v>
+        <v>0.5265263523729643</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>0.5236900362851913</v>
+        <v>0.5127258974587042</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>0.510952486515638</v>
+        <v>0.4997576320354005</v>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>0.498918216718421</v>
-      </c>
-      <c r="R44" s="2" t="n">
         <v>0.4874696705720056</v>
       </c>
     </row>
@@ -3131,48 +2996,45 @@
         <v>0.6782385842413425</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.643214529192673</v>
+        <v>0.6409348747810822</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.6136523105156737</v>
+        <v>0.6099312108617739</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.5887936152570951</v>
+        <v>0.5839642163141671</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.5677540916068736</v>
+        <v>0.5623586698183529</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>0.5499809814157157</v>
+        <v>0.5443753293059497</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0.5350291239574648</v>
+        <v>0.5293569349417038</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.5224636408854563</v>
+        <v>0.5169259680265388</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.5118446529185583</v>
+        <v>0.5065707167473752</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0.5029385154667761</v>
+        <v>0.4979615563447621</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>0.4954940187138565</v>
+        <v>0.4908246248958253</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.4890974289424548</v>
+        <v>0.4847079498592656</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>0.4835953035356831</v>
+        <v>0.4794327098427777</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>0.4787769555053555</v>
+        <v>0.4747187532369735</v>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>0.4744184312736267</v>
-      </c>
-      <c r="R45" s="2" t="n">
         <v>0.4703500200761771</v>
       </c>
     </row>

--- a/results/Расчет_ступеней_по_высоте_лопаток.xlsx
+++ b/results/Расчет_ступеней_по_высоте_лопаток.xlsx
@@ -428,14 +428,14 @@
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="21" customWidth="1" min="15" max="15"/>
@@ -599,13 +599,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>143.8937069864961</v>
+        <v>143.8937069864959</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>199.3218027121427</v>
+        <v>199.3218027121426</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>214.6106485564616</v>
+        <v>214.6106485564615</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>223.5946434223144</v>
@@ -656,49 +656,49 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>63.1329097750037</v>
+        <v>63.13290977500401</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>62.80642477082593</v>
+        <v>62.80642477082615</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>62.78941520151581</v>
+        <v>62.7894152015159</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>63.0603909279457</v>
+        <v>63.06039092794582</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>63.60787993305775</v>
+        <v>63.6078799330578</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>64.42213701134727</v>
+        <v>64.42213701134742</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>65.50441864600705</v>
+        <v>65.50441864600704</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>66.85804007069402</v>
+        <v>66.858040070694</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>68.4969900497446</v>
+        <v>68.49699004974445</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>70.43856590231844</v>
+        <v>70.43856590231832</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>72.70674107972968</v>
+        <v>72.70674107972957</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>75.334499370907</v>
+        <v>75.33449937090703</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>78.35800689750069</v>
+        <v>78.35800689750074</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>81.82277126626019</v>
+        <v>81.82277126626025</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>85.77863645278707</v>
+        <v>85.77863645278723</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>118.4818050203147</v>
+        <v>118.4818050203144</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>123.5823732775564</v>
+        <v>123.5823732775562</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>128.7448987217674</v>
+        <v>128.7448987217673</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>133.9908714920751</v>
+        <v>133.990871492075</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>139.3317636055374</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>144.7773202676591</v>
+        <v>144.777320267659</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>150.3262849952473</v>
@@ -737,25 +737,25 @@
         <v>155.9753425546451</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>161.7105041815161</v>
+        <v>161.7105041815163</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>167.5144725567006</v>
+        <v>167.5144725567007</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>173.3632742288845</v>
+        <v>173.3632742288846</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>179.2239254091391</v>
+        <v>179.223925409139</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>185.0602599758142</v>
+        <v>185.0602599758141</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>190.8267703221603</v>
+        <v>190.8267703221602</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>196.4736124725758</v>
+        <v>196.4736124725756</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
@@ -770,49 +770,49 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>62.80642477082593</v>
+        <v>62.80642477082615</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>62.78941520151581</v>
+        <v>62.7894152015159</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>63.0603909279457</v>
+        <v>63.06039092794582</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>63.60787993305775</v>
+        <v>63.6078799330578</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>64.42213701134727</v>
+        <v>64.42213701134742</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>65.50441864600705</v>
+        <v>65.50441864600704</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>66.85804007069402</v>
+        <v>66.858040070694</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>68.4969900497446</v>
+        <v>68.49699004974445</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>70.43856590231844</v>
+        <v>70.43856590231832</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>72.70674107972968</v>
+        <v>72.70674107972957</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>75.334499370907</v>
+        <v>75.33449937090703</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>78.35800689750069</v>
+        <v>78.35800689750074</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>81.82277126626019</v>
+        <v>81.82277126626025</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>85.77863645278707</v>
+        <v>85.77863645278723</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>89.73450163931395</v>
+        <v>89.7345016393142</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -947,7 +947,7 @@
         <v>258.5548508629961</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>264.6032607952698</v>
+        <v>264.6032607952697</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>268.2970418587446</v>
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>202.8734164043706</v>
+        <v>202.8734164043707</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>196.8398307513589</v>
+        <v>196.839830751359</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>190.9217032817525</v>
@@ -1181,16 +1181,16 @@
         <v>185.1274296102574</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>179.4680384343991</v>
+        <v>179.4680384343992</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>173.96091393112</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>168.6274509688981</v>
+        <v>168.627450968898</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>163.4972467107021</v>
+        <v>163.497246710702</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>158.6065550151372</v>
@@ -1202,16 +1202,16 @@
         <v>149.7382247975115</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>145.887258409893</v>
+        <v>145.8872584098931</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>142.5327678950195</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>139.773928026296</v>
+        <v>139.7739280262961</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>137.3675838037859</v>
+        <v>137.3675838037861</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
@@ -1226,16 +1226,16 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1.263960413517295</v>
+        <v>1.263960413517294</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1.256040502296066</v>
+        <v>1.256040502296065</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1.246135503953614</v>
+        <v>1.246135503953613</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1.234180744644355</v>
+        <v>1.234180744644354</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>1.220059669161307</v>
@@ -1250,25 +1250,25 @@
         <v>1.16311285290277</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1.138508913756399</v>
+        <v>1.1385089137564</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1.110616990886047</v>
+        <v>1.110616990886048</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1.079103625265681</v>
+        <v>1.079103625265682</v>
       </c>
       <c r="N14" s="2" t="n">
         <v>1.043605004052686</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1.003785044743806</v>
+        <v>1.003785044743805</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>0.9593371267112549</v>
+        <v>0.9593371267112546</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>0.9100635927466534</v>
+        <v>0.9100635927466525</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
@@ -1283,49 +1283,49 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1.027259602127857</v>
+        <v>1.027259602127858</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.9934702855998878</v>
+        <v>0.9934702855998885</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.9586894843126806</v>
+        <v>0.9586894843126808</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.9229100135873011</v>
+        <v>0.9229100135873015</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0.8861805048961304</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.8485751747230408</v>
+        <v>0.8485751747230412</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.8102244494859512</v>
+        <v>0.810224449485951</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0.7712795787154946</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.7319352811294417</v>
+        <v>0.7319352811294413</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0.6923972572989723</v>
+        <v>0.6923972572989718</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0.6528843072915057</v>
+        <v>0.6528843072915055</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.6136243984002563</v>
+        <v>0.6136243984002564</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>0.5748284642310716</v>
+        <v>0.5748284642310718</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>0.5366982795159334</v>
+        <v>0.5366982795159335</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>0.4994059576906549</v>
+        <v>0.4994059576906553</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
@@ -1340,13 +1340,13 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1.256040502296066</v>
+        <v>1.256040502296065</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1.246135503953614</v>
+        <v>1.246135503953613</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1.234180744644355</v>
+        <v>1.234180744644354</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>1.220059669161307</v>
@@ -1361,28 +1361,28 @@
         <v>1.16311285290277</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.138508913756399</v>
+        <v>1.1385089137564</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1.110616990886047</v>
+        <v>1.110616990886048</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1.079103625265681</v>
+        <v>1.079103625265682</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>1.043605004052686</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>1.003785044743806</v>
+        <v>1.003785044743805</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>0.9593371267112549</v>
+        <v>0.9593371267112546</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>0.9100635927466534</v>
+        <v>0.9100635927466525</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>0.8589357287416615</v>
+        <v>0.85893572874166</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
@@ -1397,22 +1397,22 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>1.238854298178526</v>
+        <v>1.238854298178527</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>1.179090818970713</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1.119707946820009</v>
+        <v>1.11970794682001</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1.060935254666393</v>
+        <v>1.060935254666394</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>1.003026602926231</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.9462156398576294</v>
+        <v>0.9462156398576298</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>0.8907446283554146</v>
@@ -1421,25 +1421,25 @@
         <v>0.8368194719467054</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.784635000875035</v>
+        <v>0.7846350008750345</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0.7343416704175429</v>
+        <v>0.7343416704175426</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0.6860549834527299</v>
+        <v>0.6860549834527295</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.639860226576201</v>
+        <v>0.6398602265762011</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>0.5957954851603467</v>
+        <v>0.595795485160347</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>0.5538714632197934</v>
+        <v>0.5538714632197935</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>0.5140608900158519</v>
+        <v>0.5140608900158523</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
@@ -1469,10 +1469,10 @@
         <v>1.08031894092724</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1.061988888304444</v>
+        <v>1.061988888304443</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1.045162292914203</v>
+        <v>1.045162292914204</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>1.028975604591301</v>
@@ -1481,22 +1481,22 @@
         <v>1.012858663989262</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0.9964147465708382</v>
+        <v>0.9964147465708389</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0.9793475061685435</v>
+        <v>0.9793475061685438</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.9613388689653023</v>
+        <v>0.961338868965302</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>0.9420774356570143</v>
+        <v>0.942077435657014</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>0.9212094507966357</v>
+        <v>0.9212094507966355</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>0.8983629074856455</v>
+        <v>0.8983629074856447</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
@@ -1511,49 +1511,49 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.2030617804976078</v>
+        <v>0.2030617804976063</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.01189560743330786</v>
+        <v>0.01189560743330653</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.01317414360831437</v>
+        <v>0.01317414360831415</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.04130953482780408</v>
+        <v>0.04130953482780275</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0.07729233800100932</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.1157732484468146</v>
+        <v>0.1157732484468135</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0.1544176645587889</v>
+        <v>0.1544176645587891</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0.1921561326445961</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.2282236631142266</v>
+        <v>0.2282236631142278</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0.2620730761532952</v>
+        <v>0.2620730761532963</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>0.2932925227158136</v>
+        <v>0.2932925227158143</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.3214786423891013</v>
+        <v>0.3214786423891008</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>0.3462819504966675</v>
+        <v>0.346281950496667</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>0.3673379875768423</v>
+        <v>0.367337987576842</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>0.3843020174697936</v>
+        <v>0.3843020174697924</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
@@ -1568,49 +1568,49 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.2287809001682086</v>
+        <v>0.2287809001682064</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.2526652183537259</v>
+        <v>0.2526652183537248</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.275491260331674</v>
+        <v>0.2754912603316733</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.2971496555740062</v>
+        <v>0.2971496555740055</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.317460698965184</v>
+        <v>0.3174606989651834</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.3361552918697579</v>
+        <v>0.3361552918697575</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.3528884034168187</v>
+        <v>0.3528884034168189</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.3672293350409043</v>
+        <v>0.3672293350409052</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.3786817097566055</v>
+        <v>0.3786817097566066</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0.3867063679667089</v>
+        <v>0.3867063679667102</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>0.3907206967611802</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.3901606463435494</v>
+        <v>0.3901606463435489</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>0.3845086624801833</v>
+        <v>0.3845086624801828</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>0.37336531323072</v>
+        <v>0.373365313230719</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>0.3595297710510065</v>
+        <v>0.3595297710510048</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -1739,49 +1739,49 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>63.1329097750037</v>
+        <v>63.13290977500402</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>62.80642477082593</v>
+        <v>62.80642477082616</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>62.7894152015158</v>
+        <v>62.78941520151588</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>63.06039092794571</v>
+        <v>63.06039092794581</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>63.60787993305775</v>
+        <v>63.6078799330578</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>64.42213701134727</v>
+        <v>64.42213701134742</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>65.50441864600705</v>
+        <v>65.50441864600704</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>66.85804007069403</v>
+        <v>66.858040070694</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>68.4969900497446</v>
+        <v>68.49699004974445</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>70.43856590231844</v>
+        <v>70.43856590231833</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>72.70674107972968</v>
+        <v>72.70674107972957</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>75.334499370907</v>
+        <v>75.33449937090704</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>78.35800689750067</v>
+        <v>78.35800689750074</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>81.82277126626018</v>
+        <v>81.82277126626022</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>85.77863645278707</v>
+        <v>85.77863645278721</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
@@ -1796,22 +1796,22 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>118.4818050203147</v>
+        <v>118.4818050203144</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>123.5823732775564</v>
+        <v>123.5823732775562</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>128.7448987217674</v>
+        <v>128.7448987217673</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>133.9908714920751</v>
+        <v>133.9908714920749</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>139.3317636055374</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>144.7773202676591</v>
+        <v>144.777320267659</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>150.3262849952473</v>
@@ -1820,25 +1820,25 @@
         <v>155.9753425546451</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>161.7105041815161</v>
+        <v>161.7105041815163</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>167.5144725567006</v>
+        <v>167.5144725567007</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>173.3632742288845</v>
+        <v>173.3632742288846</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>179.2239254091391</v>
+        <v>179.223925409139</v>
       </c>
       <c r="O24" s="2" t="n">
         <v>185.0602599758142</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>190.8267703221603</v>
+        <v>190.8267703221602</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>196.4736124725757</v>
+        <v>196.4736124725756</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
@@ -1853,49 +1853,49 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>62.80642477082593</v>
+        <v>62.80642477082616</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>62.7894152015158</v>
+        <v>62.78941520151588</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>63.06039092794571</v>
+        <v>63.06039092794581</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>63.60787993305775</v>
+        <v>63.6078799330578</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>64.42213701134727</v>
+        <v>64.42213701134742</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>65.50441864600705</v>
+        <v>65.50441864600704</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>66.85804007069403</v>
+        <v>66.858040070694</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>68.4969900497446</v>
+        <v>68.49699004974445</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>70.43856590231844</v>
+        <v>70.43856590231833</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>72.70674107972968</v>
+        <v>72.70674107972957</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>75.334499370907</v>
+        <v>75.33449937090704</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>78.35800689750067</v>
+        <v>78.35800689750074</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>81.82277126626018</v>
+        <v>81.82277126626022</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>85.77863645278707</v>
+        <v>85.77863645278721</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>89.73450163931396</v>
+        <v>89.7345016393142</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
@@ -2084,7 +2084,7 @@
         <v>202.8734164043707</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>196.8398307513589</v>
+        <v>196.839830751359</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>190.9217032817525</v>
@@ -2093,16 +2093,16 @@
         <v>185.1274296102574</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>179.4680384343991</v>
+        <v>179.4680384343992</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>173.96091393112</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>168.6274509688981</v>
+        <v>168.627450968898</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>163.4972467107021</v>
+        <v>163.497246710702</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>158.6065550151372</v>
@@ -2114,16 +2114,16 @@
         <v>149.7382247975115</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>145.887258409893</v>
+        <v>145.8872584098931</v>
       </c>
       <c r="O29" s="2" t="n">
         <v>142.5327678950195</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>139.773928026296</v>
+        <v>139.7739280262961</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>137.3675838037859</v>
+        <v>137.3675838037861</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
@@ -2138,13 +2138,13 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>1.263960413517295</v>
+        <v>1.263960413517294</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1.256040502296066</v>
+        <v>1.256040502296065</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1.246135503953614</v>
+        <v>1.246135503953613</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>1.234180744644354</v>
@@ -2162,25 +2162,25 @@
         <v>1.16311285290277</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1.138508913756399</v>
+        <v>1.1385089137564</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1.110616990886047</v>
+        <v>1.110616990886048</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1.079103625265681</v>
+        <v>1.079103625265682</v>
       </c>
       <c r="N30" s="2" t="n">
         <v>1.043605004052686</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1.003785044743806</v>
+        <v>1.003785044743805</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>0.9593371267112549</v>
+        <v>0.9593371267112547</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>0.9100635927466534</v>
+        <v>0.9100635927466526</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
@@ -2195,22 +2195,22 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>1.027259602127857</v>
+        <v>1.027259602127859</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.9934702855998878</v>
+        <v>0.9934702855998886</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.9586894843126805</v>
+        <v>0.9586894843126808</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.9229100135873012</v>
+        <v>0.9229100135873016</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>0.8861805048961303</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0.8485751747230408</v>
+        <v>0.8485751747230412</v>
       </c>
       <c r="I31" s="2" t="n">
         <v>0.8102244494859511</v>
@@ -2219,25 +2219,25 @@
         <v>0.7712795787154946</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.7319352811294417</v>
+        <v>0.7319352811294413</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0.6923972572989722</v>
+        <v>0.6923972572989718</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>0.6528843072915056</v>
+        <v>0.6528843072915055</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.6136243984002563</v>
+        <v>0.6136243984002564</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>0.5748284642310716</v>
+        <v>0.5748284642310717</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>0.5366982795159333</v>
+        <v>0.5366982795159334</v>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>0.4994059576906551</v>
+        <v>0.4994059576906553</v>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>1.256040502296066</v>
+        <v>1.256040502296065</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1.246135503953614</v>
+        <v>1.246135503953613</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>1.234180744644354</v>
@@ -2273,28 +2273,28 @@
         <v>1.16311285290277</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.138508913756399</v>
+        <v>1.1385089137564</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1.110616990886047</v>
+        <v>1.110616990886048</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1.079103625265681</v>
+        <v>1.079103625265682</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>1.043605004052686</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>1.003785044743806</v>
+        <v>1.003785044743805</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>0.9593371267112549</v>
+        <v>0.9593371267112547</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>0.9100635927466534</v>
+        <v>0.9100635927466526</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>0.8589357287416614</v>
+        <v>0.85893572874166</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>0.6859713621172263</v>
+        <v>0.6859713621172269</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.6694979483838538</v>
+        <v>0.6694979483838542</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.6532416357917733</v>
+        <v>0.6532416357917734</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.6371380242861987</v>
+        <v>0.6371380242861989</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.6211422733362593</v>
+        <v>0.6211422733362594</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>0.6052120725482549</v>
+        <v>0.6052120725482553</v>
       </c>
       <c r="I33" s="2" t="n">
         <v>0.5893250755336579</v>
@@ -2333,25 +2333,25 @@
         <v>0.5734608119872697</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.5576165131413827</v>
+        <v>0.5576165131413824</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0.5417922061935735</v>
+        <v>0.5417922061935732</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>0.5259963576530508</v>
+        <v>0.5259963576530506</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.5102492768364771</v>
+        <v>0.5102492768364773</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>0.4945713844241342</v>
+        <v>0.4945713844241343</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>0.4789937430112529</v>
+        <v>0.478993743011253</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>0.4635480071574731</v>
+        <v>0.4635480071574734</v>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
@@ -2366,22 +2366,22 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>0.8062590248346283</v>
+        <v>0.8062590248346274</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.8035488409222</v>
+        <v>0.8035488409221995</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.8008406719728749</v>
+        <v>0.8008406719728746</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.798195588988343</v>
+        <v>0.7981955889883425</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>0.7956524962048552</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>0.7932503279827856</v>
+        <v>0.7932503279827852</v>
       </c>
       <c r="I34" s="2" t="n">
         <v>0.7909985954175668</v>
@@ -2390,25 +2390,25 @@
         <v>0.788901795817506</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.7869287247700162</v>
+        <v>0.7869287247700167</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0.7850315016047531</v>
+        <v>0.7850315016047533</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>0.7831290676610276</v>
+        <v>0.7831290676610279</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.781090136549892</v>
+        <v>0.7810901365498918</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>0.7787448545022609</v>
+        <v>0.7787448545022608</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>0.7758485229457669</v>
+        <v>0.7758485229457667</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>0.7720854603304109</v>
+        <v>0.7720854603304104</v>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
@@ -2423,22 +2423,22 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>0.120287662717402</v>
+        <v>0.1202876627174005</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.1340508925383462</v>
+        <v>0.1340508925383452</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.1475990361811016</v>
+        <v>0.1475990361811012</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.1610575647021443</v>
+        <v>0.1610575647021436</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.174510222868596</v>
+        <v>0.1745102228685959</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>0.1880382554345307</v>
+        <v>0.1880382554345299</v>
       </c>
       <c r="I35" s="2" t="n">
         <v>0.2016735198839089</v>
@@ -2447,25 +2447,25 @@
         <v>0.2154409838302362</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.2293122116286335</v>
+        <v>0.2293122116286344</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0.2432392954111796</v>
+        <v>0.2432392954111802</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>0.2571327100079769</v>
+        <v>0.2571327100079772</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.2708408597134149</v>
+        <v>0.2708408597134145</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>0.2841734700781267</v>
+        <v>0.2841734700781265</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>0.296854779934514</v>
+        <v>0.2968547799345136</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>0.3085374531729378</v>
+        <v>0.308537453172937</v>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
@@ -2480,49 +2480,49 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>0.2287809001682086</v>
+        <v>0.2287809001682062</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.2526652183537259</v>
+        <v>0.2526652183537249</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.2754912603316739</v>
+        <v>0.2754912603316733</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.2971496555740061</v>
+        <v>0.2971496555740054</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.3174606989651841</v>
+        <v>0.3174606989651835</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>0.3361552918697579</v>
+        <v>0.3361552918697575</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0.3528884034168186</v>
+        <v>0.3528884034168188</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.3672293350409043</v>
+        <v>0.3672293350409052</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.3786817097566055</v>
+        <v>0.3786817097566066</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0.386706367966709</v>
+        <v>0.3867063679667102</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.3907206967611803</v>
+        <v>0.3907206967611802</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.3901606463435494</v>
+        <v>0.3901606463435489</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>0.3845086624801833</v>
+        <v>0.384508662480183</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>0.3733653132307201</v>
+        <v>0.3733653132307192</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>0.3595297710510063</v>
+        <v>0.3595297710510047</v>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
@@ -2537,22 +2537,22 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>314.5701555829461</v>
+        <v>314.5701555829459</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>310.8427598996605</v>
+        <v>310.8427598996603</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>306.9559346026879</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>302.9207638070474</v>
+        <v>302.9207638070473</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>298.7413489718616</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>294.4211040077454</v>
+        <v>294.4211040077453</v>
       </c>
       <c r="I37" s="2" t="n">
         <v>289.9549368669936</v>
@@ -2561,13 +2561,13 @@
         <v>285.3362605202641</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>280.5496006135498</v>
+        <v>280.5496006135499</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>275.5764745381484</v>
+        <v>275.5764745381486</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>270.392380015182</v>
+        <v>270.3923800151821</v>
       </c>
       <c r="N37" s="2" t="n">
         <v>264.9645390307169</v>
@@ -2579,7 +2579,7 @@
         <v>253.2238528296889</v>
       </c>
       <c r="Q37" s="2" t="n">
-        <v>246.8160263197884</v>
+        <v>246.8160263197882</v>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
@@ -2594,22 +2594,22 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>210.7618081429513</v>
+        <v>210.7618081429512</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>208.7148607457964</v>
+        <v>208.7148607457963</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>207.2914216524928</v>
+        <v>207.2914216524927</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>206.4668160957835</v>
+        <v>206.4668160957834</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>206.2108279038947</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>206.4906048898825</v>
+        <v>206.4906048898824</v>
       </c>
       <c r="I38" s="2" t="n">
         <v>207.2651334141023</v>
@@ -2618,25 +2618,25 @@
         <v>208.4897047254191</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>210.1104609744029</v>
+        <v>210.1104609744031</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>212.0690315173985</v>
+        <v>212.0690315173986</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>214.3006327876197</v>
+        <v>214.3006327876198</v>
       </c>
       <c r="N38" s="2" t="n">
         <v>216.7323962214619</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>219.2881728305482</v>
+        <v>219.2881728305481</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>221.8840666464611</v>
+        <v>221.884066646461</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>224.4327929220609</v>
+        <v>224.4327929220607</v>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
@@ -2651,22 +2651,22 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>271.6930594156023</v>
+        <v>271.6930594156025</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>263.5806325950786</v>
+        <v>263.5806325950787</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>255.4271322666185</v>
+        <v>255.4271322666186</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>247.2173753669849</v>
+        <v>247.217375366985</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>238.9430309708183</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>230.5969050892176</v>
+        <v>230.5969050892178</v>
       </c>
       <c r="I39" s="2" t="n">
         <v>222.179487723706</v>
@@ -2678,22 +2678,22 @@
         <v>205.1462206860301</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>196.5518859932046</v>
+        <v>196.5518859932045</v>
       </c>
       <c r="M39" s="2" t="n">
         <v>187.9265470344896</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>179.2935385859933</v>
+        <v>179.2935385859934</v>
       </c>
       <c r="O39" s="2" t="n">
         <v>170.6786585177232</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>162.1146520852101</v>
+        <v>162.1146520852102</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>153.6378717408676</v>
+        <v>153.6378717408677</v>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
@@ -2711,19 +2711,19 @@
         <v>197.72143536107</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>204.2904132647651</v>
+        <v>204.2904132647652</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>202.4889939477017</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>198.4164783157589</v>
+        <v>198.416478315759</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>193.4931563061065</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>188.1679122287415</v>
+        <v>188.1679122287416</v>
       </c>
       <c r="I40" s="2" t="n">
         <v>182.6368963206165</v>
@@ -2732,25 +2732,25 @@
         <v>176.9808315853231</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>171.2528367629632</v>
+        <v>171.2528367629631</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>165.4883769649389</v>
+        <v>165.4883769649388</v>
       </c>
       <c r="M40" s="2" t="n">
         <v>159.7119364372569</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>153.9496216547927</v>
+        <v>153.9496216547928</v>
       </c>
       <c r="O40" s="2" t="n">
         <v>148.2259193760605</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>142.5689441551482</v>
+        <v>142.5689441551483</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>137.0080521648779</v>
+        <v>137.008052164878</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
@@ -2774,7 +2774,7 @@
         <v>361.4111258356249</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>377.5784039499244</v>
+        <v>377.5784039499243</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>393.0634234348115</v>
@@ -2801,7 +2801,7 @@
         <v>487.1703723797199</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>499.0549259694296</v>
+        <v>499.0549259694295</v>
       </c>
       <c r="P41" s="2" t="n">
         <v>510.6318774865657</v>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>0.9634966919575119</v>
+        <v>0.9634966919575113</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.9025239195527458</v>
+        <v>0.9025239195527452</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>0.8493261902022795</v>
@@ -2834,10 +2834,10 @@
         <v>0.8022724833786353</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.7600334479389865</v>
+        <v>0.7600334479389863</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>0.721733286354365</v>
+        <v>0.7217332863543645</v>
       </c>
       <c r="I42" s="2" t="n">
         <v>0.6866945906418306</v>
@@ -2846,25 +2846,25 @@
         <v>0.6543364519024089</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.6242298112366838</v>
+        <v>0.624229811236684</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0.5959918686650948</v>
+        <v>0.5959918686650951</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>0.5692962495888619</v>
+        <v>0.5692962495888622</v>
       </c>
       <c r="N42" s="2" t="n">
         <v>0.5438847558327973</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>0.5194954107412336</v>
+        <v>0.5194954107412335</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>0.4959029469059166</v>
+        <v>0.4959029469059165</v>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>0.4728976237548241</v>
+        <v>0.4728976237548239</v>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
@@ -2879,22 +2879,22 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>1.012297336253858</v>
+        <v>1.012297336253857</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.9545557258404633</v>
+        <v>0.9545557258404628</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>0.9031825985895713</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.8567715131510854</v>
+        <v>0.8567715131510852</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.8146991568544276</v>
+        <v>0.8146991568544275</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>0.7761882703298274</v>
+        <v>0.776188270329827</v>
       </c>
       <c r="I43" s="2" t="n">
         <v>0.7405474047796768</v>
@@ -2903,25 +2903,25 @@
         <v>0.7074580631056323</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.6763976034649201</v>
+        <v>0.6763976034649203</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0.6470840611245059</v>
+        <v>0.6470840611245063</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>0.6192946645527041</v>
+        <v>0.6192946645527042</v>
       </c>
       <c r="N43" s="2" t="n">
         <v>0.5925760095770414</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>0.5668165391510179</v>
+        <v>0.5668165391510178</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>0.5417699140006729</v>
+        <v>0.5417699140006728</v>
       </c>
       <c r="Q43" s="2" t="n">
-        <v>0.5172591822396891</v>
+        <v>0.5172591822396889</v>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
@@ -2936,22 +2936,22 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>0.8102668014124158</v>
+        <v>0.810266801412415</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.7666797833898045</v>
+        <v>0.7666797833898039</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>0.7286899647968932</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0.6951371042708789</v>
+        <v>0.6951371042708787</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.6654966735829467</v>
+        <v>0.6654966735829465</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>0.6391258250398036</v>
+        <v>0.6391258250398033</v>
       </c>
       <c r="I44" s="2" t="n">
         <v>0.6154468860696426</v>
@@ -2960,25 +2960,25 @@
         <v>0.5941904540151988</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.5749133725656465</v>
+        <v>0.5749133725656468</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0.5573725168712873</v>
+        <v>0.5573725168712876</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.5413756198605113</v>
+        <v>0.5413756198605114</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.5265263523729643</v>
+        <v>0.5265263523729644</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>0.5127258974587042</v>
+        <v>0.512725897458704</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>0.4997576320354005</v>
+        <v>0.4997576320354004</v>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>0.4874696705720056</v>
+        <v>0.4874696705720054</v>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
@@ -2993,22 +2993,22 @@
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>0.6782385842413425</v>
+        <v>0.6782385842413422</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.6409348747810822</v>
+        <v>0.6409348747810819</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.6099312108617739</v>
+        <v>0.6099312108617738</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.5839642163141671</v>
+        <v>0.5839642163141668</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>0.5623586698183529</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>0.5443753293059497</v>
+        <v>0.5443753293059495</v>
       </c>
       <c r="I45" s="2" t="n">
         <v>0.5293569349417038</v>
@@ -3017,25 +3017,25 @@
         <v>0.5169259680265388</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.5065707167473752</v>
+        <v>0.5065707167473755</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0.4979615563447621</v>
+        <v>0.4979615563447622</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>0.4908246248958253</v>
+        <v>0.4908246248958255</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.4847079498592656</v>
+        <v>0.4847079498592655</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>0.4794327098427777</v>
+        <v>0.4794327098427775</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>0.4747187532369735</v>
+        <v>0.4747187532369734</v>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>0.4703500200761771</v>
+        <v>0.4703500200761768</v>
       </c>
     </row>
   </sheetData>

--- a/results/Расчет_ступеней_по_высоте_лопаток.xlsx
+++ b/results/Расчет_ступеней_по_высоте_лопаток.xlsx
@@ -428,14 +428,14 @@
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="21" customWidth="1" min="15" max="15"/>
@@ -599,13 +599,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>143.8937069864959</v>
+        <v>143.8937069864961</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>199.3218027121426</v>
+        <v>199.3218027121427</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>214.6106485564615</v>
+        <v>214.6106485564616</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>223.5946434223144</v>
@@ -656,49 +656,49 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>63.13290977500401</v>
+        <v>63.1329097750037</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>62.80642477082615</v>
+        <v>62.80642477082593</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>62.7894152015159</v>
+        <v>62.78941520151581</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>63.06039092794582</v>
+        <v>63.0603909279457</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>63.6078799330578</v>
+        <v>63.60787993305775</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>64.42213701134742</v>
+        <v>64.42213701134727</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>65.50441864600704</v>
+        <v>65.50441864600705</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>66.858040070694</v>
+        <v>66.85804007069402</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>68.49699004974445</v>
+        <v>68.4969900497446</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>70.43856590231832</v>
+        <v>70.43856590231844</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>72.70674107972957</v>
+        <v>72.70674107972968</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>75.33449937090703</v>
+        <v>75.334499370907</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>78.35800689750074</v>
+        <v>78.35800689750069</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>81.82277126626025</v>
+        <v>81.82277126626019</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>85.77863645278723</v>
+        <v>85.77863645278707</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>118.4818050203144</v>
+        <v>118.4818050203147</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>123.5823732775562</v>
+        <v>123.5823732775564</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>128.7448987217673</v>
+        <v>128.7448987217674</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>133.990871492075</v>
+        <v>133.9908714920751</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>139.3317636055374</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>144.777320267659</v>
+        <v>144.7773202676591</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>150.3262849952473</v>
@@ -737,25 +737,25 @@
         <v>155.9753425546451</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>161.7105041815163</v>
+        <v>161.7105041815161</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>167.5144725567007</v>
+        <v>167.5144725567006</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>173.3632742288846</v>
+        <v>173.3632742288845</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>179.223925409139</v>
+        <v>179.2239254091391</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>185.0602599758141</v>
+        <v>185.0602599758142</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>190.8267703221602</v>
+        <v>190.8267703221603</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>196.4736124725756</v>
+        <v>196.4736124725758</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
@@ -770,49 +770,49 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>62.80642477082615</v>
+        <v>62.80642477082593</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>62.7894152015159</v>
+        <v>62.78941520151581</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>63.06039092794582</v>
+        <v>63.0603909279457</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>63.6078799330578</v>
+        <v>63.60787993305775</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>64.42213701134742</v>
+        <v>64.42213701134727</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>65.50441864600704</v>
+        <v>65.50441864600705</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>66.858040070694</v>
+        <v>66.85804007069402</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>68.49699004974445</v>
+        <v>68.4969900497446</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>70.43856590231832</v>
+        <v>70.43856590231844</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>72.70674107972957</v>
+        <v>72.70674107972968</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>75.33449937090703</v>
+        <v>75.334499370907</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>78.35800689750074</v>
+        <v>78.35800689750069</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>81.82277126626025</v>
+        <v>81.82277126626019</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>85.77863645278723</v>
+        <v>85.77863645278707</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>89.7345016393142</v>
+        <v>89.73450163931395</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -947,7 +947,7 @@
         <v>258.5548508629961</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>264.6032607952697</v>
+        <v>264.6032607952698</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>268.2970418587446</v>
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>202.8734164043707</v>
+        <v>202.8734164043706</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>196.839830751359</v>
+        <v>196.8398307513589</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>190.9217032817525</v>
@@ -1181,16 +1181,16 @@
         <v>185.1274296102574</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>179.4680384343992</v>
+        <v>179.4680384343991</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>173.96091393112</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>168.627450968898</v>
+        <v>168.6274509688981</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>163.497246710702</v>
+        <v>163.4972467107021</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>158.6065550151372</v>
@@ -1202,16 +1202,16 @@
         <v>149.7382247975115</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>145.8872584098931</v>
+        <v>145.887258409893</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>142.5327678950195</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>139.7739280262961</v>
+        <v>139.773928026296</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>137.3675838037861</v>
+        <v>137.3675838037859</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
@@ -1226,16 +1226,16 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1.263960413517294</v>
+        <v>1.263960413517295</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1.256040502296065</v>
+        <v>1.256040502296066</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1.246135503953613</v>
+        <v>1.246135503953614</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1.234180744644354</v>
+        <v>1.234180744644355</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>1.220059669161307</v>
@@ -1250,25 +1250,25 @@
         <v>1.16311285290277</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1.1385089137564</v>
+        <v>1.138508913756399</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1.110616990886048</v>
+        <v>1.110616990886047</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1.079103625265682</v>
+        <v>1.079103625265681</v>
       </c>
       <c r="N14" s="2" t="n">
         <v>1.043605004052686</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1.003785044743805</v>
+        <v>1.003785044743806</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>0.9593371267112546</v>
+        <v>0.9593371267112549</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>0.9100635927466525</v>
+        <v>0.9100635927466534</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
@@ -1283,49 +1283,49 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1.027259602127858</v>
+        <v>1.027259602127857</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.9934702855998885</v>
+        <v>0.9934702855998878</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.9586894843126808</v>
+        <v>0.9586894843126806</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.9229100135873015</v>
+        <v>0.9229100135873011</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0.8861805048961304</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.8485751747230412</v>
+        <v>0.8485751747230408</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.810224449485951</v>
+        <v>0.8102244494859512</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0.7712795787154946</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.7319352811294413</v>
+        <v>0.7319352811294417</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0.6923972572989718</v>
+        <v>0.6923972572989723</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0.6528843072915055</v>
+        <v>0.6528843072915057</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.6136243984002564</v>
+        <v>0.6136243984002563</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>0.5748284642310718</v>
+        <v>0.5748284642310716</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>0.5366982795159335</v>
+        <v>0.5366982795159334</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>0.4994059576906553</v>
+        <v>0.4994059576906549</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
@@ -1340,13 +1340,13 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1.256040502296065</v>
+        <v>1.256040502296066</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1.246135503953613</v>
+        <v>1.246135503953614</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1.234180744644354</v>
+        <v>1.234180744644355</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>1.220059669161307</v>
@@ -1361,28 +1361,28 @@
         <v>1.16311285290277</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.1385089137564</v>
+        <v>1.138508913756399</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1.110616990886048</v>
+        <v>1.110616990886047</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1.079103625265682</v>
+        <v>1.079103625265681</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>1.043605004052686</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>1.003785044743805</v>
+        <v>1.003785044743806</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>0.9593371267112546</v>
+        <v>0.9593371267112549</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>0.9100635927466525</v>
+        <v>0.9100635927466534</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>0.85893572874166</v>
+        <v>0.8589357287416615</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
@@ -1397,22 +1397,22 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>1.238854298178527</v>
+        <v>1.238854298178526</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>1.179090818970713</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1.11970794682001</v>
+        <v>1.119707946820009</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1.060935254666394</v>
+        <v>1.060935254666393</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>1.003026602926231</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.9462156398576298</v>
+        <v>0.9462156398576294</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>0.8907446283554146</v>
@@ -1421,25 +1421,25 @@
         <v>0.8368194719467054</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.7846350008750345</v>
+        <v>0.784635000875035</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0.7343416704175426</v>
+        <v>0.7343416704175429</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0.6860549834527295</v>
+        <v>0.6860549834527299</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.6398602265762011</v>
+        <v>0.639860226576201</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>0.595795485160347</v>
+        <v>0.5957954851603467</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>0.5538714632197935</v>
+        <v>0.5538714632197934</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>0.5140608900158523</v>
+        <v>0.5140608900158519</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
@@ -1469,10 +1469,10 @@
         <v>1.08031894092724</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1.061988888304443</v>
+        <v>1.061988888304444</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1.045162292914204</v>
+        <v>1.045162292914203</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>1.028975604591301</v>
@@ -1481,22 +1481,22 @@
         <v>1.012858663989262</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0.9964147465708389</v>
+        <v>0.9964147465708382</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0.9793475061685438</v>
+        <v>0.9793475061685435</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.961338868965302</v>
+        <v>0.9613388689653023</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>0.942077435657014</v>
+        <v>0.9420774356570143</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>0.9212094507966355</v>
+        <v>0.9212094507966357</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>0.8983629074856447</v>
+        <v>0.8983629074856455</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
@@ -1511,49 +1511,49 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.2030617804976063</v>
+        <v>0.2030617804976078</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.01189560743330653</v>
+        <v>0.01189560743330786</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.01317414360831415</v>
+        <v>0.01317414360831437</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.04130953482780275</v>
+        <v>0.04130953482780408</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0.07729233800100932</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.1157732484468135</v>
+        <v>0.1157732484468146</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0.1544176645587891</v>
+        <v>0.1544176645587889</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0.1921561326445961</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.2282236631142278</v>
+        <v>0.2282236631142266</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0.2620730761532963</v>
+        <v>0.2620730761532952</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>0.2932925227158143</v>
+        <v>0.2932925227158136</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.3214786423891008</v>
+        <v>0.3214786423891013</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>0.346281950496667</v>
+        <v>0.3462819504966675</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>0.367337987576842</v>
+        <v>0.3673379875768423</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>0.3843020174697924</v>
+        <v>0.3843020174697936</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
@@ -1568,49 +1568,49 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.2287809001682064</v>
+        <v>0.2287809001682086</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.2526652183537248</v>
+        <v>0.2526652183537259</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.2754912603316733</v>
+        <v>0.275491260331674</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.2971496555740055</v>
+        <v>0.2971496555740062</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.3174606989651834</v>
+        <v>0.317460698965184</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.3361552918697575</v>
+        <v>0.3361552918697579</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.3528884034168189</v>
+        <v>0.3528884034168187</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.3672293350409052</v>
+        <v>0.3672293350409043</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.3786817097566066</v>
+        <v>0.3786817097566055</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0.3867063679667102</v>
+        <v>0.3867063679667089</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>0.3907206967611802</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.3901606463435489</v>
+        <v>0.3901606463435494</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>0.3845086624801828</v>
+        <v>0.3845086624801833</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>0.373365313230719</v>
+        <v>0.37336531323072</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>0.3595297710510048</v>
+        <v>0.3595297710510065</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -1739,49 +1739,49 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>63.13290977500402</v>
+        <v>63.1329097750037</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>62.80642477082616</v>
+        <v>62.80642477082593</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>62.78941520151588</v>
+        <v>62.7894152015158</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>63.06039092794581</v>
+        <v>63.06039092794571</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>63.6078799330578</v>
+        <v>63.60787993305775</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>64.42213701134742</v>
+        <v>64.42213701134727</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>65.50441864600704</v>
+        <v>65.50441864600705</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>66.858040070694</v>
+        <v>66.85804007069403</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>68.49699004974445</v>
+        <v>68.4969900497446</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>70.43856590231833</v>
+        <v>70.43856590231844</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>72.70674107972957</v>
+        <v>72.70674107972968</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>75.33449937090704</v>
+        <v>75.334499370907</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>78.35800689750074</v>
+        <v>78.35800689750067</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>81.82277126626022</v>
+        <v>81.82277126626018</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>85.77863645278721</v>
+        <v>85.77863645278707</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
@@ -1796,22 +1796,22 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>118.4818050203144</v>
+        <v>118.4818050203147</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>123.5823732775562</v>
+        <v>123.5823732775564</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>128.7448987217673</v>
+        <v>128.7448987217674</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>133.9908714920749</v>
+        <v>133.9908714920751</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>139.3317636055374</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>144.777320267659</v>
+        <v>144.7773202676591</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>150.3262849952473</v>
@@ -1820,25 +1820,25 @@
         <v>155.9753425546451</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>161.7105041815163</v>
+        <v>161.7105041815161</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>167.5144725567007</v>
+        <v>167.5144725567006</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>173.3632742288846</v>
+        <v>173.3632742288845</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>179.223925409139</v>
+        <v>179.2239254091391</v>
       </c>
       <c r="O24" s="2" t="n">
         <v>185.0602599758142</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>190.8267703221602</v>
+        <v>190.8267703221603</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>196.4736124725756</v>
+        <v>196.4736124725757</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
@@ -1853,49 +1853,49 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>62.80642477082616</v>
+        <v>62.80642477082593</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>62.78941520151588</v>
+        <v>62.7894152015158</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>63.06039092794581</v>
+        <v>63.06039092794571</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>63.6078799330578</v>
+        <v>63.60787993305775</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>64.42213701134742</v>
+        <v>64.42213701134727</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>65.50441864600704</v>
+        <v>65.50441864600705</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>66.858040070694</v>
+        <v>66.85804007069403</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>68.49699004974445</v>
+        <v>68.4969900497446</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>70.43856590231833</v>
+        <v>70.43856590231844</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>72.70674107972957</v>
+        <v>72.70674107972968</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>75.33449937090704</v>
+        <v>75.334499370907</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>78.35800689750074</v>
+        <v>78.35800689750067</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>81.82277126626022</v>
+        <v>81.82277126626018</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>85.77863645278721</v>
+        <v>85.77863645278707</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>89.7345016393142</v>
+        <v>89.73450163931396</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
@@ -2084,7 +2084,7 @@
         <v>202.8734164043707</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>196.839830751359</v>
+        <v>196.8398307513589</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>190.9217032817525</v>
@@ -2093,16 +2093,16 @@
         <v>185.1274296102574</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>179.4680384343992</v>
+        <v>179.4680384343991</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>173.96091393112</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>168.627450968898</v>
+        <v>168.6274509688981</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>163.497246710702</v>
+        <v>163.4972467107021</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>158.6065550151372</v>
@@ -2114,16 +2114,16 @@
         <v>149.7382247975115</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>145.8872584098931</v>
+        <v>145.887258409893</v>
       </c>
       <c r="O29" s="2" t="n">
         <v>142.5327678950195</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>139.7739280262961</v>
+        <v>139.773928026296</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>137.3675838037861</v>
+        <v>137.3675838037859</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
@@ -2138,13 +2138,13 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>1.263960413517294</v>
+        <v>1.263960413517295</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1.256040502296065</v>
+        <v>1.256040502296066</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1.246135503953613</v>
+        <v>1.246135503953614</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>1.234180744644354</v>
@@ -2162,25 +2162,25 @@
         <v>1.16311285290277</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1.1385089137564</v>
+        <v>1.138508913756399</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1.110616990886048</v>
+        <v>1.110616990886047</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1.079103625265682</v>
+        <v>1.079103625265681</v>
       </c>
       <c r="N30" s="2" t="n">
         <v>1.043605004052686</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1.003785044743805</v>
+        <v>1.003785044743806</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>0.9593371267112547</v>
+        <v>0.9593371267112549</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>0.9100635927466526</v>
+        <v>0.9100635927466534</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
@@ -2195,22 +2195,22 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>1.027259602127859</v>
+        <v>1.027259602127857</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.9934702855998886</v>
+        <v>0.9934702855998878</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.9586894843126808</v>
+        <v>0.9586894843126805</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.9229100135873016</v>
+        <v>0.9229100135873012</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>0.8861805048961303</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0.8485751747230412</v>
+        <v>0.8485751747230408</v>
       </c>
       <c r="I31" s="2" t="n">
         <v>0.8102244494859511</v>
@@ -2219,25 +2219,25 @@
         <v>0.7712795787154946</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.7319352811294413</v>
+        <v>0.7319352811294417</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0.6923972572989718</v>
+        <v>0.6923972572989722</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>0.6528843072915055</v>
+        <v>0.6528843072915056</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.6136243984002564</v>
+        <v>0.6136243984002563</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>0.5748284642310717</v>
+        <v>0.5748284642310716</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>0.5366982795159334</v>
+        <v>0.5366982795159333</v>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>0.4994059576906553</v>
+        <v>0.4994059576906551</v>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>1.256040502296065</v>
+        <v>1.256040502296066</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1.246135503953613</v>
+        <v>1.246135503953614</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>1.234180744644354</v>
@@ -2273,28 +2273,28 @@
         <v>1.16311285290277</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.1385089137564</v>
+        <v>1.138508913756399</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1.110616990886048</v>
+        <v>1.110616990886047</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1.079103625265682</v>
+        <v>1.079103625265681</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>1.043605004052686</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>1.003785044743805</v>
+        <v>1.003785044743806</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>0.9593371267112547</v>
+        <v>0.9593371267112549</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>0.9100635927466526</v>
+        <v>0.9100635927466534</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>0.85893572874166</v>
+        <v>0.8589357287416614</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>0.6859713621172269</v>
+        <v>0.6859713621172263</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.6694979483838542</v>
+        <v>0.6694979483838538</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.6532416357917734</v>
+        <v>0.6532416357917733</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.6371380242861989</v>
+        <v>0.6371380242861987</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.6211422733362594</v>
+        <v>0.6211422733362593</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>0.6052120725482553</v>
+        <v>0.6052120725482549</v>
       </c>
       <c r="I33" s="2" t="n">
         <v>0.5893250755336579</v>
@@ -2333,25 +2333,25 @@
         <v>0.5734608119872697</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.5576165131413824</v>
+        <v>0.5576165131413827</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0.5417922061935732</v>
+        <v>0.5417922061935735</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>0.5259963576530506</v>
+        <v>0.5259963576530508</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.5102492768364773</v>
+        <v>0.5102492768364771</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>0.4945713844241343</v>
+        <v>0.4945713844241342</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>0.478993743011253</v>
+        <v>0.4789937430112529</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>0.4635480071574734</v>
+        <v>0.4635480071574731</v>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
@@ -2366,22 +2366,22 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>0.8062590248346274</v>
+        <v>0.8062590248346283</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.8035488409221995</v>
+        <v>0.8035488409222</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.8008406719728746</v>
+        <v>0.8008406719728749</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.7981955889883425</v>
+        <v>0.798195588988343</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>0.7956524962048552</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>0.7932503279827852</v>
+        <v>0.7932503279827856</v>
       </c>
       <c r="I34" s="2" t="n">
         <v>0.7909985954175668</v>
@@ -2390,25 +2390,25 @@
         <v>0.788901795817506</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.7869287247700167</v>
+        <v>0.7869287247700162</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0.7850315016047533</v>
+        <v>0.7850315016047531</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>0.7831290676610279</v>
+        <v>0.7831290676610276</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.7810901365498918</v>
+        <v>0.781090136549892</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>0.7787448545022608</v>
+        <v>0.7787448545022609</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>0.7758485229457667</v>
+        <v>0.7758485229457669</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>0.7720854603304104</v>
+        <v>0.7720854603304109</v>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
@@ -2423,22 +2423,22 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>0.1202876627174005</v>
+        <v>0.120287662717402</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.1340508925383452</v>
+        <v>0.1340508925383462</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.1475990361811012</v>
+        <v>0.1475990361811016</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.1610575647021436</v>
+        <v>0.1610575647021443</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.1745102228685959</v>
+        <v>0.174510222868596</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>0.1880382554345299</v>
+        <v>0.1880382554345307</v>
       </c>
       <c r="I35" s="2" t="n">
         <v>0.2016735198839089</v>
@@ -2447,25 +2447,25 @@
         <v>0.2154409838302362</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.2293122116286344</v>
+        <v>0.2293122116286335</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0.2432392954111802</v>
+        <v>0.2432392954111796</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>0.2571327100079772</v>
+        <v>0.2571327100079769</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.2708408597134145</v>
+        <v>0.2708408597134149</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>0.2841734700781265</v>
+        <v>0.2841734700781267</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>0.2968547799345136</v>
+        <v>0.296854779934514</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>0.308537453172937</v>
+        <v>0.3085374531729378</v>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
@@ -2480,49 +2480,49 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>0.2287809001682062</v>
+        <v>0.2287809001682086</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.2526652183537249</v>
+        <v>0.2526652183537259</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.2754912603316733</v>
+        <v>0.2754912603316739</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.2971496555740054</v>
+        <v>0.2971496555740061</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.3174606989651835</v>
+        <v>0.3174606989651841</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>0.3361552918697575</v>
+        <v>0.3361552918697579</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0.3528884034168188</v>
+        <v>0.3528884034168186</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.3672293350409052</v>
+        <v>0.3672293350409043</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.3786817097566066</v>
+        <v>0.3786817097566055</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0.3867063679667102</v>
+        <v>0.386706367966709</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.3907206967611802</v>
+        <v>0.3907206967611803</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.3901606463435489</v>
+        <v>0.3901606463435494</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>0.384508662480183</v>
+        <v>0.3845086624801833</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>0.3733653132307192</v>
+        <v>0.3733653132307201</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>0.3595297710510047</v>
+        <v>0.3595297710510063</v>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
@@ -2537,22 +2537,22 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>314.5701555829459</v>
+        <v>314.5701555829461</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>310.8427598996603</v>
+        <v>310.8427598996605</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>306.9559346026879</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>302.9207638070473</v>
+        <v>302.9207638070474</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>298.7413489718616</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>294.4211040077453</v>
+        <v>294.4211040077454</v>
       </c>
       <c r="I37" s="2" t="n">
         <v>289.9549368669936</v>
@@ -2561,13 +2561,13 @@
         <v>285.3362605202641</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>280.5496006135499</v>
+        <v>280.5496006135498</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>275.5764745381486</v>
+        <v>275.5764745381484</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>270.3923800151821</v>
+        <v>270.392380015182</v>
       </c>
       <c r="N37" s="2" t="n">
         <v>264.9645390307169</v>
@@ -2579,7 +2579,7 @@
         <v>253.2238528296889</v>
       </c>
       <c r="Q37" s="2" t="n">
-        <v>246.8160263197882</v>
+        <v>246.8160263197884</v>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
@@ -2594,22 +2594,22 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>210.7618081429512</v>
+        <v>210.7618081429513</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>208.7148607457963</v>
+        <v>208.7148607457964</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>207.2914216524927</v>
+        <v>207.2914216524928</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>206.4668160957834</v>
+        <v>206.4668160957835</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>206.2108279038947</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>206.4906048898824</v>
+        <v>206.4906048898825</v>
       </c>
       <c r="I38" s="2" t="n">
         <v>207.2651334141023</v>
@@ -2618,25 +2618,25 @@
         <v>208.4897047254191</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>210.1104609744031</v>
+        <v>210.1104609744029</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>212.0690315173986</v>
+        <v>212.0690315173985</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>214.3006327876198</v>
+        <v>214.3006327876197</v>
       </c>
       <c r="N38" s="2" t="n">
         <v>216.7323962214619</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>219.2881728305481</v>
+        <v>219.2881728305482</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>221.884066646461</v>
+        <v>221.8840666464611</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>224.4327929220607</v>
+        <v>224.4327929220609</v>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
@@ -2651,22 +2651,22 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>271.6930594156025</v>
+        <v>271.6930594156023</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>263.5806325950787</v>
+        <v>263.5806325950786</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>255.4271322666186</v>
+        <v>255.4271322666185</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>247.217375366985</v>
+        <v>247.2173753669849</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>238.9430309708183</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>230.5969050892178</v>
+        <v>230.5969050892176</v>
       </c>
       <c r="I39" s="2" t="n">
         <v>222.179487723706</v>
@@ -2678,22 +2678,22 @@
         <v>205.1462206860301</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>196.5518859932045</v>
+        <v>196.5518859932046</v>
       </c>
       <c r="M39" s="2" t="n">
         <v>187.9265470344896</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>179.2935385859934</v>
+        <v>179.2935385859933</v>
       </c>
       <c r="O39" s="2" t="n">
         <v>170.6786585177232</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>162.1146520852102</v>
+        <v>162.1146520852101</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>153.6378717408677</v>
+        <v>153.6378717408676</v>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
@@ -2711,19 +2711,19 @@
         <v>197.72143536107</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>204.2904132647652</v>
+        <v>204.2904132647651</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>202.4889939477017</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>198.416478315759</v>
+        <v>198.4164783157589</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>193.4931563061065</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>188.1679122287416</v>
+        <v>188.1679122287415</v>
       </c>
       <c r="I40" s="2" t="n">
         <v>182.6368963206165</v>
@@ -2732,25 +2732,25 @@
         <v>176.9808315853231</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>171.2528367629631</v>
+        <v>171.2528367629632</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>165.4883769649388</v>
+        <v>165.4883769649389</v>
       </c>
       <c r="M40" s="2" t="n">
         <v>159.7119364372569</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>153.9496216547928</v>
+        <v>153.9496216547927</v>
       </c>
       <c r="O40" s="2" t="n">
         <v>148.2259193760605</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>142.5689441551483</v>
+        <v>142.5689441551482</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>137.008052164878</v>
+        <v>137.0080521648779</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
@@ -2774,7 +2774,7 @@
         <v>361.4111258356249</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>377.5784039499243</v>
+        <v>377.5784039499244</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>393.0634234348115</v>
@@ -2801,7 +2801,7 @@
         <v>487.1703723797199</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>499.0549259694295</v>
+        <v>499.0549259694296</v>
       </c>
       <c r="P41" s="2" t="n">
         <v>510.6318774865657</v>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>0.9634966919575113</v>
+        <v>0.9634966919575119</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.9025239195527452</v>
+        <v>0.9025239195527458</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>0.8493261902022795</v>
@@ -2834,10 +2834,10 @@
         <v>0.8022724833786353</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.7600334479389863</v>
+        <v>0.7600334479389865</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>0.7217332863543645</v>
+        <v>0.721733286354365</v>
       </c>
       <c r="I42" s="2" t="n">
         <v>0.6866945906418306</v>
@@ -2846,25 +2846,25 @@
         <v>0.6543364519024089</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.624229811236684</v>
+        <v>0.6242298112366838</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0.5959918686650951</v>
+        <v>0.5959918686650948</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>0.5692962495888622</v>
+        <v>0.5692962495888619</v>
       </c>
       <c r="N42" s="2" t="n">
         <v>0.5438847558327973</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>0.5194954107412335</v>
+        <v>0.5194954107412336</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>0.4959029469059165</v>
+        <v>0.4959029469059166</v>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>0.4728976237548239</v>
+        <v>0.4728976237548241</v>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
@@ -2879,22 +2879,22 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>1.012297336253857</v>
+        <v>1.012297336253858</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.9545557258404628</v>
+        <v>0.9545557258404633</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>0.9031825985895713</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.8567715131510852</v>
+        <v>0.8567715131510854</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.8146991568544275</v>
+        <v>0.8146991568544276</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>0.776188270329827</v>
+        <v>0.7761882703298274</v>
       </c>
       <c r="I43" s="2" t="n">
         <v>0.7405474047796768</v>
@@ -2903,25 +2903,25 @@
         <v>0.7074580631056323</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.6763976034649203</v>
+        <v>0.6763976034649201</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0.6470840611245063</v>
+        <v>0.6470840611245059</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>0.6192946645527042</v>
+        <v>0.6192946645527041</v>
       </c>
       <c r="N43" s="2" t="n">
         <v>0.5925760095770414</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>0.5668165391510178</v>
+        <v>0.5668165391510179</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>0.5417699140006728</v>
+        <v>0.5417699140006729</v>
       </c>
       <c r="Q43" s="2" t="n">
-        <v>0.5172591822396889</v>
+        <v>0.5172591822396891</v>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
@@ -2936,22 +2936,22 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>0.810266801412415</v>
+        <v>0.8102668014124158</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.7666797833898039</v>
+        <v>0.7666797833898045</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>0.7286899647968932</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0.6951371042708787</v>
+        <v>0.6951371042708789</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.6654966735829465</v>
+        <v>0.6654966735829467</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>0.6391258250398033</v>
+        <v>0.6391258250398036</v>
       </c>
       <c r="I44" s="2" t="n">
         <v>0.6154468860696426</v>
@@ -2960,25 +2960,25 @@
         <v>0.5941904540151988</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.5749133725656468</v>
+        <v>0.5749133725656465</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0.5573725168712876</v>
+        <v>0.5573725168712873</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.5413756198605114</v>
+        <v>0.5413756198605113</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.5265263523729644</v>
+        <v>0.5265263523729643</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>0.512725897458704</v>
+        <v>0.5127258974587042</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>0.4997576320354004</v>
+        <v>0.4997576320354005</v>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>0.4874696705720054</v>
+        <v>0.4874696705720056</v>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
@@ -2993,22 +2993,22 @@
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>0.6782385842413422</v>
+        <v>0.6782385842413425</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.6409348747810819</v>
+        <v>0.6409348747810822</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.6099312108617738</v>
+        <v>0.6099312108617739</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.5839642163141668</v>
+        <v>0.5839642163141671</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>0.5623586698183529</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>0.5443753293059495</v>
+        <v>0.5443753293059497</v>
       </c>
       <c r="I45" s="2" t="n">
         <v>0.5293569349417038</v>
@@ -3017,25 +3017,25 @@
         <v>0.5169259680265388</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.5065707167473755</v>
+        <v>0.5065707167473752</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0.4979615563447622</v>
+        <v>0.4979615563447621</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>0.4908246248958255</v>
+        <v>0.4908246248958253</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.4847079498592655</v>
+        <v>0.4847079498592656</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>0.4794327098427775</v>
+        <v>0.4794327098427777</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>0.4747187532369734</v>
+        <v>0.4747187532369735</v>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>0.4703500200761768</v>
+        <v>0.4703500200761771</v>
       </c>
     </row>
   </sheetData>

--- a/results/Расчет_ступеней_по_высоте_лопаток.xlsx
+++ b/results/Расчет_ступеней_по_высоте_лопаток.xlsx
@@ -429,14 +429,14 @@
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="21" customWidth="1" min="15" max="15"/>
     <col width="21" customWidth="1" min="16" max="16"/>
@@ -599,49 +599,49 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>143.8937069864959</v>
+        <v>144.5912795806906</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>199.3218027121426</v>
+        <v>199.5330254890436</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>214.6106485564615</v>
+        <v>214.7515744803019</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>223.5946434223144</v>
+        <v>223.7079666847588</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>230.4761436463095</v>
+        <v>230.5749780874513</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>236.4407028896329</v>
+        <v>236.5308769110849</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>241.9664569227971</v>
+        <v>242.0509709478663</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>247.2437889129714</v>
+        <v>247.3245761526613</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>252.378219696918</v>
+        <v>252.4565832985944</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>257.426908181266</v>
+        <v>257.5037757061709</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>262.4129518738098</v>
+        <v>262.4890872885626</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>267.3481807597404</v>
+        <v>267.4241981852856</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>272.2332725443987</v>
+        <v>272.3096948422368</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>277.0606615803001</v>
+        <v>277.137941746648</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>281.8147654251001</v>
+        <v>281.8933098937937</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -722,22 +722,22 @@
         <v>128.7448987217673</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>133.990871492075</v>
+        <v>133.9908714920749</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>139.3317636055374</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>144.777320267659</v>
+        <v>144.7773202676589</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>150.3262849952473</v>
+        <v>150.3262849952472</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>155.9753425546451</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>161.7105041815163</v>
+        <v>161.7105041815162</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>167.5144725567007</v>
@@ -746,10 +746,10 @@
         <v>173.3632742288846</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>179.223925409139</v>
+        <v>179.2239254091391</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>185.0602599758141</v>
+        <v>185.0602599758142</v>
       </c>
       <c r="P5" s="2" t="n">
         <v>190.8267703221602</v>
@@ -941,49 +941,49 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>239.4550476430488</v>
+        <v>239.665056802129</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>258.5548508629961</v>
+        <v>258.6362977561012</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>264.6032607952697</v>
+        <v>264.6604234816028</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>268.2970418587446</v>
+        <v>268.3442706034388</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>271.1930065130997</v>
+        <v>271.2350099942692</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>273.748284703391</v>
+        <v>273.7872317197067</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>276.1519573069561</v>
+        <v>276.1889872079975</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>278.4793815789563</v>
+        <v>278.5152480047076</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>280.772867769074</v>
+        <v>280.8080903606181</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>283.0553424941136</v>
+        <v>283.0902994417929</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>285.3354149805807</v>
+        <v>285.3704274436444</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>287.6170114307365</v>
+        <v>287.6523444613279</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>289.8991164641476</v>
+        <v>289.9350019213152</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>292.1768736300561</v>
+        <v>292.2135174223828</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>294.441507590861</v>
+        <v>294.4790985248634</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
@@ -1055,49 +1055,49 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>196.0816188216095</v>
+        <v>197.1426054034075</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>189.7316836503905</v>
+        <v>190.7577455887468</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>183.3817484791714</v>
+        <v>184.3728857740859</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>177.0318133079523</v>
+        <v>177.9880259594252</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>170.6818781367333</v>
+        <v>171.6031661447644</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>164.3319429655142</v>
+        <v>165.2183063301036</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>157.9820077942951</v>
+        <v>158.8334465154429</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>151.6320726230761</v>
+        <v>152.4485867007821</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>145.282137451857</v>
+        <v>146.0637268861213</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>138.9322022806379</v>
+        <v>139.6788670714606</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>132.5822671094188</v>
+        <v>133.2940072567998</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>126.2323319381998</v>
+        <v>126.909147442139</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>119.8823967669807</v>
+        <v>120.5242876274782</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>113.5324615957616</v>
+        <v>114.1394278128175</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>107.1825264245426</v>
+        <v>107.7545679981567</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
@@ -1283,49 +1283,49 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1.027259602127858</v>
+        <v>1.029645213699535</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.9934702855998885</v>
+        <v>0.9959341338261571</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.9586894843126808</v>
+        <v>0.9612220116865665</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.9229100135873015</v>
+        <v>0.9255002978333444</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.8861805048961304</v>
+        <v>0.8888161674402923</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.8485751747230412</v>
+        <v>0.8512424378085346</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.810224449485951</v>
+        <v>0.8129082640211223</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.7712795787154946</v>
+        <v>0.7739638944609534</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.7319352811294413</v>
+        <v>0.7346034034331341</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0.6923972572989718</v>
+        <v>0.6950322856870597</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0.6528843072915055</v>
+        <v>0.6554696089049291</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.6136243984002564</v>
+        <v>0.6161440934011531</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>0.5748284642310718</v>
+        <v>0.5772678464310962</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>0.5366982795159335</v>
+        <v>0.5390441828190905</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>0.4994059576906553</v>
+        <v>0.501646994611311</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
@@ -1454,49 +1454,49 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1.441916078676133</v>
+        <v>1.439123085381212</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1.19098642640402</v>
+        <v>1.191883731462567</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1.132882090428324</v>
+        <v>1.13432062736136</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1.102244789494197</v>
+        <v>1.103903975620986</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1.08031894092724</v>
+        <v>1.082103261525045</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1.061988888304443</v>
+        <v>1.063856899691283</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1.045162292914204</v>
+        <v>1.047092953362125</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.028975604591301</v>
+        <v>1.030955421008825</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1.012858663989262</v>
+        <v>1.014878483060427</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0.9964147465708389</v>
+        <v>0.9984678757614197</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0.9793475061685438</v>
+        <v>0.9814282532082018</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.961338868965302</v>
+        <v>0.9634423754101273</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>0.942077435657014</v>
+        <v>0.9441991670065244</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>0.9212094507966355</v>
+        <v>0.9233449423630647</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>0.8983629074856447</v>
+        <v>0.9005073713215879</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
@@ -1511,49 +1511,49 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.2030617804976063</v>
+        <v>0.2002687872026845</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.01189560743330653</v>
+        <v>0.01279291249185333</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.01317414360831415</v>
+        <v>0.01461268054135045</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.04130953482780275</v>
+        <v>0.04296872095459237</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.07729233800100932</v>
+        <v>0.07907665859881452</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.1157732484468135</v>
+        <v>0.1176412598336531</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0.1544176645587891</v>
+        <v>0.1563483250067104</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.1921561326445961</v>
+        <v>0.1941359490621192</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.2282236631142278</v>
+        <v>0.2302434821853927</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0.2620730761532963</v>
+        <v>0.2641262053438771</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>0.2932925227158143</v>
+        <v>0.2953732697554723</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.3214786423891008</v>
+        <v>0.3235821488339262</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>0.346281950496667</v>
+        <v>0.3484036818461774</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>0.367337987576842</v>
+        <v>0.3694734791432712</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>0.3843020174697924</v>
+        <v>0.3864464813057356</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
@@ -1568,49 +1568,49 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.2287809001682064</v>
+        <v>0.2263952885965297</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.2526652183537248</v>
+        <v>0.2502013701274561</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.2754912603316733</v>
+        <v>0.2729587329577875</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.2971496555740055</v>
+        <v>0.2945593713279626</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.3174606989651834</v>
+        <v>0.3148250364210214</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.3361552918697575</v>
+        <v>0.3334880287842641</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.3528884034168189</v>
+        <v>0.3502045888816476</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.3672293350409052</v>
+        <v>0.3645450192954464</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.3786817097566066</v>
+        <v>0.3760135874529138</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0.3867063679667102</v>
+        <v>0.3840713395786224</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>0.3907206967611802</v>
+        <v>0.3881353951477565</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.3901606463435489</v>
+        <v>0.3876409513426522</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>0.3845086624801828</v>
+        <v>0.3820692802801584</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>0.373365313230719</v>
+        <v>0.371019409927562</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>0.3595297710510048</v>
+        <v>0.357288734130349</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -1811,10 +1811,10 @@
         <v>139.3317636055374</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>144.777320267659</v>
+        <v>144.7773202676589</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>150.3262849952473</v>
+        <v>150.3262849952472</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>155.9753425546451</v>
@@ -1829,7 +1829,7 @@
         <v>173.3632742288846</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>179.223925409139</v>
+        <v>179.2239254091391</v>
       </c>
       <c r="O24" s="2" t="n">
         <v>185.0602599758142</v>
@@ -1967,49 +1967,49 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>196.0816188216095</v>
+        <v>197.1426054034075</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>189.7316836503905</v>
+        <v>190.7577455887468</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>183.3817484791714</v>
+        <v>184.3728857740859</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>177.0318133079523</v>
+        <v>177.9880259594252</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>170.6818781367333</v>
+        <v>171.6031661447644</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>164.3319429655142</v>
+        <v>165.2183063301036</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>157.9820077942951</v>
+        <v>158.8334465154429</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>151.6320726230761</v>
+        <v>152.4485867007821</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>145.282137451857</v>
+        <v>146.0637268861213</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>138.9322022806379</v>
+        <v>139.6788670714606</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>132.5822671094188</v>
+        <v>133.2940072567998</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>126.2323319381998</v>
+        <v>126.909147442139</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>119.8823967669807</v>
+        <v>120.5242876274782</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>113.5324615957616</v>
+        <v>114.1394278128175</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>107.1825264245426</v>
+        <v>107.7545679981567</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
@@ -2195,49 +2195,49 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>1.027259602127859</v>
+        <v>1.029645213699535</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.9934702855998886</v>
+        <v>0.9959341338261571</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.9586894843126808</v>
+        <v>0.9612220116865665</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.9229100135873016</v>
+        <v>0.9255002978333444</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.8861805048961303</v>
+        <v>0.8888161674402923</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0.8485751747230412</v>
+        <v>0.8512424378085347</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0.8102244494859511</v>
+        <v>0.8129082640211223</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.7712795787154946</v>
+        <v>0.7739638944609536</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.7319352811294413</v>
+        <v>0.7346034034331341</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0.6923972572989718</v>
+        <v>0.6950322856870597</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>0.6528843072915055</v>
+        <v>0.6554696089049293</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.6136243984002564</v>
+        <v>0.6161440934011531</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>0.5748284642310717</v>
+        <v>0.5772678464310962</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>0.5366982795159334</v>
+        <v>0.5390441828190906</v>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>0.4994059576906553</v>
+        <v>0.501646994611311</v>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
@@ -2366,49 +2366,49 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>0.8062590248346274</v>
+        <v>0.8089545389121022</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.8035488409221995</v>
+        <v>0.8062434837670328</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.8008406719728746</v>
+        <v>0.8035342608173265</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.7981955889883425</v>
+        <v>0.8008879209714846</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.7956524962048552</v>
+        <v>0.7983433564079111</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>0.7932503279827852</v>
+        <v>0.7959394914756208</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0.7909985954175668</v>
+        <v>0.7936858305984129</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.788901795817506</v>
+        <v>0.7915868620387772</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.7869287247700167</v>
+        <v>0.7896113696081962</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0.7850315016047533</v>
+        <v>0.7877114535235428</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>0.7831290676610279</v>
+        <v>0.785806026206291</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.7810901365498918</v>
+        <v>0.7837637574907681</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>0.7787448545022608</v>
+        <v>0.7814147274849071</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>0.7758485229457667</v>
+        <v>0.7785141351953598</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>0.7720854603304104</v>
+        <v>0.7747461364395911</v>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
@@ -2423,49 +2423,49 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>0.1202876627174005</v>
+        <v>0.1229831767948754</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.1340508925383452</v>
+        <v>0.1367455353831786</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.1475990361811012</v>
+        <v>0.1502926250255531</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.1610575647021436</v>
+        <v>0.1637498966852857</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.1745102228685959</v>
+        <v>0.1772010830716517</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>0.1880382554345299</v>
+        <v>0.1907274189273656</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0.2016735198839089</v>
+        <v>0.204360755064755</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.2154409838302362</v>
+        <v>0.2181260500515074</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.2293122116286344</v>
+        <v>0.2319948564668138</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0.2432392954111802</v>
+        <v>0.2459192473299696</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>0.2571327100079772</v>
+        <v>0.2598096685532404</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.2708408597134145</v>
+        <v>0.2735144806542908</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>0.2841734700781265</v>
+        <v>0.2868433430607728</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>0.2968547799345136</v>
+        <v>0.2995203921841068</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>0.308537453172937</v>
+        <v>0.3111981292821177</v>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
@@ -2480,49 +2480,49 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>0.2287809001682062</v>
+        <v>0.2263952885965299</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.2526652183537249</v>
+        <v>0.2502013701274564</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.2754912603316733</v>
+        <v>0.2729587329577875</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.2971496555740054</v>
+        <v>0.2945593713279626</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.3174606989651835</v>
+        <v>0.3148250364210214</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>0.3361552918697575</v>
+        <v>0.333488028784264</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0.3528884034168188</v>
+        <v>0.3502045888816476</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.3672293350409052</v>
+        <v>0.3645450192954461</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.3786817097566066</v>
+        <v>0.3760135874529138</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0.3867063679667102</v>
+        <v>0.3840713395786224</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.3907206967611802</v>
+        <v>0.3881353951477563</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.3901606463435489</v>
+        <v>0.3876409513426522</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>0.384508662480183</v>
+        <v>0.3820692802801585</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>0.3733653132307192</v>
+        <v>0.371019409927562</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>0.3595297710510047</v>
+        <v>0.357288734130349</v>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
@@ -2651,49 +2651,49 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>271.6930594156025</v>
+        <v>272.4597661309845</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>263.5806325950787</v>
+        <v>264.3201763023608</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>255.4271322666186</v>
+        <v>256.1396401015171</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>247.217375366985</v>
+        <v>247.9030156032235</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>238.9430309708183</v>
+        <v>239.6019932223987</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>230.5969050892178</v>
+        <v>231.2293967135076</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>222.179487723706</v>
+        <v>222.7857125365669</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>213.6927458785889</v>
+        <v>214.2729002469217</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>205.1462206860301</v>
+        <v>205.7004732883338</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>196.5518859932045</v>
+        <v>197.0803718367314</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>187.9265470344896</v>
+        <v>188.4293551944832</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>179.2935385859934</v>
+        <v>179.7706957671962</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>170.6786585177232</v>
+        <v>171.1301239610516</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>162.1146520852102</v>
+        <v>162.5403013598567</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>153.6378717408677</v>
+        <v>154.0374908481209</v>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
@@ -2708,49 +2708,49 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>197.72143536107</v>
+        <v>198.8640528779965</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>204.2904132647652</v>
+        <v>205.3217452523024</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>202.4889939477017</v>
+        <v>203.4465759940379</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>198.416478315759</v>
+        <v>199.3210840697645</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>193.4931563061065</v>
+        <v>194.352696970997</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>188.1679122287416</v>
+        <v>188.986253212519</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>182.6368963206165</v>
+        <v>183.4161436326712</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>176.9808315853231</v>
+        <v>177.7224073267376</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>171.2528367629631</v>
+        <v>171.9577366302152</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>165.4883769649388</v>
+        <v>166.1573368458161</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>159.7119364372569</v>
+        <v>160.3455734472407</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>153.9496216547928</v>
+        <v>154.548438433642</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>148.2259193760605</v>
+        <v>148.7903484525164</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>142.5689441551483</v>
+        <v>143.0993616131976</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>137.008052164878</v>
+        <v>137.5048058505659</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">

--- a/results/Расчет_ступеней_по_высоте_лопаток.xlsx
+++ b/results/Расчет_ступеней_по_высоте_лопаток.xlsx
@@ -431,15 +431,15 @@
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
     <col width="21" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
@@ -533,7 +533,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>U_вт_1_i</t>
+          <t>u_вт1_i</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -541,26 +541,56 @@
           <t>Окружная скорость во втулочном сечении на входе</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
-      <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
-      <c r="G2" s="1" t="inlineStr"/>
-      <c r="H2" s="1" t="inlineStr"/>
-      <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr"/>
-      <c r="K2" s="1" t="inlineStr"/>
-      <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
-      <c r="N2" s="1" t="inlineStr"/>
-      <c r="O2" s="1" t="inlineStr"/>
-      <c r="P2" s="1" t="inlineStr"/>
-      <c r="Q2" s="1" t="inlineStr"/>
+      <c r="C2" s="2" t="n">
+        <v>131.8158956232372</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>142.4865164189247</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>153.1571372146122</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>163.8277580102997</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>174.4983788059872</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>185.1689996016746</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>195.8396203973622</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>206.5102411930496</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>217.1808619887371</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>227.8514827844246</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>238.5221035801121</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>249.1927243757996</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>259.8633451714871</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>270.5339659671745</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>281.204586762862</v>
+      </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U_вт_2_i</t>
+          <t>u_вт2_i</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
@@ -568,21 +598,51 @@
           <t>Окружная скорость во втулочном сечении на выходе</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr"/>
-      <c r="D3" s="1" t="inlineStr"/>
-      <c r="E3" s="1" t="inlineStr"/>
-      <c r="F3" s="1" t="inlineStr"/>
-      <c r="G3" s="1" t="inlineStr"/>
-      <c r="H3" s="1" t="inlineStr"/>
-      <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr"/>
-      <c r="K3" s="1" t="inlineStr"/>
-      <c r="L3" s="1" t="inlineStr"/>
-      <c r="M3" s="1" t="inlineStr"/>
-      <c r="N3" s="1" t="inlineStr"/>
-      <c r="O3" s="1" t="inlineStr"/>
-      <c r="P3" s="1" t="inlineStr"/>
-      <c r="Q3" s="1" t="inlineStr"/>
+      <c r="C3" s="2" t="n">
+        <v>145.9995670990902</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>151.4349696111518</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>169.1488443304935</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>174.3826274800896</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>177.0337158338059</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>183.0426810447201</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>199.9488219355482</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>205.631461215578</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>206.6116888748281</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>212.215065908898</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>220.4543500749806</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>225.9104548664873</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>235.2409331149642</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>241.1434613249833</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>251.8799421649579</v>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
@@ -596,22 +656,22 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>146.820720406986</v>
+        <v>146.8207204069853</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>135.1231100404073</v>
+        <v>135.1231100404068</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>125.6748939542572</v>
+        <v>125.674893954257</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>117.9963300519682</v>
+        <v>117.996330051968</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>111.7426209016137</v>
+        <v>111.7426209016136</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>106.6513055437714</v>
+        <v>106.6513055437712</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>102.5343463541131</v>
@@ -620,25 +680,25 @@
         <v>99.24562624333812</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>96.68281004633279</v>
+        <v>96.682810046333</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>94.7671839136281</v>
+        <v>94.7671839136283</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>93.44269965819629</v>
+        <v>93.44269965819643</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>92.67399341332711</v>
+        <v>92.67399341332708</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>92.43526386630325</v>
+        <v>92.4352638663032</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>92.71536547308145</v>
+        <v>92.71536547308141</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>93.50957160082369</v>
+        <v>93.50957160082355</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
@@ -653,49 +713,49 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>248.7708115936304</v>
+        <v>248.7708115936307</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>250.1668070928765</v>
+        <v>250.1668070928766</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>233.3244894748944</v>
+        <v>233.3244894748943</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>235.5436084523396</v>
+        <v>235.5436084523393</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>241.2645303043239</v>
+        <v>241.2645303043237</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>242.4641279632687</v>
+        <v>242.4641279632689</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>230.4705320666584</v>
+        <v>230.4705320666581</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>232.5228919245434</v>
+        <v>232.5228919245432</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>239.9289606423911</v>
+        <v>239.9289606423907</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>241.9777591951351</v>
+        <v>241.9777591951348</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>241.0669965458377</v>
+        <v>241.0669965458376</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>243.1974317545935</v>
+        <v>243.1974317545934</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>241.1568507110271</v>
+        <v>241.1568507110269</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>242.5845507424997</v>
+        <v>242.5845507424996</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>239.1167364767257</v>
+        <v>239.1167364767258</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
@@ -710,55 +770,55 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>132.4185940676047</v>
+        <v>132.4185940676041</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>110.8833505652231</v>
+        <v>110.8833505652228</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>120.6945927728266</v>
+        <v>120.6945927728264</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>103.243541288678</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>101.9874795532157</v>
+        <v>101.9874795532155</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>96.5854834042281</v>
+        <v>96.58548340422814</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>100.6418562512798</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>93.21488518827287</v>
+        <v>93.21488518827316</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>86.9585629883387</v>
+        <v>86.95856298833887</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>87.91973405526059</v>
+        <v>87.91973405526092</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>82.05639834291608</v>
+        <v>82.05639834291607</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>85.6427201092505</v>
+        <v>85.64272010925045</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>80.20244419400781</v>
+        <v>80.20244419400788</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>85.72097016087849</v>
+        <v>85.72097016087834</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>82.14967925055809</v>
+        <v>82.14967925055781</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>U_1_ср_i</t>
+          <t>u_ср1_i</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
@@ -766,53 +826,113 @@
           <t>Окружная скорость в среднем сечении на входе</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr"/>
-      <c r="D7" s="1" t="inlineStr"/>
-      <c r="E7" s="1" t="inlineStr"/>
-      <c r="F7" s="1" t="inlineStr"/>
-      <c r="G7" s="1" t="inlineStr"/>
-      <c r="H7" s="1" t="inlineStr"/>
-      <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr"/>
-      <c r="L7" s="1" t="inlineStr"/>
-      <c r="M7" s="1" t="inlineStr"/>
-      <c r="N7" s="1" t="inlineStr"/>
-      <c r="O7" s="1" t="inlineStr"/>
-      <c r="P7" s="1" t="inlineStr"/>
-      <c r="Q7" s="1" t="inlineStr"/>
-    </row>
-    <row r="8" ht="15" customHeight="1">
+      <c r="C7" s="2" t="n">
+        <v>235.9528248528826</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>239.0339391533705</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>242.3109050919186</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>245.7758888376108</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>249.421054623574</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>253.2386218437454</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>257.2209144787189</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>261.3604029790717</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>265.6497389301605</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>270.0817829660258</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>274.6496264965926</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>279.3466078682424</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>284.1663236001668</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>289.1026353348257</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>294.1496731169576</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>U_k2_i</t>
+          <t>u_к2_i</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>Окружная скорость концов лопаток на выходе</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr"/>
-      <c r="D8" s="1" t="inlineStr"/>
-      <c r="E8" s="1" t="inlineStr"/>
-      <c r="F8" s="1" t="inlineStr"/>
-      <c r="G8" s="1" t="inlineStr"/>
-      <c r="H8" s="1" t="inlineStr"/>
-      <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr"/>
-      <c r="K8" s="1" t="inlineStr"/>
-      <c r="L8" s="1" t="inlineStr"/>
-      <c r="M8" s="1" t="inlineStr"/>
-      <c r="N8" s="1" t="inlineStr"/>
-      <c r="O8" s="1" t="inlineStr"/>
-      <c r="P8" s="1" t="inlineStr"/>
-      <c r="Q8" s="1" t="inlineStr"/>
+          <t>Окружная скорость в периферийном сечении на выходе</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>U_2_ср_i</t>
+          <t>u_ср2_i</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
@@ -820,26 +940,56 @@
           <t>Окружная скорость в среднем сечении на выходе</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr"/>
-      <c r="D9" s="1" t="inlineStr"/>
-      <c r="E9" s="1" t="inlineStr"/>
-      <c r="F9" s="1" t="inlineStr"/>
-      <c r="G9" s="1" t="inlineStr"/>
-      <c r="H9" s="1" t="inlineStr"/>
-      <c r="I9" s="1" t="inlineStr"/>
-      <c r="J9" s="1" t="inlineStr"/>
-      <c r="K9" s="1" t="inlineStr"/>
-      <c r="L9" s="1" t="inlineStr"/>
-      <c r="M9" s="1" t="inlineStr"/>
-      <c r="N9" s="1" t="inlineStr"/>
-      <c r="O9" s="1" t="inlineStr"/>
-      <c r="P9" s="1" t="inlineStr"/>
-      <c r="Q9" s="1" t="inlineStr"/>
+      <c r="C9" s="2" t="n">
+        <v>240.0915599998006</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>241.7690952068569</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>247.5715778431518</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>249.3805741632793</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>250.3127816503571</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>252.4645161772176</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>258.7968046234029</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>261.0137339440281</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>261.4004884777979</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>263.6354253243216</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>266.9945329404107</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>269.2652729105047</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>273.2309804780134</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>275.7917780799019</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>280.5490563503793</v>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>c_a1_вт_i</t>
+          <t>c_1a_вт_i</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
@@ -847,26 +997,56 @@
           <t>Осевая скорость (втулка), вход</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr"/>
-      <c r="D10" s="1" t="inlineStr"/>
-      <c r="E10" s="1" t="inlineStr"/>
-      <c r="F10" s="1" t="inlineStr"/>
-      <c r="G10" s="1" t="inlineStr"/>
-      <c r="H10" s="1" t="inlineStr"/>
-      <c r="I10" s="1" t="inlineStr"/>
-      <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr"/>
-      <c r="L10" s="1" t="inlineStr"/>
-      <c r="M10" s="1" t="inlineStr"/>
-      <c r="N10" s="1" t="inlineStr"/>
-      <c r="O10" s="1" t="inlineStr"/>
-      <c r="P10" s="1" t="inlineStr"/>
-      <c r="Q10" s="1" t="inlineStr"/>
+      <c r="C10" s="2" t="n">
+        <v>199.2565864072191</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>192.906651236</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>186.5567160647809</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>180.2067808935618</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>173.8568457223428</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>167.5069105511237</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>161.1569753799047</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>154.8070402086856</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>148.4571050374665</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>142.1071698662474</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>135.7572346950284</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>129.4072995238093</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>123.0573643525902</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>116.7074291813712</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>110.3574940101521</v>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>c_a2_вт_i</t>
+          <t>c_2a_вт_i</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
@@ -874,26 +1054,56 @@
           <t>Осевая скорость (втулка), выход из РК</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr"/>
-      <c r="D11" s="1" t="inlineStr"/>
-      <c r="E11" s="1" t="inlineStr"/>
-      <c r="F11" s="1" t="inlineStr"/>
-      <c r="G11" s="1" t="inlineStr"/>
-      <c r="H11" s="1" t="inlineStr"/>
-      <c r="I11" s="1" t="inlineStr"/>
-      <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr"/>
-      <c r="L11" s="1" t="inlineStr"/>
-      <c r="M11" s="1" t="inlineStr"/>
-      <c r="N11" s="1" t="inlineStr"/>
-      <c r="O11" s="1" t="inlineStr"/>
-      <c r="P11" s="1" t="inlineStr"/>
-      <c r="Q11" s="1" t="inlineStr"/>
+      <c r="C11" s="2" t="n">
+        <v>197.1426054034075</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>190.7577455887468</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>184.3728857740859</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>177.9880259594252</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>171.6031661447644</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>165.2183063301036</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>158.8334465154429</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>152.4485867007821</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>146.0637268861213</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>139.6788670714606</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>133.2940072567998</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>126.909147442139</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>120.5242876274782</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>114.1394278128175</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>107.7545679981567</v>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>c_a3_вт_i</t>
+          <t>c_3a_вт_i</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
@@ -901,21 +1111,51 @@
           <t>Осевая скорость (втулка), выход из ступени</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr"/>
-      <c r="D12" s="1" t="inlineStr"/>
-      <c r="E12" s="1" t="inlineStr"/>
-      <c r="F12" s="1" t="inlineStr"/>
-      <c r="G12" s="1" t="inlineStr"/>
-      <c r="H12" s="1" t="inlineStr"/>
-      <c r="I12" s="1" t="inlineStr"/>
-      <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr"/>
-      <c r="L12" s="1" t="inlineStr"/>
-      <c r="M12" s="1" t="inlineStr"/>
-      <c r="N12" s="1" t="inlineStr"/>
-      <c r="O12" s="1" t="inlineStr"/>
-      <c r="P12" s="1" t="inlineStr"/>
-      <c r="Q12" s="1" t="inlineStr"/>
+      <c r="C12" s="2" t="n">
+        <v>201.4484088576984</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>195.028624399596</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>188.6088399414935</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>182.189055483391</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>175.7692710252886</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>169.3494865671861</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>162.9297021090836</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>156.5099176509811</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>150.0901331928787</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>143.6703487347761</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>137.2505642766737</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>130.8307798185712</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>124.4109953604687</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>117.9912109023662</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>111.5714264442637</v>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
@@ -929,22 +1169,22 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>247.5065881294555</v>
+        <v>247.5065881294551</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>235.5233129821329</v>
+        <v>235.5233129821327</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>224.9390745941866</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>215.401062638403</v>
+        <v>215.4010626384029</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>206.6703078104938</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>198.5776071377965</v>
+        <v>198.5776071377964</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>191.0101120251607</v>
@@ -953,13 +1193,13 @@
         <v>183.8883194403765</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>177.1639856024938</v>
+        <v>177.1639856024939</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>170.8076897399936</v>
+        <v>170.8076897399937</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>164.8076602936068</v>
+        <v>164.8076602936069</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>159.1688355967282</v>
@@ -968,10 +1208,10 @@
         <v>153.9070918685661</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>149.0528866574943</v>
+        <v>149.0528866574942</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>144.6472138175165</v>
+        <v>144.6472138175164</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
@@ -986,22 +1226,22 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.9357693383761195</v>
+        <v>0.9357693383761218</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.9597626880440346</v>
+        <v>0.9597626880440363</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.97797112982242</v>
+        <v>0.9779711298224204</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9910660867781437</v>
+        <v>0.9910660867781445</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9995504016785581</v>
+        <v>0.9995504016785584</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1.003829196966643</v>
+        <v>1.003829196966644</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>1.004155854775696</v>
@@ -1010,25 +1250,25 @@
         <v>1.00070850583557</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.9935423040006223</v>
+        <v>0.9935423040006213</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0.9826521121805142</v>
+        <v>0.9826521121805133</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>0.9679609741964843</v>
+        <v>0.9679609741964836</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.9493188028615026</v>
+        <v>0.9493188028615027</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>0.9265558596622766</v>
+        <v>0.9265558596622768</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>0.8994636845602023</v>
+        <v>0.8994636845602025</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>0.8678525000979801</v>
+        <v>0.8678525000979808</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
@@ -1043,49 +1283,49 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.6701306095578138</v>
+        <v>0.6701306095578132</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.6514672691731751</v>
+        <v>0.6514672691731749</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.6687363691389252</v>
+        <v>0.6687363691389254</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.6471059571111401</v>
+        <v>0.6471059571111407</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.6182468370017625</v>
+        <v>0.6182468370017631</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.5981425179055381</v>
+        <v>0.5981425179055377</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.6034206732604221</v>
+        <v>0.6034206732604228</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.5803216712473841</v>
+        <v>0.5803216712473845</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.5468496968550552</v>
+        <v>0.5468496968550559</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0.5235149084448187</v>
+        <v>0.5235149084448194</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0.5050925934805094</v>
+        <v>0.5050925934805096</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.4809633307626583</v>
+        <v>0.4809633307626585</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>0.4634679994591497</v>
+        <v>0.46346799945915</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>0.439781806577173</v>
+        <v>0.4397818065771732</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>0.4233825535435953</v>
+        <v>0.4233825535435952</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
@@ -1100,10 +1340,10 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.9892836800361827</v>
+        <v>0.9892836800361847</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1.053823576871488</v>
+        <v>1.053823576871489</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>1.001539801476524</v>
@@ -1112,7 +1352,7 @@
         <v>1.055234537470887</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1.045036720179754</v>
+        <v>1.045036720179755</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>1.052477017347905</v>
@@ -1121,28 +1361,28 @@
         <v>1.017462884162148</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.033629823651341</v>
+        <v>1.033629823651339</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1.045679875184491</v>
+        <v>1.04567987518449</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1.021633002567162</v>
+        <v>1.02163300256716</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>1.031953044022862</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.9911893859798868</v>
+        <v>0.9911893859798871</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>0.9981862014797537</v>
+        <v>0.9981862014797532</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>0.9425036598425223</v>
+        <v>0.9425036598425232</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>0.9361231330451247</v>
+        <v>0.9361231330451264</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
@@ -1157,22 +1397,22 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-1.495634152443003</v>
+        <v>-1.495634152443007</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1.532644022227341</v>
+        <v>1.532644022227338</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1.424535210134284</v>
+        <v>1.424535210134283</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1.321749472258416</v>
+        <v>1.321749472258415</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1.224389158914516</v>
+        <v>1.224389158914515</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1.132465494757526</v>
+        <v>1.132465494757525</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>1.045982582658903</v>
@@ -1181,25 +1421,25 @@
         <v>0.9648565380841142</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.8889804416835984</v>
+        <v>0.8889804416835992</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0.8181740333860354</v>
+        <v>0.818174033386036</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0.7522160699711019</v>
+        <v>0.7522160699711024</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.6908610696384311</v>
+        <v>0.690861069638431</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>0.6338229652055751</v>
+        <v>0.633822965205575</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>0.5808112756428321</v>
+        <v>0.580811275642832</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>0.5315208362072309</v>
+        <v>0.5315208362072307</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
@@ -1220,43 +1460,43 @@
         <v>2.048406519628786</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1.905755451914805</v>
+        <v>1.905755451914803</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1.901779832706976</v>
+        <v>1.901779832706973</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1.928951876262905</v>
+        <v>1.928951876262902</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1.916045689327377</v>
+        <v>1.916045689327378</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1.760643855719956</v>
+        <v>1.760643855719953</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.7453968878768</v>
+        <v>1.745396887876798</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1.795060310503146</v>
+        <v>1.795060310503142</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1.780736049328555</v>
+        <v>1.780736049328552</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1.724221502183452</v>
+        <v>1.72422150218345</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>1.70617848141086</v>
+        <v>1.706178481410858</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1.619841821685546</v>
+        <v>1.619841821685542</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>1.583421349354248</v>
+        <v>1.583421349354246</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>4.59449128532887</v>
+        <v>4.594491285328869</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
@@ -1271,49 +1511,49 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>3.546975734384747</v>
+        <v>3.546975734384751</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.5157624974014454</v>
+        <v>0.5157624974014474</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.4812202417805209</v>
+        <v>0.4812202417805203</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.5800303604485604</v>
+        <v>0.5800303604485579</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.7045627173483888</v>
+        <v>0.7045627173483866</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.7835801945698511</v>
+        <v>0.7835801945698533</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0.7146612730610531</v>
+        <v>0.71466127306105</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.7805403497926863</v>
+        <v>0.7805403497926841</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.9060798688195472</v>
+        <v>0.9060798688195429</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0.9625620159425197</v>
+        <v>0.9625620159425156</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>0.9720054322123503</v>
+        <v>0.972005432212348</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1.015317411772429</v>
+        <v>1.015317411772428</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>0.986018856479971</v>
+        <v>0.9860188564799671</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>1.002610073711416</v>
+        <v>1.002610073711414</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>4.062970449121639</v>
+        <v>4.062970449121638</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
@@ -1328,55 +1568,55 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.3191530704783689</v>
+        <v>0.3191530704783715</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.4023563076983128</v>
+        <v>0.4023563076983141</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.3328034323375986</v>
+        <v>0.332803432337599</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.4081285803597469</v>
+        <v>0.4081285803597462</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.4267898831779912</v>
+        <v>0.4267898831779915</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.4543344994423667</v>
+        <v>0.454334499442367</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.4140422109017263</v>
+        <v>0.4140422109017257</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.4533081524039565</v>
+        <v>0.4533081524039547</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.4988301783294361</v>
+        <v>0.4988301783294345</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0.4981180941223431</v>
+        <v>0.4981180941223406</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>0.5268604505423528</v>
+        <v>0.5268604505423525</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.5102260552172284</v>
+        <v>0.5102260552172286</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>0.534718202020604</v>
+        <v>0.5347182020206032</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>0.5027218532653492</v>
+        <v>0.5027218532653499</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>0.5127405795015294</v>
+        <v>0.5127405795015312</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>U_к_1_i</t>
+          <t>u_к1_i</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
@@ -1384,26 +1624,56 @@
           <t>Окружная скорость в периферийном сечении на входе</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr"/>
-      <c r="D21" s="1" t="inlineStr"/>
-      <c r="E21" s="1" t="inlineStr"/>
-      <c r="F21" s="1" t="inlineStr"/>
-      <c r="G21" s="1" t="inlineStr"/>
-      <c r="H21" s="1" t="inlineStr"/>
-      <c r="I21" s="1" t="inlineStr"/>
-      <c r="J21" s="1" t="inlineStr"/>
-      <c r="K21" s="1" t="inlineStr"/>
-      <c r="L21" s="1" t="inlineStr"/>
-      <c r="M21" s="1" t="inlineStr"/>
-      <c r="N21" s="1" t="inlineStr"/>
-      <c r="O21" s="1" t="inlineStr"/>
-      <c r="P21" s="1" t="inlineStr"/>
-      <c r="Q21" s="1" t="inlineStr"/>
+      <c r="C21" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>U_к_2_i</t>
+          <t>u_к2_i</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
@@ -1411,21 +1681,51 @@
           <t>Окружная скорость в периферийном сечении на выходе</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr"/>
-      <c r="D22" s="1" t="inlineStr"/>
-      <c r="E22" s="1" t="inlineStr"/>
-      <c r="F22" s="1" t="inlineStr"/>
-      <c r="G22" s="1" t="inlineStr"/>
-      <c r="H22" s="1" t="inlineStr"/>
-      <c r="I22" s="1" t="inlineStr"/>
-      <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr"/>
-      <c r="L22" s="1" t="inlineStr"/>
-      <c r="M22" s="1" t="inlineStr"/>
-      <c r="N22" s="1" t="inlineStr"/>
-      <c r="O22" s="1" t="inlineStr"/>
-      <c r="P22" s="1" t="inlineStr"/>
-      <c r="Q22" s="1" t="inlineStr"/>
+      <c r="C22" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>306.5485944726447</v>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
@@ -1439,22 +1739,22 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>63.13290977500399</v>
+        <v>63.13290977500368</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>62.80642477082618</v>
+        <v>62.80642477082594</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>62.78941520151587</v>
+        <v>62.78941520151579</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>63.06039092794581</v>
+        <v>63.0603909279457</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>63.60787993305777</v>
+        <v>63.60787993305775</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>64.42213701134742</v>
+        <v>64.42213701134727</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>65.50441864600705</v>
@@ -1463,25 +1763,25 @@
         <v>66.85804007069403</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>68.49699004974445</v>
+        <v>68.4969900497446</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>70.4385659023183</v>
+        <v>70.43856590231846</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>72.70674107972958</v>
+        <v>72.7067410797297</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>75.33449937090704</v>
+        <v>75.33449937090701</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>78.35800689750073</v>
+        <v>78.35800689750069</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>81.82277126626022</v>
+        <v>81.82277126626018</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>85.77863645278721</v>
+        <v>85.77863645278708</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
@@ -1496,37 +1796,37 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>118.4818050203144</v>
+        <v>118.4818050203147</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>123.5823732775562</v>
+        <v>123.5823732775564</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>128.7448987217673</v>
+        <v>128.7448987217674</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>133.990871492075</v>
+        <v>133.9908714920751</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>139.3317636055374</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>144.777320267659</v>
+        <v>144.7773202676591</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>150.3262849952473</v>
+        <v>150.3262849952472</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>155.9753425546452</v>
+        <v>155.9753425546451</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>161.7105041815163</v>
+        <v>161.7105041815161</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>167.5144725567007</v>
+        <v>167.5144725567006</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>173.3632742288846</v>
+        <v>173.3632742288845</v>
       </c>
       <c r="N24" s="2" t="n">
         <v>179.223925409139</v>
@@ -1538,7 +1838,7 @@
         <v>190.8267703221602</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>196.4736124725756</v>
+        <v>196.4736124725758</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
@@ -1553,7 +1853,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>69.10460548639993</v>
+        <v>69.10460548639976</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>66.72746659113298</v>
@@ -1562,46 +1862,46 @@
         <v>71.2233240437417</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>68.95847535548729</v>
+        <v>68.95847535548742</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>65.1272143989743</v>
+        <v>65.12721439897426</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>63.31386711620316</v>
+        <v>63.3138671162033</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>68.7254529473923</v>
+        <v>68.72545294739244</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>66.96644031474798</v>
+        <v>66.96644031474831</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>61.96955708524636</v>
+        <v>61.96955708524656</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>60.25270430821459</v>
+        <v>60.25270430821484</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>60.58961621578489</v>
+        <v>60.58961621578496</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>59.11856899885703</v>
+        <v>59.11856899885709</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>60.85362392937763</v>
+        <v>60.85362392937776</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>60.30788612638593</v>
+        <v>60.30788612638592</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>63.7044893532279</v>
+        <v>63.70448935322771</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>c_a1_к_i</t>
+          <t>c_1a_к_i</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
@@ -1609,26 +1909,56 @@
           <t>Осевая скорость (периферия), вход</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr"/>
-      <c r="D26" s="1" t="inlineStr"/>
-      <c r="E26" s="1" t="inlineStr"/>
-      <c r="F26" s="1" t="inlineStr"/>
-      <c r="G26" s="1" t="inlineStr"/>
-      <c r="H26" s="1" t="inlineStr"/>
-      <c r="I26" s="1" t="inlineStr"/>
-      <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr"/>
-      <c r="L26" s="1" t="inlineStr"/>
-      <c r="M26" s="1" t="inlineStr"/>
-      <c r="N26" s="1" t="inlineStr"/>
-      <c r="O26" s="1" t="inlineStr"/>
-      <c r="P26" s="1" t="inlineStr"/>
-      <c r="Q26" s="1" t="inlineStr"/>
+      <c r="C26" s="2" t="n">
+        <v>199.2565864072191</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>192.906651236</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>186.5567160647809</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>180.2067808935618</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>173.8568457223428</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>167.5069105511237</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>161.1569753799047</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>154.8070402086856</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>148.4571050374665</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>142.1071698662474</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>135.7572346950284</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>129.4072995238093</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>123.0573643525902</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>116.7074291813712</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>110.3574940101521</v>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>c_a2_к_i</t>
+          <t>c_2a_к_i</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
@@ -1636,26 +1966,56 @@
           <t>Осевая скорость (периферия), выход из РК</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr"/>
-      <c r="D27" s="1" t="inlineStr"/>
-      <c r="E27" s="1" t="inlineStr"/>
-      <c r="F27" s="1" t="inlineStr"/>
-      <c r="G27" s="1" t="inlineStr"/>
-      <c r="H27" s="1" t="inlineStr"/>
-      <c r="I27" s="1" t="inlineStr"/>
-      <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr"/>
-      <c r="L27" s="1" t="inlineStr"/>
-      <c r="M27" s="1" t="inlineStr"/>
-      <c r="N27" s="1" t="inlineStr"/>
-      <c r="O27" s="1" t="inlineStr"/>
-      <c r="P27" s="1" t="inlineStr"/>
-      <c r="Q27" s="1" t="inlineStr"/>
+      <c r="C27" s="2" t="n">
+        <v>197.1426054034075</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>190.7577455887468</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>184.3728857740859</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>177.9880259594252</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>171.6031661447644</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>165.2183063301036</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>158.8334465154429</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>152.4485867007821</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>146.0637268861213</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>139.6788670714606</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>133.2940072567998</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>126.909147442139</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>120.5242876274782</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>114.1394278128175</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>107.7545679981567</v>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>c_a3_к_i</t>
+          <t>c_3a_к_i</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
@@ -1663,21 +2023,51 @@
           <t>Осевая скорость (периферия), выход из ступени</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr"/>
-      <c r="D28" s="1" t="inlineStr"/>
-      <c r="E28" s="1" t="inlineStr"/>
-      <c r="F28" s="1" t="inlineStr"/>
-      <c r="G28" s="1" t="inlineStr"/>
-      <c r="H28" s="1" t="inlineStr"/>
-      <c r="I28" s="1" t="inlineStr"/>
-      <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr"/>
-      <c r="L28" s="1" t="inlineStr"/>
-      <c r="M28" s="1" t="inlineStr"/>
-      <c r="N28" s="1" t="inlineStr"/>
-      <c r="O28" s="1" t="inlineStr"/>
-      <c r="P28" s="1" t="inlineStr"/>
-      <c r="Q28" s="1" t="inlineStr"/>
+      <c r="C28" s="2" t="n">
+        <v>201.4484088576984</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>195.028624399596</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>188.6088399414935</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>182.189055483391</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>175.7692710252886</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>169.3494865671861</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>162.9297021090836</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>156.5099176509811</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>150.0901331928787</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>143.6703487347761</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>137.2505642766737</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>130.8307798185712</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>124.4109953604687</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>117.9912109023662</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>111.5714264442637</v>
+      </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
@@ -1691,13 +2081,13 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>209.0190219174235</v>
+        <v>209.0190219174234</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>202.8734164043707</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>196.839830751359</v>
+        <v>196.8398307513589</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>190.9217032817525</v>
@@ -1706,7 +2096,7 @@
         <v>185.1274296102574</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>179.4680384343992</v>
+        <v>179.4680384343991</v>
       </c>
       <c r="I29" s="2" t="n">
         <v>173.96091393112</v>
@@ -1715,25 +2105,25 @@
         <v>168.6274509688981</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>163.497246710702</v>
+        <v>163.4972467107021</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>158.6065550151372</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>154.0009641868383</v>
+        <v>154.0009641868384</v>
       </c>
       <c r="N29" s="2" t="n">
         <v>149.7382247975115</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>145.8872584098931</v>
+        <v>145.887258409893</v>
       </c>
       <c r="P29" s="2" t="n">
         <v>142.5327678950195</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>139.7739280262961</v>
+        <v>139.773928026296</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
@@ -1748,16 +2138,16 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>1.263960413517294</v>
+        <v>1.263960413517295</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1.256040502296065</v>
+        <v>1.256040502296066</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1.246135503953613</v>
+        <v>1.246135503953614</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1.234180744644354</v>
+        <v>1.234180744644355</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>1.220059669161307</v>
@@ -1772,25 +2162,25 @@
         <v>1.16311285290277</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1.1385089137564</v>
+        <v>1.138508913756399</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1.110616990886048</v>
+        <v>1.110616990886047</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1.079103625265682</v>
+        <v>1.079103625265681</v>
       </c>
       <c r="N30" s="2" t="n">
         <v>1.043605004052686</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1.003785044743805</v>
+        <v>1.003785044743806</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>0.9593371267112547</v>
+        <v>0.9593371267112549</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>0.9100635927466526</v>
+        <v>0.9100635927466533</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
@@ -1805,40 +2195,40 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>1.029645213699535</v>
+        <v>1.029645213699534</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.9959341338261571</v>
+        <v>0.9959341338261564</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.9612220116865666</v>
+        <v>0.9612220116865663</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.9255002978333443</v>
+        <v>0.925500297833344</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.8888161674402923</v>
+        <v>0.8888161674402922</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0.8512424378085345</v>
+        <v>0.8512424378085339</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0.812908264021122</v>
+        <v>0.8129082640211223</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.7739638944609533</v>
+        <v>0.7739638944609534</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.734603403433134</v>
+        <v>0.7346034034331345</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0.6950322856870598</v>
+        <v>0.6950322856870601</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>0.6554696089049291</v>
+        <v>0.6554696089049294</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.6161440934011533</v>
+        <v>0.6161440934011532</v>
       </c>
       <c r="O31" s="2" t="n">
         <v>0.5772678464310962</v>
@@ -1847,7 +2237,7 @@
         <v>0.5390441828190906</v>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>0.501646994611311</v>
+        <v>0.5016469946113107</v>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
@@ -1862,7 +2252,7 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>1.240336498118821</v>
+        <v>1.240336498118822</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>1.241139110073123</v>
@@ -1877,34 +2267,34 @@
         <v>1.215953177530597</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>1.21302098567914</v>
+        <v>1.213020985679139</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1.171630345421313</v>
+        <v>1.171630345421312</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.166494350842133</v>
+        <v>1.166494350842132</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1.179234096373354</v>
+        <v>1.179234096373353</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1.17369410163869</v>
+        <v>1.173694101638688</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1.155073127145677</v>
+        <v>1.155073127145676</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>1.146387986290166</v>
+        <v>1.146387986290165</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1.115879398144555</v>
+        <v>1.115879398144554</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>1.098290875881704</v>
+        <v>1.098290875881705</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>1.051992242046127</v>
+        <v>1.051992242046128</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
@@ -1919,22 +2309,22 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>0.6859713621172269</v>
+        <v>0.6859713621172262</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.6694979483838543</v>
+        <v>0.6694979483838538</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>0.6532416357917733</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.6371380242861989</v>
+        <v>0.6371380242861987</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.6211422733362594</v>
+        <v>0.6211422733362593</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>0.6052120725482553</v>
+        <v>0.6052120725482549</v>
       </c>
       <c r="I33" s="2" t="n">
         <v>0.5893250755336579</v>
@@ -1943,25 +2333,25 @@
         <v>0.5734608119872697</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.5576165131413824</v>
+        <v>0.5576165131413827</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0.5417922061935732</v>
+        <v>0.5417922061935735</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>0.5259963576530506</v>
+        <v>0.5259963576530508</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.5102492768364773</v>
+        <v>0.5102492768364771</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>0.4945713844241343</v>
+        <v>0.4945713844241342</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>0.478993743011253</v>
+        <v>0.4789937430112529</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>0.4635480071574734</v>
+        <v>0.4635480071574731</v>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
@@ -1976,7 +2366,7 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>2.332638114677691</v>
+        <v>2.33263811467769</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>2.33534916982276</v>
@@ -2033,7 +2423,7 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>1.646666752560464</v>
+        <v>1.646666752560463</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>1.665851221438906</v>
@@ -2057,10 +2447,10 @@
         <v>1.776544979563746</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1.794364770840214</v>
+        <v>1.794364770840215</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>1.812088993872677</v>
+        <v>1.812088993872678</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>1.829790269730451</v>
@@ -2069,13 +2459,13 @@
         <v>1.847579619262548</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>1.865606541680751</v>
+        <v>1.865606541680752</v>
       </c>
       <c r="P35" s="2" t="n">
         <v>1.88408477538318</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>1.903298509992729</v>
+        <v>1.903298509992728</v>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
@@ -2090,49 +2480,49 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>0.2106912844192863</v>
+        <v>0.2106912844192881</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.2452049762469657</v>
+        <v>0.2452049762469665</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.2485046770583867</v>
+        <v>0.2485046770583871</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.2834607963264969</v>
+        <v>0.2834607963264966</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.3271370100903046</v>
+        <v>0.3271370100903049</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>0.3617785478706056</v>
+        <v>0.3617785478706055</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0.3587220814001908</v>
+        <v>0.3587220814001899</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.3925304563811802</v>
+        <v>0.3925304563811783</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.4446306929402198</v>
+        <v>0.4446306929402181</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0.4786618159516299</v>
+        <v>0.478661815951628</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.4996035182407476</v>
+        <v>0.499603518240747</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.5302438928890125</v>
+        <v>0.5302438928890122</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>0.5386115517134585</v>
+        <v>0.5386115517134576</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>0.5592466930626139</v>
+        <v>0.5592466930626141</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>0.5503452474348157</v>
+        <v>0.5503452474348174</v>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
@@ -2258,46 +2648,46 @@
         <v>326.4880494232335</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>337.4424622869855</v>
+        <v>337.4424622869856</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>348.829328466098</v>
+        <v>348.8293284660982</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>360.6202868898617</v>
+        <v>360.6202868898619</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>372.5982660259929</v>
+        <v>372.598266025993</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>384.7242675588149</v>
+        <v>384.7242675588152</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>396.91753897224</v>
+        <v>396.9175389722403</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>409.4131693996462</v>
+        <v>409.4131693996464</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>422.0815291621177</v>
+        <v>422.0815291621179</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>434.7461463191176</v>
+        <v>434.7461463191179</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>447.5145695556853</v>
+        <v>447.5145695556855</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>460.2827537395842</v>
+        <v>460.2827537395844</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>472.9969691502184</v>
+        <v>472.9969691502186</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>485.5860288731274</v>
+        <v>485.5860288731276</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>497.9893327862694</v>
+        <v>497.9893327862697</v>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
@@ -2312,46 +2702,46 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>0.9634966919575113</v>
+        <v>0.9634966919575121</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.9211726283436643</v>
+        <v>0.9211726283436646</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.8799602256853251</v>
+        <v>0.8799602256853244</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0.8399992313786921</v>
+        <v>0.8399992313786919</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.8017786882320623</v>
+        <v>0.8017786882320621</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>0.7652782234817966</v>
+        <v>0.7652782234817965</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0.7305168162076927</v>
+        <v>0.7305168162076922</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.6969396244353216</v>
+        <v>0.6969396244353212</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.664681065694759</v>
+        <v>0.6646810656947584</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0.6338790507319797</v>
+        <v>0.6338790507319788</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>0.604209110518214</v>
+        <v>0.6042091105182137</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.5756560220386332</v>
+        <v>0.575656022038633</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>0.54811502114845</v>
+        <v>0.5481150211484498</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>0.5214809277304198</v>
+        <v>0.5214809277304197</v>
       </c>
       <c r="Q42" s="2" t="n">
         <v>0.4956251270260009</v>
@@ -2369,46 +2759,46 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>1.012297336253857</v>
+        <v>1.012297336253858</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.9725887174584144</v>
+        <v>0.9725887174584149</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.9330888303600683</v>
+        <v>0.9330888303600676</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.8946478786195227</v>
+        <v>0.8946478786195223</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.8571508678094153</v>
+        <v>0.8571508678094151</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>0.8207833645907787</v>
+        <v>0.8207833645907786</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0.7853054219755479</v>
+        <v>0.7853054219755472</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.7511465582408772</v>
+        <v>0.7511465582408767</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.7183524565510467</v>
+        <v>0.718352456551046</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0.6863184834034433</v>
+        <v>0.6863184834034425</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>0.6554562172406868</v>
+        <v>0.6554562172406863</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.6255980224771898</v>
+        <v>0.6255980224771895</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>0.5966899684120511</v>
+        <v>0.596689968412051</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>0.5685822338124686</v>
+        <v>0.5685822338124685</v>
       </c>
       <c r="Q43" s="2" t="n">
         <v>0.541104445941942</v>
@@ -2426,46 +2816,46 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>0.810266801412415</v>
+        <v>0.8102668014124158</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.7811635162230529</v>
+        <v>0.7811635162230534</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.7528183869012189</v>
+        <v>0.7528183869012187</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>0.7258678960956438</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.7001738574130227</v>
+        <v>0.7001738574130226</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>0.6758461382701839</v>
+        <v>0.6758461382701838</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0.6526439407511666</v>
+        <v>0.6526439407511662</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.6308842004200312</v>
+        <v>0.6308842004200309</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.6105734724236028</v>
+        <v>0.610573472423602</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0.5911674903645295</v>
+        <v>0.5911674903645289</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.5729873616082219</v>
+        <v>0.5729873616082214</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.5558676684561757</v>
+        <v>0.5558676684561754</v>
       </c>
       <c r="O44" s="2" t="n">
         <v>0.5397485401835868</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>0.5244907541823461</v>
+        <v>0.524490754182346</v>
       </c>
       <c r="Q44" s="2" t="n">
         <v>0.5099416599358474</v>
@@ -2483,49 +2873,49 @@
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>-0.6430298902039351</v>
+        <v>-0.6430298902039349</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>0.604020708966129</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.5732179531473994</v>
+        <v>0.5732179531473992</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.5491667199573567</v>
+        <v>0.5491667199573566</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.5303339006039507</v>
+        <v>0.5303339006039506</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>0.5157300205707432</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0.5043495450443859</v>
+        <v>0.5043495450443856</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.4957970362550228</v>
+        <v>0.4957970362550225</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.4895835511668041</v>
+        <v>0.4895835511668035</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0.4848828653376094</v>
+        <v>0.4848828653376089</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>0.4816450944088743</v>
+        <v>0.4816450944088738</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.4795014324833634</v>
+        <v>0.4795014324833632</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>0.4782293678742363</v>
+        <v>0.4782293678742361</v>
       </c>
       <c r="P45" s="2" t="n">
         <v>0.4775846381673637</v>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>0.4773472857509931</v>
+        <v>0.477347285750993</v>
       </c>
     </row>
   </sheetData>
